--- a/data/audio_interfaces.xlsx
+++ b/data/audio_interfaces.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>ADAT入力 (ch)</t>
+          <t>ADAT入力 (ch@48kHz)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>ADAT出力 (ch)</t>
+          <t>ADAT出力 (ch@48kHz)</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -19236,7 +19236,7 @@
       <c r="U176" s="11" t="n"/>
       <c r="V176" s="11" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>○ (UAD)</t>
         </is>
       </c>
       <c r="W176" s="11" t="inlineStr">
@@ -19352,7 +19352,7 @@
       </c>
       <c r="V177" s="13" t="inlineStr">
         <is>
-          <t>○ (UAD DUO Core DSP)</t>
+          <t>○ (UAD)</t>
         </is>
       </c>
       <c r="W177" s="13" t="inlineStr">
@@ -19464,7 +19464,7 @@
       </c>
       <c r="V178" s="11" t="inlineStr">
         <is>
-          <t>○ (UAD QUAD Core DSP)</t>
+          <t>○ (UAD)</t>
         </is>
       </c>
       <c r="W178" s="11" t="inlineStr">
@@ -19570,7 +19570,7 @@
       <c r="U179" s="13" t="n"/>
       <c r="V179" s="13" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>○ (UAD)</t>
         </is>
       </c>
       <c r="W179" s="13" t="inlineStr">
@@ -19674,7 +19674,7 @@
       <c r="U180" s="11" t="n"/>
       <c r="V180" s="11" t="inlineStr">
         <is>
-          <t>○ (HEXA Core UAD)</t>
+          <t>○ (UAD)</t>
         </is>
       </c>
       <c r="W180" s="11" t="inlineStr">
@@ -19790,7 +19790,7 @@
       <c r="U181" s="13" t="n"/>
       <c r="V181" s="13" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>○ (UAD)</t>
         </is>
       </c>
       <c r="W181" s="13" t="inlineStr">
@@ -19803,17 +19803,11 @@
           <t>10-65</t>
         </is>
       </c>
-      <c r="Y181" s="14" t="n">
-        <v>129</v>
-      </c>
+      <c r="Y181" s="14" t="n"/>
       <c r="Z181" s="14" t="n">
         <v>129</v>
       </c>
-      <c r="AA181" s="13" t="inlineStr">
-        <is>
-          <t>設計値</t>
-        </is>
-      </c>
+      <c r="AA181" s="13" t="n"/>
       <c r="AB181" s="13" t="n"/>
       <c r="AC181" s="13" t="inlineStr">
         <is>
@@ -19825,12 +19819,12 @@
       <c r="AF181" s="13" t="n"/>
       <c r="AG181" s="13" t="inlineStr">
         <is>
-          <t>iOS/iPadOS/macOS/Windows</t>
+          <t>macOS/Windows</t>
         </is>
       </c>
       <c r="AH181" s="13" t="inlineStr">
         <is>
-          <t>UAD Studio+, Neve, API, Manley, Fender emulations</t>
+          <t>Realtime Analog Classics Plus (Essentials+ or Studio+ available)</t>
         </is>
       </c>
       <c r="AI181" s="13" t="inlineStr">
@@ -19916,7 +19910,7 @@
       <c r="U182" s="11" t="n"/>
       <c r="V182" s="11" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>○ (UAD)</t>
         </is>
       </c>
       <c r="W182" s="11" t="inlineStr">
@@ -20036,7 +20030,7 @@
       <c r="U183" s="13" t="n"/>
       <c r="V183" s="13" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>○ (UAD)</t>
         </is>
       </c>
       <c r="W183" s="13" t="inlineStr">
@@ -20154,7 +20148,7 @@
       <c r="U184" s="11" t="n"/>
       <c r="V184" s="11" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>○ (UAD)</t>
         </is>
       </c>
       <c r="W184" s="11" t="inlineStr">

--- a/data/audio_interfaces.xlsx
+++ b/data/audio_interfaces.xlsx
@@ -3278,9 +3278,7 @@
       <c r="K26" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L26" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="L26" s="12" t="n"/>
       <c r="M26" s="12" t="n">
         <v>1</v>
       </c>
@@ -3372,9 +3370,7 @@
       <c r="K27" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="L27" s="14" t="n"/>
       <c r="M27" s="14" t="n">
         <v>1</v>
       </c>
@@ -3798,9 +3794,7 @@
       <c r="K31" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="L31" s="14" t="n"/>
       <c r="M31" s="14" t="n">
         <v>1</v>
       </c>
@@ -4280,9 +4274,7 @@
       <c r="K35" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="L35" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="L35" s="14" t="n"/>
       <c r="M35" s="14" t="n">
         <v>1</v>
       </c>
@@ -4898,12 +4890,8 @@
       <c r="K40" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="L40" s="12" t="n"/>
+      <c r="M40" s="12" t="n"/>
       <c r="N40" s="12" t="n">
         <v>16</v>
       </c>
@@ -5406,9 +5394,7 @@
       <c r="K45" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="L45" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="L45" s="14" t="n"/>
       <c r="M45" s="14" t="n">
         <v>1</v>
       </c>
@@ -5596,9 +5582,7 @@
       <c r="K47" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="L47" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="L47" s="14" t="n"/>
       <c r="M47" s="14" t="n">
         <v>1</v>
       </c>
@@ -8298,9 +8282,7 @@
       <c r="K73" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="L73" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="L73" s="14" t="n"/>
       <c r="M73" s="14" t="n">
         <v>1</v>
       </c>
@@ -8530,9 +8512,7 @@
       <c r="K75" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="L75" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="L75" s="14" t="n"/>
       <c r="M75" s="14" t="n">
         <v>1</v>
       </c>
@@ -11076,9 +11056,7 @@
       <c r="K99" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="L99" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="L99" s="14" t="n"/>
       <c r="M99" s="14" t="n">
         <v>1</v>
       </c>
@@ -11166,9 +11144,7 @@
       <c r="K100" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L100" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="L100" s="12" t="n"/>
       <c r="M100" s="12" t="n">
         <v>1</v>
       </c>
@@ -12787,9 +12763,7 @@
       <c r="H115" s="13" t="n"/>
       <c r="I115" s="13" t="n"/>
       <c r="J115" s="13" t="n"/>
-      <c r="K115" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="K115" s="14" t="n"/>
       <c r="L115" s="14" t="n">
         <v>2</v>
       </c>
@@ -12895,9 +12869,7 @@
       <c r="H116" s="11" t="n"/>
       <c r="I116" s="11" t="n"/>
       <c r="J116" s="11" t="n"/>
-      <c r="K116" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="K116" s="12" t="n"/>
       <c r="L116" s="12" t="n">
         <v>4</v>
       </c>
@@ -13007,9 +12979,7 @@
       <c r="H117" s="13" t="n"/>
       <c r="I117" s="13" t="n"/>
       <c r="J117" s="13" t="n"/>
-      <c r="K117" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="K117" s="14" t="n"/>
       <c r="L117" s="14" t="n">
         <v>4</v>
       </c>
@@ -13254,9 +13224,7 @@
       <c r="K119" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="L119" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="L119" s="14" t="n"/>
       <c r="M119" s="14" t="n">
         <v>1</v>
       </c>
@@ -13348,9 +13316,7 @@
       <c r="K120" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L120" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="L120" s="12" t="n"/>
       <c r="M120" s="12" t="n">
         <v>1</v>
       </c>
@@ -13900,9 +13866,7 @@
       <c r="K125" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="L125" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="L125" s="14" t="n"/>
       <c r="M125" s="14" t="n">
         <v>1</v>
       </c>
@@ -14432,9 +14396,7 @@
       <c r="K130" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L130" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="L130" s="12" t="n"/>
       <c r="M130" s="12" t="n">
         <v>1</v>
       </c>
@@ -15485,9 +15447,7 @@
       <c r="D140" s="12" t="n">
         <v>1799</v>
       </c>
-      <c r="E140" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="E140" s="12" t="n"/>
       <c r="F140" s="11" t="n"/>
       <c r="G140" s="12" t="n">
         <v>2</v>
@@ -15497,9 +15457,7 @@
       <c r="J140" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K140" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="K140" s="12" t="n"/>
       <c r="L140" s="12" t="n">
         <v>2</v>
       </c>
@@ -15682,9 +15640,7 @@
       <c r="K142" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L142" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="L142" s="12" t="n"/>
       <c r="M142" s="12" t="n">
         <v>2</v>
       </c>
@@ -16835,9 +16791,7 @@
       <c r="D153" s="14" t="n">
         <v>399</v>
       </c>
-      <c r="E153" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E153" s="14" t="n"/>
       <c r="F153" s="13" t="n"/>
       <c r="G153" s="14" t="n">
         <v>2</v>
@@ -16848,9 +16802,7 @@
       <c r="K153" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="L153" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="L153" s="14" t="n"/>
       <c r="M153" s="14" t="n">
         <v>1</v>
       </c>
@@ -16942,9 +16894,7 @@
       <c r="K154" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L154" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="L154" s="12" t="n"/>
       <c r="M154" s="12" t="n">
         <v>1</v>
       </c>
@@ -18076,9 +18026,7 @@
       <c r="K165" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="L165" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="L165" s="14" t="n"/>
       <c r="M165" s="14" t="n">
         <v>2</v>
       </c>
@@ -18990,9 +18938,7 @@
       <c r="K174" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L174" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="L174" s="12" t="n"/>
       <c r="M174" s="12" t="n">
         <v>1</v>
       </c>
@@ -19527,9 +19473,7 @@
       <c r="D179" s="14" t="n">
         <v>3999</v>
       </c>
-      <c r="E179" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E179" s="14" t="n"/>
       <c r="F179" s="13" t="n"/>
       <c r="G179" s="14" t="n">
         <v>16</v>
@@ -20228,9 +20172,7 @@
       <c r="K185" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="L185" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="L185" s="14" t="n"/>
       <c r="M185" s="14" t="n">
         <v>1</v>
       </c>
@@ -20334,9 +20276,7 @@
       <c r="K186" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L186" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="L186" s="12" t="n"/>
       <c r="M186" s="12" t="n">
         <v>1</v>
       </c>
@@ -20444,9 +20384,7 @@
       <c r="K187" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="L187" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="L187" s="14" t="n"/>
       <c r="M187" s="14" t="n">
         <v>1</v>
       </c>
@@ -20566,9 +20504,7 @@
       <c r="K188" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L188" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="L188" s="12" t="n"/>
       <c r="M188" s="12" t="n">
         <v>1</v>
       </c>
@@ -21014,9 +20950,7 @@
       <c r="K192" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L192" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="L192" s="12" t="n"/>
       <c r="M192" s="12" t="n">
         <v>1</v>
       </c>
@@ -21120,9 +21054,7 @@
       <c r="K193" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="L193" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="L193" s="14" t="n"/>
       <c r="M193" s="14" t="n">
         <v>1</v>
       </c>
@@ -21226,9 +21158,7 @@
       <c r="K194" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L194" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="L194" s="12" t="n"/>
       <c r="M194" s="12" t="n">
         <v>2</v>
       </c>
@@ -21736,7 +21666,7 @@
       </c>
       <c r="L199" s="13" t="n"/>
       <c r="M199" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N199" s="13" t="n"/>
       <c r="O199" s="13" t="n"/>
@@ -21956,7 +21886,7 @@
       </c>
       <c r="L201" s="13" t="n"/>
       <c r="M201" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N201" s="13" t="n"/>
       <c r="O201" s="13" t="n"/>
@@ -22178,7 +22108,7 @@
       </c>
       <c r="L203" s="13" t="n"/>
       <c r="M203" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N203" s="13" t="n"/>
       <c r="O203" s="13" t="n"/>
@@ -22375,9 +22305,7 @@
       <c r="D205" s="14" t="n">
         <v>249</v>
       </c>
-      <c r="E205" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E205" s="14" t="n"/>
       <c r="F205" s="13" t="n"/>
       <c r="G205" s="14" t="n">
         <v>1</v>
@@ -22388,9 +22316,7 @@
       <c r="K205" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="L205" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="L205" s="14" t="n"/>
       <c r="M205" s="14" t="n">
         <v>1</v>
       </c>
@@ -22484,9 +22410,7 @@
       <c r="K206" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L206" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="L206" s="12" t="n"/>
       <c r="M206" s="12" t="n">
         <v>1</v>
       </c>

--- a/data/audio_interfaces.xlsx
+++ b/data/audio_interfaces.xlsx
@@ -740,7 +740,7 @@
       <c r="AA2" s="2" t="n"/>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>○ (96kHz FPGA FX)</t>
+          <t>Yes (96kHz FPGA FX)</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       <c r="AA3" s="3" t="n"/>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>○ (96kHz FPGA FX)</t>
+          <t>Yes (96kHz FPGA FX)</t>
         </is>
       </c>
       <c r="AC3" s="3" t="inlineStr">
@@ -952,7 +952,7 @@
       <c r="AA4" s="2" t="n"/>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>○ (96kHz FPGA FX)</t>
+          <t>Yes (96kHz FPGA FX)</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1056,7 +1056,7 @@
       <c r="AA5" s="3" t="n"/>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>○ (96kHz XCVI FPGA)</t>
+          <t>Yes (96kHz XCVI FPGA)</t>
         </is>
       </c>
       <c r="AC5" s="3" t="inlineStr">
@@ -1160,7 +1160,7 @@
       <c r="AA6" s="2" t="n"/>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>○ (96kHz XCVI FPGA)</t>
+          <t>Yes (96kHz XCVI FPGA)</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       <c r="AA7" s="3" t="n"/>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>○ (96kHz XCVI FPGA)</t>
+          <t>Yes (96kHz XCVI FPGA)</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>○ (Synergy Core FPGA, 37Effects, max 80 simultaneous)</t>
+          <t>Yes (Synergy Core FPGA, 37Effects, max 80 simultaneous)</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
@@ -1626,7 +1626,7 @@
       <c r="AA10" s="2" t="n"/>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>○ (Synergy Core DSP+FPGA, 37Effects)</t>
+          <t>Yes (Synergy Core DSP+FPGA, 37Effects)</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>○ (Synergy Core FPGA, 37Effects, max 160 simultaneous)</t>
+          <t>Yes (Synergy Core FPGA, 37Effects, max 160 simultaneous)</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
@@ -1868,7 +1868,7 @@
       <c r="AA12" s="2" t="n"/>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>○ (Synergy Core FPGA+DSP, 37Effects)</t>
+          <t>Yes (Synergy Core FPGA+DSP, 37Effects)</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1972,7 +1972,7 @@
       <c r="AA13" s="3" t="n"/>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>○ (Synergy Core FPGA+DSP, 37Effects)</t>
+          <t>Yes (Synergy Core FPGA+DSP, 37Effects)</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
@@ -2094,7 +2094,7 @@
       <c r="AA14" s="2" t="n"/>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>○ (Synergy Core FPGA+DSP, 50+Effects)</t>
+          <t>Yes (Synergy Core FPGA+DSP, 50+Effects)</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2218,7 +2218,7 @@
       <c r="AA15" s="3" t="n"/>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>○ (Synergy Core FPGA+DSP)</t>
+          <t>Yes (Synergy Core FPGA+DSP)</t>
         </is>
       </c>
       <c r="AC15" s="3" t="n"/>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>○ (Synergy Core FPGA, 37Effects)</t>
+          <t>Yes (Synergy Core FPGA, 37Effects)</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>○ (Synergy Core FPGA, 37Effects, max 48 simultaneous)</t>
+          <t>Yes (Synergy Core FPGA, 37Effects, max 48 simultaneous)</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>○ (Synergy Core FPGA+DSP, 37Effects)</t>
+          <t>Yes (Synergy Core FPGA+DSP, 37Effects)</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2702,7 +2702,7 @@
       <c r="AA19" s="3" t="n"/>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>○ (Synergy Core DSP+FPGA, 36Effects)</t>
+          <t>Yes (Synergy Core DSP+FPGA, 36Effects)</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       <c r="AA22" s="2" t="n"/>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       <c r="AA23" s="3" t="n"/>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
@@ -3262,7 +3262,7 @@
       <c r="AA24" s="2" t="n"/>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5120,7 +5120,7 @@
       <c r="AA40" s="2" t="n"/>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
@@ -5392,7 +5392,7 @@
       <c r="AA42" s="2" t="n"/>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       <c r="AA43" s="3" t="n"/>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC47" s="3" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="AB57" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC57" s="3" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="AB59" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC59" s="3" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7614,7 +7614,7 @@
       <c r="AA62" s="2" t="n"/>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -8068,7 +8068,7 @@
       <c r="AA66" s="2" t="n"/>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8198,7 +8198,7 @@
       <c r="AA67" s="3" t="n"/>
       <c r="AB67" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC67" s="3" t="inlineStr">
@@ -8334,7 +8334,7 @@
       <c r="AA68" s="2" t="n"/>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="AB75" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC75" s="3" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="AB77" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC77" s="3" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="AB79" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC79" s="3" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10038,7 +10038,7 @@
       <c r="AA83" s="3" t="n"/>
       <c r="AB83" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC83" s="3" t="inlineStr">
@@ -10144,7 +10144,7 @@
       <c r="AA84" s="2" t="n"/>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10262,7 +10262,7 @@
       <c r="AA85" s="3" t="n"/>
       <c r="AB85" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC85" s="3" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10688,7 +10688,7 @@
       </c>
       <c r="AB89" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC89" s="3" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="AB99" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC99" s="3" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
@@ -12238,7 +12238,7 @@
       <c r="AA103" s="3" t="n"/>
       <c r="AB103" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC103" s="3" t="inlineStr">
@@ -12342,7 +12342,7 @@
       <c r="AA104" s="2" t="n"/>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
@@ -12448,7 +12448,7 @@
       <c r="AA105" s="3" t="n"/>
       <c r="AB105" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC105" s="3" t="inlineStr">
@@ -12560,7 +12560,7 @@
       <c r="AA106" s="2" t="n"/>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
@@ -12670,7 +12670,7 @@
       <c r="AA107" s="3" t="n"/>
       <c r="AB107" s="3" t="inlineStr">
         <is>
-          <t>○ (DSP/FPGAハイブリッド、100+プラグイン)</t>
+          <t>Yes (DSP/FPGA Hybrid, 100+ Plugins)</t>
         </is>
       </c>
       <c r="AC107" s="3" t="inlineStr">
@@ -12776,7 +12776,7 @@
       <c r="AA108" s="2" t="n"/>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
@@ -12890,7 +12890,7 @@
       <c r="AA109" s="3" t="n"/>
       <c r="AB109" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC109" s="3" t="n"/>
@@ -13010,7 +13010,7 @@
       </c>
       <c r="AB110" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC110" s="2" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="AB111" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC111" s="3" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="AB112" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC112" s="2" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="AB113" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC113" s="3" t="inlineStr">
@@ -13524,7 +13524,7 @@
       <c r="AA114" s="2" t="n"/>
       <c r="AB114" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC114" s="2" t="inlineStr">
@@ -13646,7 +13646,7 @@
       </c>
       <c r="AB115" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC115" s="3" t="inlineStr">
@@ -13764,7 +13764,7 @@
       </c>
       <c r="AB116" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC116" s="2" t="inlineStr">
@@ -14238,7 +14238,7 @@
       </c>
       <c r="AB120" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC120" s="2" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="AB124" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC124" s="2" t="inlineStr">
@@ -15482,7 +15482,7 @@
       </c>
       <c r="AB131" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC131" s="3" t="inlineStr">
@@ -15832,7 +15832,7 @@
       <c r="AA134" s="2" t="n"/>
       <c r="AB134" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC134" s="2" t="inlineStr">
@@ -15940,7 +15940,7 @@
       <c r="AA135" s="3" t="n"/>
       <c r="AB135" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC135" s="3" t="inlineStr">
@@ -16046,7 +16046,7 @@
       <c r="AA136" s="2" t="n"/>
       <c r="AB136" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC136" s="2" t="inlineStr">
@@ -16944,7 +16944,7 @@
       <c r="AA144" s="2" t="n"/>
       <c r="AB144" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC144" s="2" t="inlineStr">
@@ -17162,7 +17162,7 @@
       </c>
       <c r="AB146" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC146" s="2" t="inlineStr">
@@ -17292,7 +17292,7 @@
       <c r="AA147" s="3" t="n"/>
       <c r="AB147" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC147" s="3" t="inlineStr">
@@ -17414,7 +17414,7 @@
       </c>
       <c r="AB148" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC148" s="2" t="inlineStr">
@@ -17542,7 +17542,7 @@
       <c r="AA149" s="3" t="n"/>
       <c r="AB149" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC149" s="3" t="inlineStr">
@@ -17744,7 +17744,7 @@
       </c>
       <c r="AB151" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC151" s="3" t="inlineStr">
@@ -17856,7 +17856,7 @@
       </c>
       <c r="AB152" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC152" s="2" t="inlineStr">
@@ -17972,7 +17972,7 @@
       </c>
       <c r="AB153" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC153" s="3" t="inlineStr">
@@ -18082,7 +18082,7 @@
       </c>
       <c r="AB154" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC154" s="2" t="inlineStr">
@@ -18184,7 +18184,7 @@
       </c>
       <c r="AB155" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC155" s="3" t="inlineStr">
@@ -18502,7 +18502,7 @@
       <c r="AA158" s="2" t="n"/>
       <c r="AB158" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC158" s="2" t="inlineStr">
@@ -18604,7 +18604,7 @@
       <c r="AA159" s="3" t="n"/>
       <c r="AB159" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC159" s="3" t="n"/>
@@ -18702,7 +18702,7 @@
       <c r="AA160" s="2" t="n"/>
       <c r="AB160" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC160" s="2" t="inlineStr">
@@ -18804,7 +18804,7 @@
       <c r="AA161" s="3" t="n"/>
       <c r="AB161" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC161" s="3" t="inlineStr">
@@ -18906,7 +18906,7 @@
       <c r="AA162" s="2" t="n"/>
       <c r="AB162" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC162" s="2" t="inlineStr">
@@ -19012,7 +19012,7 @@
       <c r="AA163" s="3" t="n"/>
       <c r="AB163" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC163" s="3" t="inlineStr">
@@ -19118,7 +19118,7 @@
       <c r="AA164" s="2" t="n"/>
       <c r="AB164" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC164" s="2" t="inlineStr">
@@ -19238,7 +19238,7 @@
       </c>
       <c r="AB165" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC165" s="3" t="inlineStr">
@@ -19376,7 +19376,7 @@
       <c r="AA166" s="2" t="n"/>
       <c r="AB166" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC166" s="2" t="inlineStr">
@@ -19486,7 +19486,7 @@
       <c r="AA167" s="3" t="n"/>
       <c r="AB167" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC167" s="3" t="inlineStr">
@@ -19608,7 +19608,7 @@
       </c>
       <c r="AB168" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC168" s="2" t="inlineStr">
@@ -19806,7 +19806,7 @@
       </c>
       <c r="AB170" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC170" s="2" t="inlineStr">
@@ -20142,7 +20142,7 @@
       <c r="AA173" s="3" t="n"/>
       <c r="AB173" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC173" s="3" t="inlineStr">
@@ -20344,7 +20344,7 @@
       <c r="AA175" s="3" t="n"/>
       <c r="AB175" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC175" s="3" t="inlineStr">
@@ -20682,7 +20682,7 @@
       <c r="AA178" s="2" t="n"/>
       <c r="AB178" s="2" t="inlineStr">
         <is>
-          <t>○ (UAD)</t>
+          <t>Yes (UAD)</t>
         </is>
       </c>
       <c r="AC178" s="2" t="inlineStr">
@@ -20806,7 +20806,7 @@
       </c>
       <c r="AB179" s="3" t="inlineStr">
         <is>
-          <t>○ (UAD)</t>
+          <t>Yes (UAD)</t>
         </is>
       </c>
       <c r="AC179" s="3" t="inlineStr">
@@ -20926,7 +20926,7 @@
       </c>
       <c r="AB180" s="2" t="inlineStr">
         <is>
-          <t>○ (UAD)</t>
+          <t>Yes (UAD)</t>
         </is>
       </c>
       <c r="AC180" s="2" t="inlineStr">
@@ -21036,7 +21036,7 @@
       <c r="AA181" s="3" t="n"/>
       <c r="AB181" s="3" t="inlineStr">
         <is>
-          <t>○ (UAD)</t>
+          <t>Yes (UAD)</t>
         </is>
       </c>
       <c r="AC181" s="3" t="inlineStr">
@@ -21142,7 +21142,7 @@
       <c r="AA182" s="2" t="n"/>
       <c r="AB182" s="2" t="inlineStr">
         <is>
-          <t>○ (UAD)</t>
+          <t>Yes (UAD)</t>
         </is>
       </c>
       <c r="AC182" s="2" t="inlineStr">
@@ -21268,7 +21268,7 @@
       <c r="AA183" s="3" t="n"/>
       <c r="AB183" s="3" t="inlineStr">
         <is>
-          <t>○ (UAD)</t>
+          <t>Yes (UAD)</t>
         </is>
       </c>
       <c r="AC183" s="3" t="inlineStr">
@@ -21398,7 +21398,7 @@
       <c r="AA184" s="2" t="n"/>
       <c r="AB184" s="2" t="inlineStr">
         <is>
-          <t>○ (UAD)</t>
+          <t>Yes (UAD)</t>
         </is>
       </c>
       <c r="AC184" s="2" t="inlineStr">
@@ -21528,7 +21528,7 @@
       <c r="AA185" s="3" t="n"/>
       <c r="AB185" s="3" t="inlineStr">
         <is>
-          <t>○ (UAD)</t>
+          <t>Yes (UAD)</t>
         </is>
       </c>
       <c r="AC185" s="3" t="inlineStr">
@@ -21656,7 +21656,7 @@
       <c r="AA186" s="2" t="n"/>
       <c r="AB186" s="2" t="inlineStr">
         <is>
-          <t>○ (UAD)</t>
+          <t>Yes (UAD)</t>
         </is>
       </c>
       <c r="AC186" s="2" t="inlineStr">
@@ -21772,7 +21772,7 @@
       </c>
       <c r="AB187" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC187" s="3" t="inlineStr">
@@ -21886,7 +21886,7 @@
       </c>
       <c r="AB188" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC188" s="2" t="inlineStr">
@@ -22000,7 +22000,7 @@
       </c>
       <c r="AB189" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC189" s="3" t="inlineStr">
@@ -22126,7 +22126,7 @@
       </c>
       <c r="AB190" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC190" s="2" t="inlineStr">
@@ -22354,7 +22354,7 @@
       </c>
       <c r="AB192" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC192" s="2" t="inlineStr">
@@ -22476,7 +22476,7 @@
       <c r="AA193" s="3" t="n"/>
       <c r="AB193" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC193" s="3" t="inlineStr">
@@ -22596,7 +22596,7 @@
       </c>
       <c r="AB194" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC194" s="2" t="inlineStr">
@@ -22706,7 +22706,7 @@
       </c>
       <c r="AB195" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC195" s="3" t="inlineStr">
@@ -22820,7 +22820,7 @@
       </c>
       <c r="AB196" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC196" s="2" t="inlineStr">
@@ -22924,7 +22924,7 @@
       <c r="AA197" s="3" t="n"/>
       <c r="AB197" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC197" s="3" t="inlineStr">
@@ -23014,7 +23014,7 @@
       <c r="AA198" s="2" t="n"/>
       <c r="AB198" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC198" s="2" t="n"/>
@@ -23348,7 +23348,7 @@
       <c r="AA201" s="3" t="n"/>
       <c r="AB201" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC201" s="3" t="n"/>
@@ -23466,7 +23466,7 @@
       <c r="AA202" s="2" t="n"/>
       <c r="AB202" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC202" s="2" t="n"/>
@@ -23580,7 +23580,7 @@
       <c r="AA203" s="3" t="n"/>
       <c r="AB203" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC203" s="3" t="n"/>
@@ -23700,7 +23700,7 @@
       <c r="AA204" s="2" t="n"/>
       <c r="AB204" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC204" s="2" t="n"/>
@@ -23814,7 +23814,7 @@
       <c r="AA205" s="3" t="n"/>
       <c r="AB205" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC205" s="3" t="n"/>
@@ -23938,7 +23938,7 @@
       </c>
       <c r="AB206" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC206" s="2" t="inlineStr">
@@ -24038,7 +24038,7 @@
       </c>
       <c r="AB207" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC207" s="3" t="inlineStr">
@@ -24346,7 +24346,7 @@
       </c>
       <c r="AB210" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC210" s="2" t="n"/>
@@ -24446,7 +24446,7 @@
       <c r="AA211" s="3" t="n"/>
       <c r="AB211" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC211" s="3" t="inlineStr">
@@ -24552,7 +24552,7 @@
       </c>
       <c r="AB212" s="2" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC212" s="2" t="inlineStr">
@@ -24658,7 +24658,7 @@
       </c>
       <c r="AB213" s="3" t="inlineStr">
         <is>
-          <t>○ (Built-in)</t>
+          <t>Yes (Built-in)</t>
         </is>
       </c>
       <c r="AC213" s="3" t="n"/>

--- a/data/audio_interfaces.xlsx
+++ b/data/audio_interfaces.xlsx
@@ -2934,7 +2934,11 @@
       </c>
       <c r="Z21" s="3" t="n"/>
       <c r="AA21" s="3" t="n"/>
-      <c r="AB21" s="3" t="n"/>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>Yes (Built-in)</t>
+        </is>
+      </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
           <t>Yes</t>

--- a/data/audio_interfaces.xlsx
+++ b/data/audio_interfaces.xlsx
@@ -13881,16 +13881,20 @@
         </is>
       </c>
       <c r="AD117" s="3" t="n"/>
-      <c r="AE117" s="3" t="n"/>
-      <c r="AF117" s="3" t="n"/>
-      <c r="AG117" s="3" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+      <c r="AE117" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="AF117" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="AG117" s="3" t="n"/>
       <c r="AH117" s="3" t="n"/>
       <c r="AI117" s="3" t="n"/>
-      <c r="AJ117" s="3" t="n"/>
+      <c r="AJ117" s="3" t="inlineStr">
+        <is>
+          <t>-110.0dB (0.00032%)</t>
+        </is>
+      </c>
       <c r="AK117" s="3" t="n"/>
       <c r="AL117" s="3" t="inlineStr">
         <is>
@@ -21814,7 +21818,7 @@
       </c>
       <c r="AP187" s="3" t="inlineStr">
         <is>
-          <t>https://www.uaudio.com/audio-interfaces/volt.html</t>
+          <t>https://www.uaudio.com/products/volt-1-usb-audio-interface</t>
         </is>
       </c>
     </row>
@@ -21928,7 +21932,7 @@
       </c>
       <c r="AP188" s="2" t="inlineStr">
         <is>
-          <t>https://www.uaudio.com/audio-interfaces/volt-176.html</t>
+          <t>https://www.uaudio.com/products/volt-176-usb-audio-interface</t>
         </is>
       </c>
     </row>
@@ -22054,7 +22058,7 @@
       </c>
       <c r="AP189" s="3" t="inlineStr">
         <is>
-          <t>https://www.uaudio.com/audio-interfaces/volt-2.html</t>
+          <t>https://www.uaudio.com/products/volt-2-usb-audio-interface</t>
         </is>
       </c>
     </row>
@@ -22168,7 +22172,7 @@
       </c>
       <c r="AP190" s="2" t="inlineStr">
         <is>
-          <t>https://www.uaudio.com/audio-interfaces/volt-276.html</t>
+          <t>https://www.uaudio.com/products/volt-276-usb-audio-interface</t>
         </is>
       </c>
     </row>
@@ -22278,7 +22282,7 @@
       </c>
       <c r="AP191" s="3" t="inlineStr">
         <is>
-          <t>https://www.uaudio.com/audio-interfaces/volt-4.html</t>
+          <t>https://www.uaudio.com/products/volt-4-usb-audio-interface</t>
         </is>
       </c>
     </row>
@@ -22396,7 +22400,7 @@
       </c>
       <c r="AP192" s="2" t="inlineStr">
         <is>
-          <t>https://www.uaudio.com/audio-interfaces/volt-476.html</t>
+          <t>https://www.uaudio.com/products/volt-476-usb-audio-interface</t>
         </is>
       </c>
     </row>
@@ -22524,7 +22528,7 @@
       </c>
       <c r="AP193" s="3" t="inlineStr">
         <is>
-          <t>https://www.uaudio.com/products/volt-876</t>
+          <t>https://www.uaudio.com/products/volt-876-usb-audio-interface</t>
         </is>
       </c>
     </row>

--- a/data/audio_interfaces.xlsx
+++ b/data/audio_interfaces.xlsx
@@ -4713,12 +4713,8 @@
       <c r="P37" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q37" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="R37" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q37" s="3" t="n"/>
+      <c r="R37" s="3" t="n"/>
       <c r="S37" s="3" t="n"/>
       <c r="T37" s="3" t="n"/>
       <c r="U37" s="3" t="n"/>
@@ -4756,25 +4752,25 @@
         </is>
       </c>
       <c r="AE37" s="3" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AF37" s="3" t="n">
-        <v>126</v>
+        <v>125.5</v>
       </c>
       <c r="AG37" s="3" t="n"/>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>-94.0dB (0.00200%)</t>
+          <t>-95.4dB (0.00170%)</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
         <is>
-          <t>-106.0dB (0.00050%)</t>
+          <t>-104.4dB (0.00063%)</t>
         </is>
       </c>
       <c r="AJ37" s="3" t="n"/>
       <c r="AK37" s="3" t="n">
-        <v>-128</v>
+        <v>-129</v>
       </c>
       <c r="AL37" s="3" t="n"/>
       <c r="AM37" s="3" t="inlineStr">

--- a/data/audio_interfaces.xlsx
+++ b/data/audio_interfaces.xlsx
@@ -4888,18 +4888,26 @@
         <v>58</v>
       </c>
       <c r="AE38" s="2" t="n">
-        <v>126</v>
-      </c>
-      <c r="AF38" s="2" t="n"/>
+        <v>122</v>
+      </c>
+      <c r="AF38" s="2" t="n">
+        <v>126.5</v>
+      </c>
       <c r="AG38" s="2" t="n"/>
-      <c r="AH38" s="2" t="n"/>
-      <c r="AI38" s="2" t="n"/>
-      <c r="AJ38" s="2" t="inlineStr">
-        <is>
-          <t>-112.0dB (0.00025%)</t>
-        </is>
-      </c>
-      <c r="AK38" s="2" t="n"/>
+      <c r="AH38" s="2" t="inlineStr">
+        <is>
+          <t>-96.5dB (0.00150%)</t>
+        </is>
+      </c>
+      <c r="AI38" s="2" t="inlineStr">
+        <is>
+          <t>-110.5dB (0.00030%)</t>
+        </is>
+      </c>
+      <c r="AJ38" s="2" t="n"/>
+      <c r="AK38" s="2" t="n">
+        <v>-130</v>
+      </c>
       <c r="AL38" s="2" t="n"/>
       <c r="AM38" s="2" t="inlineStr">
         <is>
@@ -5011,7 +5019,7 @@
       </c>
       <c r="AI39" s="3" t="inlineStr">
         <is>
-          <t>-100.9dB (0.00090%)</t>
+          <t>-104.4dB (0.00060%)</t>
         </is>
       </c>
       <c r="AJ39" s="3" t="n"/>
@@ -5133,19 +5141,23 @@
           <t>60</t>
         </is>
       </c>
-      <c r="AE40" s="2" t="n"/>
-      <c r="AF40" s="2" t="n"/>
-      <c r="AG40" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
+      <c r="AE40" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF40" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="AG40" s="2" t="n"/>
       <c r="AH40" s="2" t="inlineStr">
         <is>
           <t>-90.5dB (0.00299%)</t>
         </is>
       </c>
-      <c r="AI40" s="2" t="n"/>
+      <c r="AI40" s="2" t="inlineStr">
+        <is>
+          <t>-104.0dB (0.00060%)</t>
+        </is>
+      </c>
       <c r="AJ40" s="2" t="n"/>
       <c r="AK40" s="2" t="n">
         <v>-126</v>

--- a/data/audio_interfaces.xlsx
+++ b/data/audio_interfaces.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3755" uniqueCount="1320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3754" uniqueCount="1319">
   <si>
     <t>Brand</t>
   </si>
@@ -1020,9 +1020,6 @@
   </si>
   <si>
     <t>AT-UMX3</t>
-  </si>
-  <si>
-    <t>159</t>
   </si>
   <si>
     <t>192</t>
@@ -4487,7 +4484,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>45</v>
       </c>
@@ -4558,7 +4555,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -4632,7 +4629,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -4706,7 +4703,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -4780,7 +4777,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>45</v>
       </c>
@@ -4857,7 +4854,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>45</v>
       </c>
@@ -4931,7 +4928,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>45</v>
       </c>
@@ -5005,7 +5002,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -5076,7 +5073,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>45</v>
       </c>
@@ -5147,7 +5144,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -5221,7 +5218,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>45</v>
       </c>
@@ -5292,7 +5289,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -5363,7 +5360,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>45</v>
       </c>
@@ -5437,7 +5434,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>45</v>
       </c>
@@ -5502,7 +5499,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>116</v>
       </c>
@@ -5585,7 +5582,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="17" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>124</v>
       </c>
@@ -5671,7 +5668,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="18" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>124</v>
       </c>
@@ -5742,7 +5739,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="19" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>124</v>
       </c>
@@ -5813,7 +5810,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="20" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>124</v>
       </c>
@@ -5911,7 +5908,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="21" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>124</v>
       </c>
@@ -5970,7 +5967,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="22" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>124</v>
       </c>
@@ -6062,7 +6059,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="23" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>124</v>
       </c>
@@ -6545,7 +6542,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="29" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>174</v>
       </c>
@@ -6598,7 +6595,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="30" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>174</v>
       </c>
@@ -6666,7 +6663,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="31" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>174</v>
       </c>
@@ -6734,7 +6731,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="32" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>174</v>
       </c>
@@ -6808,7 +6805,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="33" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>174</v>
       </c>
@@ -6882,7 +6879,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="34" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>229</v>
       </c>
@@ -6989,7 +6986,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="35" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>229</v>
       </c>
@@ -7449,7 +7446,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="40" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>229</v>
       </c>
@@ -7526,7 +7523,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="41" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>229</v>
       </c>
@@ -7612,7 +7609,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="42" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>279</v>
       </c>
@@ -7870,7 +7867,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="45" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>279</v>
       </c>
@@ -8342,7 +8339,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="50" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>279</v>
       </c>
@@ -8434,7 +8431,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="51" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>332</v>
       </c>
@@ -8444,8 +8441,8 @@
       <c r="C51" t="s">
         <v>271</v>
       </c>
-      <c r="D51" t="s">
-        <v>334</v>
+      <c r="D51">
+        <v>159</v>
       </c>
       <c r="E51" t="s">
         <v>137</v>
@@ -8466,7 +8463,7 @@
         <v>48</v>
       </c>
       <c r="W51" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="X51" t="s">
         <v>76</v>
@@ -8481,24 +8478,24 @@
         <v>48</v>
       </c>
       <c r="AD51" t="s">
+        <v>335</v>
+      </c>
+      <c r="AM51" t="s">
         <v>336</v>
       </c>
-      <c r="AM51" t="s">
+      <c r="AO51" t="s">
         <v>337</v>
       </c>
-      <c r="AO51" t="s">
+      <c r="AP51" t="s">
         <v>338</v>
       </c>
-      <c r="AP51" t="s">
+    </row>
+    <row r="52" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="52" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="B52" t="s">
         <v>340</v>
-      </c>
-      <c r="B52" t="s">
-        <v>341</v>
       </c>
       <c r="C52" t="s">
         <v>154</v>
@@ -8597,21 +8594,21 @@
         <v>54</v>
       </c>
       <c r="AN52" t="s">
+        <v>341</v>
+      </c>
+      <c r="AO52" t="s">
         <v>342</v>
       </c>
-      <c r="AO52" t="s">
+      <c r="AP52" t="s">
         <v>343</v>
       </c>
-      <c r="AP52" t="s">
+    </row>
+    <row r="53" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>339</v>
+      </c>
+      <c r="B53" t="s">
         <v>344</v>
-      </c>
-    </row>
-    <row r="53" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>340</v>
-      </c>
-      <c r="B53" t="s">
-        <v>345</v>
       </c>
       <c r="C53" t="s">
         <v>131</v>
@@ -8662,7 +8659,7 @@
         <v>32</v>
       </c>
       <c r="Y53" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AB53" t="s">
         <v>70</v>
@@ -8677,10 +8674,10 @@
         <v>120</v>
       </c>
       <c r="AH53" t="s">
+        <v>346</v>
+      </c>
+      <c r="AI53" t="s">
         <v>347</v>
-      </c>
-      <c r="AI53" t="s">
-        <v>348</v>
       </c>
       <c r="AK53">
         <v>-129</v>
@@ -8689,21 +8686,21 @@
         <v>209</v>
       </c>
       <c r="AN53" t="s">
+        <v>348</v>
+      </c>
+      <c r="AO53" t="s">
         <v>349</v>
       </c>
-      <c r="AO53" t="s">
+      <c r="AP53" t="s">
         <v>350</v>
       </c>
-      <c r="AP53" t="s">
+    </row>
+    <row r="54" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>339</v>
+      </c>
+      <c r="B54" t="s">
         <v>351</v>
-      </c>
-    </row>
-    <row r="54" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>340</v>
-      </c>
-      <c r="B54" t="s">
-        <v>352</v>
       </c>
       <c r="C54" t="s">
         <v>131</v>
@@ -8748,7 +8745,7 @@
         <v>32</v>
       </c>
       <c r="Y54" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AE54">
         <v>126</v>
@@ -8757,10 +8754,10 @@
         <v>120</v>
       </c>
       <c r="AH54" t="s">
+        <v>346</v>
+      </c>
+      <c r="AI54" t="s">
         <v>347</v>
-      </c>
-      <c r="AI54" t="s">
-        <v>348</v>
       </c>
       <c r="AK54">
         <v>-129</v>
@@ -8769,21 +8766,21 @@
         <v>209</v>
       </c>
       <c r="AN54" t="s">
+        <v>352</v>
+      </c>
+      <c r="AO54" t="s">
         <v>353</v>
       </c>
-      <c r="AO54" t="s">
+      <c r="AP54" t="s">
         <v>354</v>
       </c>
-      <c r="AP54" t="s">
+    </row>
+    <row r="55" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>339</v>
+      </c>
+      <c r="B55" t="s">
         <v>355</v>
-      </c>
-    </row>
-    <row r="55" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>340</v>
-      </c>
-      <c r="B55" t="s">
-        <v>356</v>
       </c>
       <c r="C55" t="s">
         <v>131</v>
@@ -8801,13 +8798,13 @@
         <v>24</v>
       </c>
       <c r="Y55" t="s">
+        <v>356</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD55" t="s">
         <v>357</v>
-      </c>
-      <c r="AC55" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD55" t="s">
-        <v>358</v>
       </c>
       <c r="AE55">
         <v>126</v>
@@ -8816,7 +8813,7 @@
         <v>128</v>
       </c>
       <c r="AH55" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AI55" t="s">
         <v>184</v>
@@ -8828,18 +8825,18 @@
         <v>54</v>
       </c>
       <c r="AO55" t="s">
+        <v>359</v>
+      </c>
+      <c r="AP55" t="s">
         <v>360</v>
       </c>
-      <c r="AP55" t="s">
+    </row>
+    <row r="56" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>339</v>
+      </c>
+      <c r="B56" t="s">
         <v>361</v>
-      </c>
-    </row>
-    <row r="56" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>340</v>
-      </c>
-      <c r="B56" t="s">
-        <v>362</v>
       </c>
       <c r="C56" t="s">
         <v>131</v>
@@ -8884,10 +8881,10 @@
         <v>24</v>
       </c>
       <c r="Y56" t="s">
+        <v>362</v>
+      </c>
+      <c r="AB56" t="s">
         <v>363</v>
-      </c>
-      <c r="AB56" t="s">
-        <v>364</v>
       </c>
       <c r="AC56" t="s">
         <v>48</v>
@@ -8902,7 +8899,7 @@
         <v>128</v>
       </c>
       <c r="AH56" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AK56">
         <v>-133</v>
@@ -8911,18 +8908,18 @@
         <v>54</v>
       </c>
       <c r="AO56" t="s">
+        <v>364</v>
+      </c>
+      <c r="AP56" t="s">
         <v>365</v>
       </c>
-      <c r="AP56" t="s">
+    </row>
+    <row r="57" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="57" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="B57" t="s">
         <v>367</v>
-      </c>
-      <c r="B57" t="s">
-        <v>368</v>
       </c>
       <c r="C57" t="s">
         <v>47</v>
@@ -8970,10 +8967,10 @@
         <v>48</v>
       </c>
       <c r="AD57" t="s">
+        <v>368</v>
+      </c>
+      <c r="AG57" t="s">
         <v>369</v>
-      </c>
-      <c r="AG57" t="s">
-        <v>370</v>
       </c>
       <c r="AH57" t="s">
         <v>58</v>
@@ -8982,21 +8979,21 @@
         <v>225</v>
       </c>
       <c r="AM57" t="s">
+        <v>370</v>
+      </c>
+      <c r="AO57" t="s">
         <v>371</v>
       </c>
-      <c r="AO57" t="s">
+      <c r="AP57" t="s">
         <v>372</v>
       </c>
-      <c r="AP57" t="s">
+    </row>
+    <row r="58" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>366</v>
+      </c>
+      <c r="B58" t="s">
         <v>373</v>
-      </c>
-    </row>
-    <row r="58" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>367</v>
-      </c>
-      <c r="B58" t="s">
-        <v>374</v>
       </c>
       <c r="C58" t="s">
         <v>192</v>
@@ -9029,7 +9026,7 @@
         <v>24</v>
       </c>
       <c r="Y58" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AC58" t="s">
         <v>48</v>
@@ -9041,18 +9038,18 @@
         <v>54</v>
       </c>
       <c r="AO58" t="s">
+        <v>375</v>
+      </c>
+      <c r="AP58" t="s">
         <v>376</v>
-      </c>
-      <c r="AP58" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="59" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B59" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C59" t="s">
         <v>166</v>
@@ -9118,27 +9115,27 @@
         <v>48</v>
       </c>
       <c r="AG59" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AM59" t="s">
         <v>54</v>
       </c>
       <c r="AO59" t="s">
+        <v>379</v>
+      </c>
+      <c r="AP59" t="s">
         <v>380</v>
       </c>
-      <c r="AP59" t="s">
+      <c r="AS59" t="s">
         <v>381</v>
-      </c>
-      <c r="AS59" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="60" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B60" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C60" t="s">
         <v>192</v>
@@ -9180,21 +9177,21 @@
         <v>54</v>
       </c>
       <c r="AO60" t="s">
+        <v>383</v>
+      </c>
+      <c r="AP60" t="s">
         <v>384</v>
       </c>
-      <c r="AP60" t="s">
+      <c r="AS60" t="s">
         <v>385</v>
-      </c>
-      <c r="AS60" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="61" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B61" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C61" t="s">
         <v>192</v>
@@ -9242,21 +9239,21 @@
         <v>54</v>
       </c>
       <c r="AO61" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AP61" t="s">
+        <v>387</v>
+      </c>
+      <c r="AS61" t="s">
         <v>388</v>
-      </c>
-      <c r="AS61" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="62" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B62" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C62" t="s">
         <v>192</v>
@@ -9298,21 +9295,21 @@
         <v>54</v>
       </c>
       <c r="AO62" t="s">
+        <v>390</v>
+      </c>
+      <c r="AP62" t="s">
         <v>391</v>
       </c>
-      <c r="AP62" t="s">
+      <c r="AS62" t="s">
         <v>392</v>
-      </c>
-      <c r="AS62" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="63" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B63" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C63" t="s">
         <v>192</v>
@@ -9357,21 +9354,21 @@
         <v>54</v>
       </c>
       <c r="AO63" t="s">
+        <v>394</v>
+      </c>
+      <c r="AP63" t="s">
         <v>395</v>
       </c>
-      <c r="AP63" t="s">
+      <c r="AS63" t="s">
         <v>396</v>
       </c>
-      <c r="AS63" t="s">
+    </row>
+    <row r="64" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>366</v>
+      </c>
+      <c r="B64" t="s">
         <v>397</v>
-      </c>
-    </row>
-    <row r="64" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>367</v>
-      </c>
-      <c r="B64" t="s">
-        <v>398</v>
       </c>
       <c r="C64" t="s">
         <v>47</v>
@@ -9413,7 +9410,7 @@
         <v>48</v>
       </c>
       <c r="AD64" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AH64" t="s">
         <v>107</v>
@@ -9425,18 +9422,18 @@
         <v>54</v>
       </c>
       <c r="AO64" t="s">
+        <v>399</v>
+      </c>
+      <c r="AP64" t="s">
         <v>400</v>
       </c>
-      <c r="AP64" t="s">
+    </row>
+    <row r="65" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>366</v>
+      </c>
+      <c r="B65" t="s">
         <v>401</v>
-      </c>
-    </row>
-    <row r="65" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>367</v>
-      </c>
-      <c r="B65" t="s">
-        <v>402</v>
       </c>
       <c r="C65" t="s">
         <v>47</v>
@@ -9475,7 +9472,7 @@
         <v>48</v>
       </c>
       <c r="AD65" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AH65" t="s">
         <v>107</v>
@@ -9487,18 +9484,18 @@
         <v>54</v>
       </c>
       <c r="AO65" t="s">
+        <v>402</v>
+      </c>
+      <c r="AP65" t="s">
         <v>403</v>
       </c>
-      <c r="AP65" t="s">
+    </row>
+    <row r="66" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>366</v>
+      </c>
+      <c r="B66" t="s">
         <v>404</v>
-      </c>
-    </row>
-    <row r="66" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>367</v>
-      </c>
-      <c r="B66" t="s">
-        <v>405</v>
       </c>
       <c r="C66" t="s">
         <v>271</v>
@@ -9534,30 +9531,30 @@
         <v>48</v>
       </c>
       <c r="AD66" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AH66" t="s">
+        <v>405</v>
+      </c>
+      <c r="AK66" t="s">
         <v>406</v>
-      </c>
-      <c r="AK66" t="s">
-        <v>407</v>
       </c>
       <c r="AM66" t="s">
         <v>54</v>
       </c>
       <c r="AO66" t="s">
+        <v>407</v>
+      </c>
+      <c r="AP66" t="s">
         <v>408</v>
       </c>
-      <c r="AP66" t="s">
+    </row>
+    <row r="67" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>366</v>
+      </c>
+      <c r="B67" t="s">
         <v>409</v>
-      </c>
-    </row>
-    <row r="67" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>367</v>
-      </c>
-      <c r="B67" t="s">
-        <v>410</v>
       </c>
       <c r="C67" t="s">
         <v>271</v>
@@ -9575,7 +9572,7 @@
         <v>2</v>
       </c>
       <c r="O67" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="P67">
         <v>1</v>
@@ -9596,33 +9593,33 @@
         <v>48</v>
       </c>
       <c r="AD67" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AH67" t="s">
+        <v>405</v>
+      </c>
+      <c r="AK67" t="s">
         <v>406</v>
-      </c>
-      <c r="AK67" t="s">
-        <v>407</v>
       </c>
       <c r="AM67" t="s">
         <v>54</v>
       </c>
       <c r="AO67" t="s">
+        <v>411</v>
+      </c>
+      <c r="AP67" t="s">
         <v>412</v>
-      </c>
-      <c r="AP67" t="s">
-        <v>413</v>
       </c>
       <c r="AR67" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="68" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>413</v>
+      </c>
+      <c r="B68" t="s">
         <v>414</v>
-      </c>
-      <c r="B68" t="s">
-        <v>415</v>
       </c>
       <c r="C68" t="s">
         <v>154</v>
@@ -9637,7 +9634,7 @@
         <v>4</v>
       </c>
       <c r="G68" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H68">
         <v>4</v>
@@ -9694,30 +9691,30 @@
         <v>109</v>
       </c>
       <c r="AH68" t="s">
+        <v>416</v>
+      </c>
+      <c r="AI68" t="s">
         <v>417</v>
-      </c>
-      <c r="AI68" t="s">
-        <v>418</v>
       </c>
       <c r="AM68" t="s">
         <v>54</v>
       </c>
       <c r="AN68" t="s">
+        <v>418</v>
+      </c>
+      <c r="AO68" t="s">
         <v>419</v>
       </c>
-      <c r="AO68" t="s">
+      <c r="AP68" t="s">
         <v>420</v>
-      </c>
-      <c r="AP68" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="69" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B69" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C69" t="s">
         <v>166</v>
@@ -9786,24 +9783,24 @@
         <v>54</v>
       </c>
       <c r="AN69" t="s">
+        <v>422</v>
+      </c>
+      <c r="AO69" t="s">
         <v>423</v>
       </c>
-      <c r="AO69" t="s">
+      <c r="AP69" t="s">
         <v>424</v>
       </c>
-      <c r="AP69" t="s">
+      <c r="AS69" t="s">
         <v>425</v>
-      </c>
-      <c r="AS69" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="70" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B70" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C70" t="s">
         <v>166</v>
@@ -9851,7 +9848,7 @@
         <v>48</v>
       </c>
       <c r="AD70" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AE70">
         <v>112</v>
@@ -9860,33 +9857,33 @@
         <v>106</v>
       </c>
       <c r="AH70" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AI70" t="s">
         <v>107</v>
       </c>
       <c r="AM70" t="s">
+        <v>429</v>
+      </c>
+      <c r="AN70" t="s">
         <v>430</v>
       </c>
-      <c r="AN70" t="s">
+      <c r="AO70" t="s">
         <v>431</v>
       </c>
-      <c r="AO70" t="s">
+      <c r="AP70" t="s">
         <v>432</v>
       </c>
-      <c r="AP70" t="s">
+      <c r="AS70" t="s">
         <v>433</v>
       </c>
-      <c r="AS70" t="s">
+    </row>
+    <row r="71" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="71" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="B71" t="s">
         <v>435</v>
-      </c>
-      <c r="B71" t="s">
-        <v>436</v>
       </c>
       <c r="C71" t="s">
         <v>271</v>
@@ -9934,24 +9931,24 @@
         <v>48</v>
       </c>
       <c r="AD71" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AM71" t="s">
         <v>177</v>
       </c>
       <c r="AO71" t="s">
+        <v>437</v>
+      </c>
+      <c r="AP71" t="s">
         <v>438</v>
       </c>
-      <c r="AP71" t="s">
+    </row>
+    <row r="72" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>434</v>
+      </c>
+      <c r="B72" t="s">
         <v>439</v>
-      </c>
-    </row>
-    <row r="72" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>435</v>
-      </c>
-      <c r="B72" t="s">
-        <v>440</v>
       </c>
       <c r="C72" t="s">
         <v>271</v>
@@ -9999,24 +9996,24 @@
         <v>48</v>
       </c>
       <c r="AD72" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AM72" t="s">
         <v>54</v>
       </c>
       <c r="AO72" t="s">
+        <v>440</v>
+      </c>
+      <c r="AP72" t="s">
         <v>441</v>
-      </c>
-      <c r="AP72" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="73" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>442</v>
+      </c>
+      <c r="B73" t="s">
         <v>443</v>
-      </c>
-      <c r="B73" t="s">
-        <v>444</v>
       </c>
       <c r="C73" t="s">
         <v>118</v>
@@ -10064,7 +10061,7 @@
         <v>167</v>
       </c>
       <c r="AC73" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AE73">
         <v>121</v>
@@ -10085,21 +10082,21 @@
         <v>54</v>
       </c>
       <c r="AO73" t="s">
+        <v>445</v>
+      </c>
+      <c r="AP73" t="s">
         <v>446</v>
       </c>
-      <c r="AP73" t="s">
+      <c r="AS73" t="s">
         <v>447</v>
       </c>
-      <c r="AS73" t="s">
+    </row>
+    <row r="74" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="74" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="B74" t="s">
         <v>449</v>
-      </c>
-      <c r="B74" t="s">
-        <v>450</v>
       </c>
       <c r="C74" t="s">
         <v>271</v>
@@ -10135,7 +10132,7 @@
         <v>48</v>
       </c>
       <c r="AD74" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AE74">
         <v>135</v>
@@ -10147,21 +10144,21 @@
         <v>54</v>
       </c>
       <c r="AN74" t="s">
+        <v>451</v>
+      </c>
+      <c r="AO74" t="s">
         <v>452</v>
       </c>
-      <c r="AO74" t="s">
+      <c r="AP74" t="s">
         <v>453</v>
       </c>
-      <c r="AP74" t="s">
+    </row>
+    <row r="75" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>448</v>
+      </c>
+      <c r="B75" t="s">
         <v>454</v>
-      </c>
-    </row>
-    <row r="75" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>449</v>
-      </c>
-      <c r="B75" t="s">
-        <v>455</v>
       </c>
       <c r="C75" t="s">
         <v>271</v>
@@ -10215,21 +10212,21 @@
         <v>54</v>
       </c>
       <c r="AN75" t="s">
+        <v>455</v>
+      </c>
+      <c r="AO75" t="s">
         <v>456</v>
       </c>
-      <c r="AO75" t="s">
+      <c r="AP75" t="s">
         <v>457</v>
       </c>
-      <c r="AP75" t="s">
+    </row>
+    <row r="76" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="76" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="B76" t="s">
         <v>459</v>
-      </c>
-      <c r="B76" t="s">
-        <v>460</v>
       </c>
       <c r="C76" t="s">
         <v>131</v>
@@ -10310,27 +10307,27 @@
         <v>77</v>
       </c>
       <c r="AK76" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AM76" t="s">
         <v>54</v>
       </c>
       <c r="AN76" t="s">
+        <v>461</v>
+      </c>
+      <c r="AO76" t="s">
         <v>462</v>
       </c>
-      <c r="AO76" t="s">
+      <c r="AP76" t="s">
         <v>463</v>
       </c>
-      <c r="AP76" t="s">
+    </row>
+    <row r="77" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>458</v>
+      </c>
+      <c r="B77" t="s">
         <v>464</v>
-      </c>
-    </row>
-    <row r="77" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>459</v>
-      </c>
-      <c r="B77" t="s">
-        <v>465</v>
       </c>
       <c r="C77" t="s">
         <v>118</v>
@@ -10417,21 +10414,21 @@
         <v>54</v>
       </c>
       <c r="AN77" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AO77" t="s">
+        <v>465</v>
+      </c>
+      <c r="AP77" t="s">
         <v>466</v>
       </c>
-      <c r="AP77" t="s">
+    </row>
+    <row r="78" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>458</v>
+      </c>
+      <c r="B78" t="s">
         <v>467</v>
-      </c>
-    </row>
-    <row r="78" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>459</v>
-      </c>
-      <c r="B78" t="s">
-        <v>468</v>
       </c>
       <c r="C78" t="s">
         <v>166</v>
@@ -10485,7 +10482,7 @@
         <v>75</v>
       </c>
       <c r="AG78" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AI78" t="s">
         <v>77</v>
@@ -10494,27 +10491,27 @@
         <v>77</v>
       </c>
       <c r="AL78" t="s">
+        <v>469</v>
+      </c>
+      <c r="AM78" t="s">
         <v>470</v>
       </c>
-      <c r="AM78" t="s">
+      <c r="AN78" t="s">
         <v>471</v>
       </c>
-      <c r="AN78" t="s">
+      <c r="AO78" t="s">
         <v>472</v>
       </c>
-      <c r="AO78" t="s">
+      <c r="AP78" t="s">
         <v>473</v>
       </c>
-      <c r="AP78" t="s">
+    </row>
+    <row r="79" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>458</v>
+      </c>
+      <c r="B79" t="s">
         <v>474</v>
-      </c>
-    </row>
-    <row r="79" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>459</v>
-      </c>
-      <c r="B79" t="s">
-        <v>475</v>
       </c>
       <c r="C79" t="s">
         <v>192</v>
@@ -10580,21 +10577,21 @@
         <v>54</v>
       </c>
       <c r="AN79" t="s">
+        <v>475</v>
+      </c>
+      <c r="AO79" t="s">
         <v>476</v>
       </c>
-      <c r="AO79" t="s">
+      <c r="AP79" t="s">
         <v>477</v>
       </c>
-      <c r="AP79" t="s">
+    </row>
+    <row r="80" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>458</v>
+      </c>
+      <c r="B80" t="s">
         <v>478</v>
-      </c>
-    </row>
-    <row r="80" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>459</v>
-      </c>
-      <c r="B80" t="s">
-        <v>479</v>
       </c>
       <c r="C80" t="s">
         <v>192</v>
@@ -10651,27 +10648,27 @@
         <v>77</v>
       </c>
       <c r="AL80" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AM80" t="s">
         <v>54</v>
       </c>
       <c r="AN80" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AO80" t="s">
+        <v>480</v>
+      </c>
+      <c r="AP80" t="s">
         <v>481</v>
       </c>
-      <c r="AP80" t="s">
+    </row>
+    <row r="81" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="81" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="B81" t="s">
         <v>483</v>
-      </c>
-      <c r="B81" t="s">
-        <v>484</v>
       </c>
       <c r="C81" t="s">
         <v>118</v>
@@ -10707,42 +10704,42 @@
         <v>24</v>
       </c>
       <c r="Y81" t="s">
+        <v>484</v>
+      </c>
+      <c r="Z81" t="s">
         <v>485</v>
       </c>
-      <c r="Z81" t="s">
+      <c r="AC81" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF81" t="s">
         <v>486</v>
       </c>
-      <c r="AC81" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF81" t="s">
-        <v>487</v>
-      </c>
       <c r="AG81" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AI81" t="s">
         <v>77</v>
       </c>
       <c r="AJ81" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AM81" t="s">
         <v>54</v>
       </c>
       <c r="AO81" t="s">
+        <v>487</v>
+      </c>
+      <c r="AP81" t="s">
         <v>488</v>
       </c>
-      <c r="AP81" t="s">
+    </row>
+    <row r="82" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="82" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="B82" t="s">
         <v>490</v>
-      </c>
-      <c r="B82" t="s">
-        <v>491</v>
       </c>
       <c r="C82" t="s">
         <v>154</v>
@@ -10796,7 +10793,7 @@
         <v>48</v>
       </c>
       <c r="AD82" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AE82">
         <v>118</v>
@@ -10817,21 +10814,21 @@
         <v>54</v>
       </c>
       <c r="AN82" t="s">
+        <v>492</v>
+      </c>
+      <c r="AO82" t="s">
         <v>493</v>
       </c>
-      <c r="AO82" t="s">
+      <c r="AP82" t="s">
         <v>494</v>
       </c>
-      <c r="AP82" t="s">
+    </row>
+    <row r="83" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>489</v>
+      </c>
+      <c r="B83" t="s">
         <v>495</v>
-      </c>
-    </row>
-    <row r="83" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>490</v>
-      </c>
-      <c r="B83" t="s">
-        <v>496</v>
       </c>
       <c r="C83" t="s">
         <v>154</v>
@@ -10894,7 +10891,7 @@
         <v>48</v>
       </c>
       <c r="AD83" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AE83">
         <v>118</v>
@@ -10915,21 +10912,21 @@
         <v>54</v>
       </c>
       <c r="AN83" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AO83" t="s">
+        <v>496</v>
+      </c>
+      <c r="AP83" t="s">
         <v>497</v>
-      </c>
-      <c r="AP83" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="84" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B84" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C84" t="s">
         <v>118</v>
@@ -10992,7 +10989,7 @@
         <v>24</v>
       </c>
       <c r="Y84" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="Z84" t="s">
         <v>48</v>
@@ -11001,7 +10998,7 @@
         <v>48</v>
       </c>
       <c r="AD84" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AE84">
         <v>118</v>
@@ -11022,24 +11019,24 @@
         <v>54</v>
       </c>
       <c r="AN84" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AO84" t="s">
+        <v>500</v>
+      </c>
+      <c r="AP84" t="s">
         <v>501</v>
       </c>
-      <c r="AP84" t="s">
+      <c r="AS84" t="s">
         <v>502</v>
       </c>
-      <c r="AS84" t="s">
+    </row>
+    <row r="85" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>489</v>
+      </c>
+      <c r="B85" t="s">
         <v>503</v>
-      </c>
-    </row>
-    <row r="85" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>490</v>
-      </c>
-      <c r="B85" t="s">
-        <v>504</v>
       </c>
       <c r="C85" t="s">
         <v>118</v>
@@ -11066,7 +11063,7 @@
         <v>24</v>
       </c>
       <c r="Y85" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AC85" t="s">
         <v>48</v>
@@ -11084,18 +11081,18 @@
         <v>54</v>
       </c>
       <c r="AO85" t="s">
+        <v>505</v>
+      </c>
+      <c r="AP85" t="s">
         <v>506</v>
       </c>
-      <c r="AP85" t="s">
+    </row>
+    <row r="86" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>489</v>
+      </c>
+      <c r="B86" t="s">
         <v>507</v>
-      </c>
-    </row>
-    <row r="86" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>490</v>
-      </c>
-      <c r="B86" t="s">
-        <v>508</v>
       </c>
       <c r="C86" t="s">
         <v>118</v>
@@ -11122,24 +11119,24 @@
         <v>24</v>
       </c>
       <c r="Y86" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AM86" t="s">
         <v>54</v>
       </c>
       <c r="AO86" t="s">
+        <v>508</v>
+      </c>
+      <c r="AP86" t="s">
         <v>509</v>
       </c>
-      <c r="AP86" t="s">
+    </row>
+    <row r="87" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>489</v>
+      </c>
+      <c r="B87" t="s">
         <v>510</v>
-      </c>
-    </row>
-    <row r="87" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>490</v>
-      </c>
-      <c r="B87" t="s">
-        <v>511</v>
       </c>
       <c r="C87" t="s">
         <v>131</v>
@@ -11160,16 +11157,16 @@
         <v>24</v>
       </c>
       <c r="Y87" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AD87" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AE87" t="s">
         <v>252</v>
       </c>
       <c r="AH87" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AK87" t="s">
         <v>225</v>
@@ -11178,18 +11175,18 @@
         <v>54</v>
       </c>
       <c r="AO87" t="s">
+        <v>513</v>
+      </c>
+      <c r="AP87" t="s">
         <v>514</v>
-      </c>
-      <c r="AP87" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="88" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B88" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C88" t="s">
         <v>166</v>
@@ -11267,10 +11264,10 @@
         <v>48</v>
       </c>
       <c r="AD88" t="s">
+        <v>516</v>
+      </c>
+      <c r="AE88" t="s">
         <v>517</v>
-      </c>
-      <c r="AE88" t="s">
-        <v>518</v>
       </c>
       <c r="AF88" t="s">
         <v>150</v>
@@ -11282,33 +11279,33 @@
         <v>77</v>
       </c>
       <c r="AI88" t="s">
+        <v>518</v>
+      </c>
+      <c r="AK88" t="s">
         <v>519</v>
-      </c>
-      <c r="AK88" t="s">
-        <v>520</v>
       </c>
       <c r="AM88" t="s">
         <v>54</v>
       </c>
       <c r="AN88" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AO88" t="s">
+        <v>520</v>
+      </c>
+      <c r="AP88" t="s">
         <v>521</v>
       </c>
-      <c r="AP88" t="s">
+      <c r="AS88" t="s">
         <v>522</v>
       </c>
-      <c r="AS88" t="s">
+    </row>
+    <row r="89" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>489</v>
+      </c>
+      <c r="B89" t="s">
         <v>523</v>
-      </c>
-    </row>
-    <row r="89" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>490</v>
-      </c>
-      <c r="B89" t="s">
-        <v>524</v>
       </c>
       <c r="C89" t="s">
         <v>154</v>
@@ -11389,30 +11386,30 @@
         <v>77</v>
       </c>
       <c r="AI89" t="s">
+        <v>518</v>
+      </c>
+      <c r="AK89" t="s">
         <v>519</v>
-      </c>
-      <c r="AK89" t="s">
-        <v>520</v>
       </c>
       <c r="AM89" t="s">
         <v>54</v>
       </c>
       <c r="AN89" t="s">
+        <v>524</v>
+      </c>
+      <c r="AO89" t="s">
         <v>525</v>
       </c>
-      <c r="AO89" t="s">
+      <c r="AP89" t="s">
         <v>526</v>
-      </c>
-      <c r="AP89" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="90" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B90" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C90" t="s">
         <v>154</v>
@@ -11493,33 +11490,33 @@
         <v>77</v>
       </c>
       <c r="AI90" t="s">
+        <v>518</v>
+      </c>
+      <c r="AK90" t="s">
         <v>519</v>
-      </c>
-      <c r="AK90" t="s">
-        <v>520</v>
       </c>
       <c r="AM90" t="s">
         <v>54</v>
       </c>
       <c r="AN90" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AO90" t="s">
+        <v>528</v>
+      </c>
+      <c r="AP90" t="s">
         <v>529</v>
       </c>
-      <c r="AP90" t="s">
+      <c r="AS90" t="s">
         <v>530</v>
-      </c>
-      <c r="AS90" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="91" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B91" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C91" t="s">
         <v>166</v>
@@ -11561,48 +11558,48 @@
         <v>48</v>
       </c>
       <c r="AD91" t="s">
+        <v>516</v>
+      </c>
+      <c r="AE91" t="s">
         <v>517</v>
       </c>
-      <c r="AE91" t="s">
-        <v>518</v>
-      </c>
       <c r="AF91" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AG91" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AH91" t="s">
         <v>77</v>
       </c>
       <c r="AI91" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AK91" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AM91" t="s">
         <v>177</v>
       </c>
       <c r="AN91" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AO91" t="s">
+        <v>534</v>
+      </c>
+      <c r="AP91" t="s">
         <v>535</v>
       </c>
-      <c r="AP91" t="s">
+      <c r="AS91" t="s">
         <v>536</v>
-      </c>
-      <c r="AS91" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="92" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B92" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C92" t="s">
         <v>166</v>
@@ -11656,45 +11653,45 @@
         <v>48</v>
       </c>
       <c r="AD92" t="s">
+        <v>516</v>
+      </c>
+      <c r="AE92" t="s">
         <v>517</v>
       </c>
-      <c r="AE92" t="s">
-        <v>518</v>
-      </c>
       <c r="AF92" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AH92" t="s">
         <v>77</v>
       </c>
       <c r="AI92" t="s">
+        <v>518</v>
+      </c>
+      <c r="AK92" t="s">
         <v>519</v>
-      </c>
-      <c r="AK92" t="s">
-        <v>520</v>
       </c>
       <c r="AM92" t="s">
         <v>54</v>
       </c>
       <c r="AN92" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AO92" t="s">
+        <v>538</v>
+      </c>
+      <c r="AP92" t="s">
         <v>539</v>
       </c>
-      <c r="AP92" t="s">
+      <c r="AS92" t="s">
         <v>540</v>
-      </c>
-      <c r="AS92" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="93" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B93" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C93" t="s">
         <v>192</v>
@@ -11739,7 +11736,7 @@
         <v>48</v>
       </c>
       <c r="AD93" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AE93">
         <v>113</v>
@@ -11748,10 +11745,10 @@
         <v>120</v>
       </c>
       <c r="AH93" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AI93" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AK93">
         <v>-127</v>
@@ -11760,24 +11757,24 @@
         <v>54</v>
       </c>
       <c r="AN93" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AO93" t="s">
+        <v>543</v>
+      </c>
+      <c r="AP93" t="s">
         <v>544</v>
       </c>
-      <c r="AP93" t="s">
+      <c r="AS93" t="s">
         <v>545</v>
       </c>
-      <c r="AS93" t="s">
+    </row>
+    <row r="94" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>489</v>
+      </c>
+      <c r="B94" t="s">
         <v>546</v>
-      </c>
-    </row>
-    <row r="94" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>490</v>
-      </c>
-      <c r="B94" t="s">
-        <v>547</v>
       </c>
       <c r="C94" t="s">
         <v>271</v>
@@ -11825,21 +11822,21 @@
         <v>54</v>
       </c>
       <c r="AN94" t="s">
+        <v>547</v>
+      </c>
+      <c r="AO94" t="s">
         <v>548</v>
       </c>
-      <c r="AO94" t="s">
+      <c r="AP94" t="s">
         <v>549</v>
       </c>
-      <c r="AP94" t="s">
+    </row>
+    <row r="95" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>489</v>
+      </c>
+      <c r="B95" t="s">
         <v>550</v>
-      </c>
-    </row>
-    <row r="95" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>490</v>
-      </c>
-      <c r="B95" t="s">
-        <v>551</v>
       </c>
       <c r="C95" t="s">
         <v>271</v>
@@ -11896,21 +11893,21 @@
         <v>54</v>
       </c>
       <c r="AN95" t="s">
+        <v>551</v>
+      </c>
+      <c r="AO95" t="s">
         <v>552</v>
       </c>
-      <c r="AO95" t="s">
+      <c r="AP95" t="s">
         <v>553</v>
       </c>
-      <c r="AP95" t="s">
+    </row>
+    <row r="96" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="96" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+      <c r="B96" t="s">
         <v>555</v>
-      </c>
-      <c r="B96" t="s">
-        <v>556</v>
       </c>
       <c r="C96" t="s">
         <v>154</v>
@@ -11946,16 +11943,16 @@
         <v>49</v>
       </c>
       <c r="Z96" t="s">
+        <v>556</v>
+      </c>
+      <c r="AA96" t="s">
         <v>557</v>
-      </c>
-      <c r="AA96" t="s">
-        <v>558</v>
       </c>
       <c r="AB96" t="s">
         <v>70</v>
       </c>
       <c r="AC96" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AD96">
         <v>70</v>
@@ -11973,21 +11970,21 @@
         <v>54</v>
       </c>
       <c r="AN96" t="s">
+        <v>559</v>
+      </c>
+      <c r="AO96" t="s">
         <v>560</v>
       </c>
-      <c r="AO96" t="s">
+      <c r="AP96" t="s">
         <v>561</v>
       </c>
-      <c r="AP96" t="s">
+    </row>
+    <row r="97" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>554</v>
+      </c>
+      <c r="B97" t="s">
         <v>562</v>
-      </c>
-    </row>
-    <row r="97" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>555</v>
-      </c>
-      <c r="B97" t="s">
-        <v>563</v>
       </c>
       <c r="C97" t="s">
         <v>154</v>
@@ -12008,7 +12005,7 @@
         <v>2</v>
       </c>
       <c r="I97" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="N97">
         <v>4</v>
@@ -12017,7 +12014,7 @@
         <v>2</v>
       </c>
       <c r="Q97" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="V97" t="s">
         <v>48</v>
@@ -12032,36 +12029,36 @@
         <v>213</v>
       </c>
       <c r="Z97" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AC97" t="s">
         <v>48</v>
       </c>
       <c r="AD97" t="s">
+        <v>564</v>
+      </c>
+      <c r="AE97" t="s">
+        <v>517</v>
+      </c>
+      <c r="AL97" t="s">
         <v>565</v>
-      </c>
-      <c r="AE97" t="s">
-        <v>518</v>
-      </c>
-      <c r="AL97" t="s">
-        <v>566</v>
       </c>
       <c r="AM97" t="s">
         <v>54</v>
       </c>
       <c r="AO97" t="s">
+        <v>566</v>
+      </c>
+      <c r="AP97" t="s">
         <v>567</v>
       </c>
-      <c r="AP97" t="s">
+    </row>
+    <row r="98" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>554</v>
+      </c>
+      <c r="B98" t="s">
         <v>568</v>
-      </c>
-    </row>
-    <row r="98" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>555</v>
-      </c>
-      <c r="B98" t="s">
-        <v>569</v>
       </c>
       <c r="C98" t="s">
         <v>154</v>
@@ -12100,16 +12097,16 @@
         <v>49</v>
       </c>
       <c r="Z98" t="s">
+        <v>556</v>
+      </c>
+      <c r="AA98" t="s">
         <v>557</v>
-      </c>
-      <c r="AA98" t="s">
-        <v>558</v>
       </c>
       <c r="AB98" t="s">
         <v>70</v>
       </c>
       <c r="AC98" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AD98">
         <v>70</v>
@@ -12127,21 +12124,21 @@
         <v>54</v>
       </c>
       <c r="AN98" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AO98" t="s">
+        <v>569</v>
+      </c>
+      <c r="AP98" t="s">
         <v>570</v>
       </c>
-      <c r="AP98" t="s">
+    </row>
+    <row r="99" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="99" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
+      <c r="B99" t="s">
         <v>572</v>
-      </c>
-      <c r="B99" t="s">
-        <v>573</v>
       </c>
       <c r="C99" t="s">
         <v>166</v>
@@ -12192,7 +12189,7 @@
         <v>117</v>
       </c>
       <c r="AG99" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AH99" t="s">
         <v>143</v>
@@ -12204,21 +12201,21 @@
         <v>54</v>
       </c>
       <c r="AN99" t="s">
+        <v>573</v>
+      </c>
+      <c r="AO99" t="s">
         <v>574</v>
       </c>
-      <c r="AO99" t="s">
+      <c r="AP99" t="s">
         <v>575</v>
       </c>
-      <c r="AP99" t="s">
+    </row>
+    <row r="100" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>571</v>
+      </c>
+      <c r="B100" t="s">
         <v>576</v>
-      </c>
-    </row>
-    <row r="100" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>572</v>
-      </c>
-      <c r="B100" t="s">
-        <v>577</v>
       </c>
       <c r="C100" t="s">
         <v>192</v>
@@ -12263,16 +12260,16 @@
         <v>48</v>
       </c>
       <c r="AD100" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AE100">
         <v>108</v>
       </c>
       <c r="AG100" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AI100" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AJ100" t="s">
         <v>232</v>
@@ -12281,21 +12278,21 @@
         <v>54</v>
       </c>
       <c r="AN100" t="s">
+        <v>579</v>
+      </c>
+      <c r="AO100" t="s">
         <v>580</v>
       </c>
-      <c r="AO100" t="s">
+      <c r="AP100" t="s">
         <v>581</v>
       </c>
-      <c r="AP100" t="s">
+    </row>
+    <row r="101" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>571</v>
+      </c>
+      <c r="B101" t="s">
         <v>582</v>
-      </c>
-    </row>
-    <row r="101" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>572</v>
-      </c>
-      <c r="B101" t="s">
-        <v>583</v>
       </c>
       <c r="C101" t="s">
         <v>192</v>
@@ -12340,7 +12337,7 @@
         <v>48</v>
       </c>
       <c r="AE101" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AF101" t="s">
         <v>286</v>
@@ -12355,21 +12352,21 @@
         <v>54</v>
       </c>
       <c r="AN101" t="s">
+        <v>583</v>
+      </c>
+      <c r="AO101" t="s">
         <v>584</v>
       </c>
-      <c r="AO101" t="s">
+      <c r="AP101" t="s">
         <v>585</v>
       </c>
-      <c r="AP101" t="s">
+    </row>
+    <row r="102" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>571</v>
+      </c>
+      <c r="B102" t="s">
         <v>586</v>
-      </c>
-    </row>
-    <row r="102" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>572</v>
-      </c>
-      <c r="B102" t="s">
-        <v>587</v>
       </c>
       <c r="C102" t="s">
         <v>192</v>
@@ -12408,24 +12405,24 @@
         <v>97</v>
       </c>
       <c r="AM102" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AN102" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AO102" t="s">
+        <v>587</v>
+      </c>
+      <c r="AP102" t="s">
         <v>588</v>
       </c>
-      <c r="AP102" t="s">
+    </row>
+    <row r="103" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>571</v>
+      </c>
+      <c r="B103" t="s">
         <v>589</v>
-      </c>
-    </row>
-    <row r="103" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>572</v>
-      </c>
-      <c r="B103" t="s">
-        <v>590</v>
       </c>
       <c r="C103" t="s">
         <v>192</v>
@@ -12461,7 +12458,7 @@
         <v>49</v>
       </c>
       <c r="Z103" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AA103" t="s">
         <v>48</v>
@@ -12473,30 +12470,30 @@
         <v>50</v>
       </c>
       <c r="AG103" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AK103" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AM103" t="s">
         <v>157</v>
       </c>
       <c r="AN103" t="s">
+        <v>592</v>
+      </c>
+      <c r="AO103" t="s">
         <v>593</v>
       </c>
-      <c r="AO103" t="s">
+      <c r="AP103" t="s">
         <v>594</v>
       </c>
-      <c r="AP103" t="s">
+    </row>
+    <row r="104" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>571</v>
+      </c>
+      <c r="B104" t="s">
         <v>595</v>
-      </c>
-    </row>
-    <row r="104" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>572</v>
-      </c>
-      <c r="B104" t="s">
-        <v>596</v>
       </c>
       <c r="C104" t="s">
         <v>192</v>
@@ -12535,27 +12532,27 @@
         <v>48</v>
       </c>
       <c r="AD104" t="s">
+        <v>596</v>
+      </c>
+      <c r="AM104" t="s">
+        <v>429</v>
+      </c>
+      <c r="AN104" t="s">
+        <v>583</v>
+      </c>
+      <c r="AO104" t="s">
         <v>597</v>
       </c>
-      <c r="AM104" t="s">
-        <v>430</v>
-      </c>
-      <c r="AN104" t="s">
-        <v>584</v>
-      </c>
-      <c r="AO104" t="s">
+      <c r="AP104" t="s">
         <v>598</v>
-      </c>
-      <c r="AP104" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="105" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B105" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C105" t="s">
         <v>47</v>
@@ -12588,48 +12585,48 @@
         <v>24</v>
       </c>
       <c r="Y105" t="s">
+        <v>600</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA105" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC105" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE105" t="s">
         <v>601</v>
       </c>
-      <c r="Z105" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA105" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC105" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE105" t="s">
+      <c r="AG105" t="s">
         <v>602</v>
       </c>
-      <c r="AG105" t="s">
+      <c r="AM105" t="s">
+        <v>429</v>
+      </c>
+      <c r="AN105" t="s">
         <v>603</v>
       </c>
-      <c r="AM105" t="s">
-        <v>430</v>
-      </c>
-      <c r="AN105" t="s">
+      <c r="AO105" t="s">
         <v>604</v>
       </c>
-      <c r="AO105" t="s">
+      <c r="AP105" t="s">
         <v>605</v>
-      </c>
-      <c r="AP105" t="s">
-        <v>606</v>
       </c>
       <c r="AQ105" t="s">
         <v>63</v>
       </c>
       <c r="AS105" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="106" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>571</v>
+      </c>
+      <c r="B106" t="s">
         <v>607</v>
-      </c>
-    </row>
-    <row r="106" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>572</v>
-      </c>
-      <c r="B106" t="s">
-        <v>608</v>
       </c>
       <c r="C106" t="s">
         <v>271</v>
@@ -12650,7 +12647,7 @@
         <v>24</v>
       </c>
       <c r="Y106" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AA106" t="s">
         <v>48</v>
@@ -12659,24 +12656,24 @@
         <v>48</v>
       </c>
       <c r="AM106" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AN106" t="s">
+        <v>608</v>
+      </c>
+      <c r="AO106" t="s">
         <v>609</v>
       </c>
-      <c r="AO106" t="s">
+      <c r="AP106" t="s">
         <v>610</v>
       </c>
-      <c r="AP106" t="s">
+    </row>
+    <row r="107" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>571</v>
+      </c>
+      <c r="B107" t="s">
         <v>611</v>
-      </c>
-    </row>
-    <row r="107" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>572</v>
-      </c>
-      <c r="B107" t="s">
-        <v>612</v>
       </c>
       <c r="C107" t="s">
         <v>271</v>
@@ -12712,7 +12709,7 @@
         <v>24</v>
       </c>
       <c r="Y107" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AA107" t="s">
         <v>48</v>
@@ -12721,27 +12718,27 @@
         <v>48</v>
       </c>
       <c r="AD107" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AM107" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AN107" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AO107" t="s">
+        <v>612</v>
+      </c>
+      <c r="AP107" t="s">
         <v>613</v>
       </c>
-      <c r="AP107" t="s">
+    </row>
+    <row r="108" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
         <v>614</v>
       </c>
-    </row>
-    <row r="108" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+      <c r="B108" t="s">
         <v>615</v>
-      </c>
-      <c r="B108" t="s">
-        <v>616</v>
       </c>
       <c r="C108" t="s">
         <v>192</v>
@@ -12780,7 +12777,7 @@
         <v>48</v>
       </c>
       <c r="AB108" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AC108" t="s">
         <v>48</v>
@@ -12789,27 +12786,27 @@
         <v>258</v>
       </c>
       <c r="AG108" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AM108" t="s">
         <v>157</v>
       </c>
       <c r="AN108" t="s">
+        <v>618</v>
+      </c>
+      <c r="AO108" t="s">
         <v>619</v>
       </c>
-      <c r="AO108" t="s">
+      <c r="AP108" t="s">
         <v>620</v>
       </c>
-      <c r="AP108" t="s">
+    </row>
+    <row r="109" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>614</v>
+      </c>
+      <c r="B109" t="s">
         <v>621</v>
-      </c>
-    </row>
-    <row r="109" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>615</v>
-      </c>
-      <c r="B109" t="s">
-        <v>622</v>
       </c>
       <c r="C109" t="s">
         <v>166</v>
@@ -12845,7 +12842,7 @@
         <v>49</v>
       </c>
       <c r="Z109" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AA109" t="s">
         <v>48</v>
@@ -12863,7 +12860,7 @@
         <v>109.5</v>
       </c>
       <c r="AH109" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AI109" t="s">
         <v>282</v>
@@ -12872,21 +12869,21 @@
         <v>54</v>
       </c>
       <c r="AN109" t="s">
+        <v>624</v>
+      </c>
+      <c r="AO109" t="s">
         <v>625</v>
       </c>
-      <c r="AO109" t="s">
+      <c r="AP109" t="s">
         <v>626</v>
       </c>
-      <c r="AP109" t="s">
+    </row>
+    <row r="110" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="110" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+      <c r="B110" t="s">
         <v>628</v>
-      </c>
-      <c r="B110" t="s">
-        <v>629</v>
       </c>
       <c r="C110" t="s">
         <v>271</v>
@@ -12937,10 +12934,10 @@
         <v>77</v>
       </c>
       <c r="AI110" t="s">
+        <v>629</v>
+      </c>
+      <c r="AK110" t="s">
         <v>630</v>
-      </c>
-      <c r="AK110" t="s">
-        <v>631</v>
       </c>
       <c r="AL110">
         <v>-126.8</v>
@@ -12949,21 +12946,21 @@
         <v>177</v>
       </c>
       <c r="AN110" t="s">
+        <v>631</v>
+      </c>
+      <c r="AO110" t="s">
         <v>632</v>
       </c>
-      <c r="AO110" t="s">
+      <c r="AP110" t="s">
         <v>633</v>
       </c>
-      <c r="AP110" t="s">
+    </row>
+    <row r="111" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>627</v>
+      </c>
+      <c r="B111" t="s">
         <v>634</v>
-      </c>
-    </row>
-    <row r="111" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>628</v>
-      </c>
-      <c r="B111" t="s">
-        <v>635</v>
       </c>
       <c r="C111" t="s">
         <v>271</v>
@@ -13008,7 +13005,7 @@
         <v>48</v>
       </c>
       <c r="AD111" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="AE111">
         <v>100</v>
@@ -13029,21 +13026,21 @@
         <v>157</v>
       </c>
       <c r="AN111" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AO111" t="s">
+        <v>636</v>
+      </c>
+      <c r="AP111" t="s">
         <v>637</v>
       </c>
-      <c r="AP111" t="s">
+    </row>
+    <row r="112" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
         <v>638</v>
       </c>
-    </row>
-    <row r="112" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
+      <c r="B112" t="s">
         <v>639</v>
-      </c>
-      <c r="B112" t="s">
-        <v>640</v>
       </c>
       <c r="C112" t="s">
         <v>131</v>
@@ -13052,7 +13049,7 @@
         <v>4600</v>
       </c>
       <c r="E112" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G112">
         <v>16</v>
@@ -13061,7 +13058,7 @@
         <v>63</v>
       </c>
       <c r="M112" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="N112">
         <v>16</v>
@@ -13073,10 +13070,10 @@
         <v>63</v>
       </c>
       <c r="U112" t="s">
+        <v>640</v>
+      </c>
+      <c r="V112" t="s">
         <v>641</v>
-      </c>
-      <c r="V112" t="s">
-        <v>642</v>
       </c>
       <c r="W112">
         <v>192</v>
@@ -13085,13 +13082,13 @@
         <v>24</v>
       </c>
       <c r="Y112" t="s">
+        <v>642</v>
+      </c>
+      <c r="AC112" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD112" t="s">
         <v>643</v>
-      </c>
-      <c r="AC112" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD112" t="s">
-        <v>644</v>
       </c>
       <c r="AE112">
         <v>119</v>
@@ -13100,7 +13097,7 @@
         <v>120</v>
       </c>
       <c r="AH112" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="AI112" t="s">
         <v>169</v>
@@ -13112,18 +13109,18 @@
         <v>54</v>
       </c>
       <c r="AO112" t="s">
+        <v>645</v>
+      </c>
+      <c r="AP112" t="s">
         <v>646</v>
       </c>
-      <c r="AP112" t="s">
+    </row>
+    <row r="113" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>638</v>
+      </c>
+      <c r="B113" t="s">
         <v>647</v>
-      </c>
-    </row>
-    <row r="113" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>639</v>
-      </c>
-      <c r="B113" t="s">
-        <v>648</v>
       </c>
       <c r="C113" t="s">
         <v>131</v>
@@ -13132,13 +13129,13 @@
         <v>3600</v>
       </c>
       <c r="E113" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G113">
         <v>8</v>
       </c>
       <c r="M113" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="N113">
         <v>8</v>
@@ -13147,10 +13144,10 @@
         <v>2</v>
       </c>
       <c r="U113" t="s">
+        <v>640</v>
+      </c>
+      <c r="V113" t="s">
         <v>641</v>
-      </c>
-      <c r="V113" t="s">
-        <v>642</v>
       </c>
       <c r="W113">
         <v>192</v>
@@ -13159,13 +13156,13 @@
         <v>24</v>
       </c>
       <c r="Y113" t="s">
+        <v>642</v>
+      </c>
+      <c r="AC113" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD113" t="s">
         <v>643</v>
-      </c>
-      <c r="AC113" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD113" t="s">
-        <v>644</v>
       </c>
       <c r="AE113">
         <v>119</v>
@@ -13174,7 +13171,7 @@
         <v>120</v>
       </c>
       <c r="AH113" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="AI113" t="s">
         <v>169</v>
@@ -13186,18 +13183,18 @@
         <v>54</v>
       </c>
       <c r="AO113" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AP113" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="114" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B114" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C114" t="s">
         <v>131</v>
@@ -13209,7 +13206,7 @@
         <v>2</v>
       </c>
       <c r="I114" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="K114" t="s">
         <v>137</v>
@@ -13224,7 +13221,7 @@
         <v>1</v>
       </c>
       <c r="Q114" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="S114" t="s">
         <v>137</v>
@@ -13239,7 +13236,7 @@
         <v>24</v>
       </c>
       <c r="Y114" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AC114" t="s">
         <v>48</v>
@@ -13251,30 +13248,30 @@
         <v>127</v>
       </c>
       <c r="AH114" t="s">
+        <v>652</v>
+      </c>
+      <c r="AI114" t="s">
         <v>653</v>
-      </c>
-      <c r="AI114" t="s">
-        <v>654</v>
       </c>
       <c r="AM114" t="s">
         <v>54</v>
       </c>
       <c r="AO114" t="s">
+        <v>654</v>
+      </c>
+      <c r="AP114" t="s">
         <v>655</v>
       </c>
-      <c r="AP114" t="s">
+      <c r="AS114" t="s">
         <v>656</v>
       </c>
-      <c r="AS114" t="s">
+    </row>
+    <row r="115" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>638</v>
+      </c>
+      <c r="B115" t="s">
         <v>657</v>
-      </c>
-    </row>
-    <row r="115" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>639</v>
-      </c>
-      <c r="B115" t="s">
-        <v>658</v>
       </c>
       <c r="C115" t="s">
         <v>118</v>
@@ -13331,16 +13328,16 @@
         <v>24</v>
       </c>
       <c r="Y115" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AA115" t="s">
+        <v>658</v>
+      </c>
+      <c r="AC115" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD115" t="s">
         <v>659</v>
-      </c>
-      <c r="AC115" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD115" t="s">
-        <v>660</v>
       </c>
       <c r="AE115">
         <v>119</v>
@@ -13349,7 +13346,7 @@
         <v>120</v>
       </c>
       <c r="AH115" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AI115" t="s">
         <v>176</v>
@@ -13361,21 +13358,21 @@
         <v>54</v>
       </c>
       <c r="AN115" t="s">
+        <v>661</v>
+      </c>
+      <c r="AO115" t="s">
         <v>662</v>
       </c>
-      <c r="AO115" t="s">
+      <c r="AP115" t="s">
         <v>663</v>
       </c>
-      <c r="AP115" t="s">
+    </row>
+    <row r="116" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
         <v>664</v>
       </c>
-    </row>
-    <row r="116" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
+      <c r="B116" t="s">
         <v>665</v>
-      </c>
-      <c r="B116" t="s">
-        <v>666</v>
       </c>
       <c r="C116" t="s">
         <v>166</v>
@@ -13420,7 +13417,7 @@
         <v>48</v>
       </c>
       <c r="AD116" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AE116">
         <v>113</v>
@@ -13429,7 +13426,7 @@
         <v>95</v>
       </c>
       <c r="AH116" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="AI116" t="s">
         <v>53</v>
@@ -13441,21 +13438,21 @@
         <v>54</v>
       </c>
       <c r="AN116" t="s">
+        <v>668</v>
+      </c>
+      <c r="AO116" t="s">
         <v>669</v>
       </c>
-      <c r="AO116" t="s">
+      <c r="AP116" t="s">
         <v>670</v>
-      </c>
-      <c r="AP116" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="117" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B117" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C117" t="s">
         <v>192</v>
@@ -13497,19 +13494,19 @@
         <v>48</v>
       </c>
       <c r="AD117" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="AE117">
         <v>104</v>
       </c>
       <c r="AG117" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="AH117" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="AI117" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AK117">
         <v>-128</v>
@@ -13518,24 +13515,24 @@
         <v>54</v>
       </c>
       <c r="AN117" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AO117" t="s">
+        <v>674</v>
+      </c>
+      <c r="AP117" t="s">
         <v>675</v>
       </c>
-      <c r="AP117" t="s">
+      <c r="AS117" t="s">
         <v>676</v>
-      </c>
-      <c r="AS117" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="118" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B118" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C118" t="s">
         <v>192</v>
@@ -13583,16 +13580,16 @@
         <v>237</v>
       </c>
       <c r="AE118" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="AF118" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AH118" t="s">
         <v>53</v>
       </c>
       <c r="AI118" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AK118" t="s">
         <v>162</v>
@@ -13601,24 +13598,24 @@
         <v>54</v>
       </c>
       <c r="AN118" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AO118" t="s">
+        <v>679</v>
+      </c>
+      <c r="AP118" t="s">
         <v>680</v>
       </c>
-      <c r="AP118" t="s">
+      <c r="AS118" t="s">
         <v>681</v>
       </c>
-      <c r="AS118" t="s">
+    </row>
+    <row r="119" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>664</v>
+      </c>
+      <c r="B119" t="s">
         <v>682</v>
-      </c>
-    </row>
-    <row r="119" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>665</v>
-      </c>
-      <c r="B119" t="s">
-        <v>683</v>
       </c>
       <c r="C119" t="s">
         <v>166</v>
@@ -13669,7 +13666,7 @@
         <v>60</v>
       </c>
       <c r="AF119" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="AG119">
         <v>104</v>
@@ -13678,30 +13675,30 @@
         <v>77</v>
       </c>
       <c r="AI119" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="AL119" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AM119" t="s">
         <v>54</v>
       </c>
       <c r="AN119" t="s">
+        <v>685</v>
+      </c>
+      <c r="AO119" t="s">
         <v>686</v>
       </c>
-      <c r="AO119" t="s">
+      <c r="AP119" t="s">
         <v>687</v>
-      </c>
-      <c r="AP119" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="120" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B120" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C120" t="s">
         <v>192</v>
@@ -13737,10 +13734,10 @@
         <v>48</v>
       </c>
       <c r="AD120" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="AH120" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="AK120" t="s">
         <v>162</v>
@@ -13749,24 +13746,24 @@
         <v>54</v>
       </c>
       <c r="AN120" t="s">
+        <v>690</v>
+      </c>
+      <c r="AO120" t="s">
         <v>691</v>
       </c>
-      <c r="AO120" t="s">
+      <c r="AP120" t="s">
         <v>692</v>
       </c>
-      <c r="AP120" t="s">
+      <c r="AS120" t="s">
         <v>693</v>
       </c>
-      <c r="AS120" t="s">
+    </row>
+    <row r="121" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>664</v>
+      </c>
+      <c r="B121" t="s">
         <v>694</v>
-      </c>
-    </row>
-    <row r="121" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>665</v>
-      </c>
-      <c r="B121" t="s">
-        <v>695</v>
       </c>
       <c r="C121" t="s">
         <v>192</v>
@@ -13805,10 +13802,10 @@
         <v>48</v>
       </c>
       <c r="AD121" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="AH121" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="AI121" t="s">
         <v>53</v>
@@ -13820,21 +13817,21 @@
         <v>272</v>
       </c>
       <c r="AN121" t="s">
+        <v>695</v>
+      </c>
+      <c r="AO121" t="s">
         <v>696</v>
       </c>
-      <c r="AO121" t="s">
+      <c r="AP121" t="s">
         <v>697</v>
-      </c>
-      <c r="AP121" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="122" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B122" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C122" t="s">
         <v>192</v>
@@ -13870,10 +13867,10 @@
         <v>48</v>
       </c>
       <c r="AD122" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="AH122" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="AI122" t="s">
         <v>53</v>
@@ -13885,24 +13882,24 @@
         <v>177</v>
       </c>
       <c r="AN122" t="s">
+        <v>699</v>
+      </c>
+      <c r="AO122" t="s">
         <v>700</v>
       </c>
-      <c r="AO122" t="s">
+      <c r="AP122" t="s">
         <v>701</v>
       </c>
-      <c r="AP122" t="s">
+      <c r="AS122" t="s">
         <v>702</v>
-      </c>
-      <c r="AS122" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="123" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>703</v>
+      </c>
+      <c r="B123" t="s">
         <v>704</v>
-      </c>
-      <c r="B123" t="s">
-        <v>705</v>
       </c>
       <c r="C123" t="s">
         <v>166</v>
@@ -13950,7 +13947,7 @@
         <v>51</v>
       </c>
       <c r="AJ123" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AK123">
         <v>-125</v>
@@ -13959,24 +13956,24 @@
         <v>54</v>
       </c>
       <c r="AN123" t="s">
+        <v>706</v>
+      </c>
+      <c r="AO123" t="s">
         <v>707</v>
       </c>
-      <c r="AO123" t="s">
+      <c r="AP123" t="s">
         <v>708</v>
       </c>
-      <c r="AP123" t="s">
+      <c r="AS123" t="s">
         <v>709</v>
-      </c>
-      <c r="AS123" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="124" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B124" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C124" t="s">
         <v>166</v>
@@ -14000,7 +13997,7 @@
         <v>6</v>
       </c>
       <c r="O124" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P124">
         <v>2</v>
@@ -14024,7 +14021,7 @@
         <v>51</v>
       </c>
       <c r="AJ124" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AK124">
         <v>-125</v>
@@ -14033,24 +14030,24 @@
         <v>54</v>
       </c>
       <c r="AN124" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AO124" t="s">
+        <v>711</v>
+      </c>
+      <c r="AP124" t="s">
         <v>712</v>
       </c>
-      <c r="AP124" t="s">
+      <c r="AS124" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="125" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>703</v>
+      </c>
+      <c r="B125" t="s">
         <v>713</v>
-      </c>
-      <c r="AS124" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="125" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>704</v>
-      </c>
-      <c r="B125" t="s">
-        <v>714</v>
       </c>
       <c r="C125" t="s">
         <v>47</v>
@@ -14095,24 +14092,24 @@
         <v>48</v>
       </c>
       <c r="AD125" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="AM125" t="s">
         <v>54</v>
       </c>
       <c r="AO125" t="s">
+        <v>715</v>
+      </c>
+      <c r="AP125" t="s">
         <v>716</v>
       </c>
-      <c r="AP125" t="s">
+    </row>
+    <row r="126" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>703</v>
+      </c>
+      <c r="B126" t="s">
         <v>717</v>
-      </c>
-    </row>
-    <row r="126" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>704</v>
-      </c>
-      <c r="B126" t="s">
-        <v>718</v>
       </c>
       <c r="C126" t="s">
         <v>271</v>
@@ -14127,7 +14124,7 @@
         <v>2</v>
       </c>
       <c r="G126" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="N126">
         <v>2</v>
@@ -14163,18 +14160,18 @@
         <v>54</v>
       </c>
       <c r="AO126" t="s">
+        <v>718</v>
+      </c>
+      <c r="AP126" t="s">
         <v>719</v>
       </c>
-      <c r="AP126" t="s">
+    </row>
+    <row r="127" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>703</v>
+      </c>
+      <c r="B127" t="s">
         <v>720</v>
-      </c>
-    </row>
-    <row r="127" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>704</v>
-      </c>
-      <c r="B127" t="s">
-        <v>721</v>
       </c>
       <c r="C127" t="s">
         <v>271</v>
@@ -14219,18 +14216,18 @@
         <v>157</v>
       </c>
       <c r="AO127" t="s">
+        <v>721</v>
+      </c>
+      <c r="AP127" t="s">
         <v>722</v>
       </c>
-      <c r="AP127" t="s">
+    </row>
+    <row r="128" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>703</v>
+      </c>
+      <c r="B128" t="s">
         <v>723</v>
-      </c>
-    </row>
-    <row r="128" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>704</v>
-      </c>
-      <c r="B128" t="s">
-        <v>724</v>
       </c>
       <c r="C128" t="s">
         <v>271</v>
@@ -14278,27 +14275,27 @@
         <v>51</v>
       </c>
       <c r="AG128" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="AM128" t="s">
         <v>54</v>
       </c>
       <c r="AN128" t="s">
+        <v>725</v>
+      </c>
+      <c r="AO128" t="s">
         <v>726</v>
       </c>
-      <c r="AO128" t="s">
+      <c r="AP128" t="s">
         <v>727</v>
       </c>
-      <c r="AP128" t="s">
+    </row>
+    <row r="129" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>703</v>
+      </c>
+      <c r="B129" t="s">
         <v>728</v>
-      </c>
-    </row>
-    <row r="129" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>704</v>
-      </c>
-      <c r="B129" t="s">
-        <v>729</v>
       </c>
       <c r="C129" t="s">
         <v>47</v>
@@ -14346,7 +14343,7 @@
         <v>51</v>
       </c>
       <c r="AJ129" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AL129">
         <v>-128</v>
@@ -14355,21 +14352,21 @@
         <v>54</v>
       </c>
       <c r="AN129" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AO129" t="s">
+        <v>729</v>
+      </c>
+      <c r="AP129" t="s">
         <v>730</v>
-      </c>
-      <c r="AP129" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="130" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B130" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C130" t="s">
         <v>47</v>
@@ -14417,7 +14414,7 @@
         <v>60</v>
       </c>
       <c r="AJ130" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="AL130" t="s">
         <v>162</v>
@@ -14426,24 +14423,24 @@
         <v>54</v>
       </c>
       <c r="AN130" t="s">
+        <v>733</v>
+      </c>
+      <c r="AO130" t="s">
         <v>734</v>
       </c>
-      <c r="AO130" t="s">
+      <c r="AP130" t="s">
         <v>735</v>
       </c>
-      <c r="AP130" t="s">
+      <c r="AS130" t="s">
         <v>736</v>
       </c>
-      <c r="AS130" t="s">
+    </row>
+    <row r="131" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>703</v>
+      </c>
+      <c r="B131" t="s">
         <v>737</v>
-      </c>
-    </row>
-    <row r="131" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>704</v>
-      </c>
-      <c r="B131" t="s">
-        <v>738</v>
       </c>
       <c r="C131" t="s">
         <v>47</v>
@@ -14464,7 +14461,7 @@
         <v>2</v>
       </c>
       <c r="O131" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P131">
         <v>1</v>
@@ -14491,7 +14488,7 @@
         <v>51</v>
       </c>
       <c r="AJ131" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AL131">
         <v>-128</v>
@@ -14500,21 +14497,21 @@
         <v>54</v>
       </c>
       <c r="AN131" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AO131" t="s">
+        <v>738</v>
+      </c>
+      <c r="AP131" t="s">
         <v>739</v>
-      </c>
-      <c r="AP131" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="132" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B132" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C132" t="s">
         <v>47</v>
@@ -14562,7 +14559,7 @@
         <v>60</v>
       </c>
       <c r="AH132" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="AL132" t="s">
         <v>162</v>
@@ -14571,21 +14568,21 @@
         <v>54</v>
       </c>
       <c r="AO132" t="s">
+        <v>741</v>
+      </c>
+      <c r="AP132" t="s">
         <v>742</v>
       </c>
-      <c r="AP132" t="s">
-        <v>743</v>
-      </c>
       <c r="AS132" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="133" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>743</v>
+      </c>
+      <c r="B133" t="s">
         <v>744</v>
-      </c>
-      <c r="B133" t="s">
-        <v>745</v>
       </c>
       <c r="C133" t="s">
         <v>131</v>
@@ -14624,16 +14621,16 @@
         <v>32</v>
       </c>
       <c r="Y133" t="s">
+        <v>745</v>
+      </c>
+      <c r="Z133" t="s">
         <v>746</v>
-      </c>
-      <c r="Z133" t="s">
-        <v>747</v>
       </c>
       <c r="AB133" t="s">
         <v>70</v>
       </c>
       <c r="AC133" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AD133">
         <v>66</v>
@@ -14648,7 +14645,7 @@
         <v>302</v>
       </c>
       <c r="AI133" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AK133">
         <v>-128</v>
@@ -14657,24 +14654,24 @@
         <v>54</v>
       </c>
       <c r="AN133" t="s">
+        <v>748</v>
+      </c>
+      <c r="AO133" t="s">
         <v>749</v>
       </c>
-      <c r="AO133" t="s">
+      <c r="AP133" t="s">
         <v>750</v>
       </c>
-      <c r="AP133" t="s">
+      <c r="AS133" t="s">
         <v>751</v>
-      </c>
-      <c r="AS133" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="134" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>752</v>
+      </c>
+      <c r="B134" t="s">
         <v>753</v>
-      </c>
-      <c r="B134" t="s">
-        <v>754</v>
       </c>
       <c r="C134" t="s">
         <v>131</v>
@@ -14689,7 +14686,7 @@
         <v>63</v>
       </c>
       <c r="M134" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="N134">
         <v>8</v>
@@ -14698,7 +14695,7 @@
         <v>1</v>
       </c>
       <c r="U134" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="W134">
         <v>192</v>
@@ -14719,30 +14716,30 @@
         <v>70</v>
       </c>
       <c r="AC134" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="AM134" t="s">
         <v>54</v>
       </c>
       <c r="AN134" t="s">
+        <v>755</v>
+      </c>
+      <c r="AO134" t="s">
         <v>756</v>
       </c>
-      <c r="AO134" t="s">
+      <c r="AP134" t="s">
         <v>757</v>
       </c>
-      <c r="AP134" t="s">
+      <c r="AS134" t="s">
         <v>758</v>
-      </c>
-      <c r="AS134" t="s">
-        <v>759</v>
       </c>
     </row>
     <row r="135" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B135" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C135" t="s">
         <v>131</v>
@@ -14760,7 +14757,7 @@
         <v>2</v>
       </c>
       <c r="M135" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="N135">
         <v>8</v>
@@ -14769,7 +14766,7 @@
         <v>1</v>
       </c>
       <c r="U135" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="V135" t="s">
         <v>48</v>
@@ -14781,7 +14778,7 @@
         <v>24</v>
       </c>
       <c r="Y135" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="Z135" t="s">
         <v>167</v>
@@ -14790,10 +14787,10 @@
         <v>48</v>
       </c>
       <c r="AB135" t="s">
+        <v>761</v>
+      </c>
+      <c r="AC135" t="s">
         <v>762</v>
-      </c>
-      <c r="AC135" t="s">
-        <v>763</v>
       </c>
       <c r="AD135">
         <v>90</v>
@@ -14802,30 +14799,30 @@
         <v>252</v>
       </c>
       <c r="AL135" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="AM135" t="s">
         <v>54</v>
       </c>
       <c r="AN135" t="s">
+        <v>764</v>
+      </c>
+      <c r="AO135" t="s">
         <v>765</v>
       </c>
-      <c r="AO135" t="s">
+      <c r="AP135" t="s">
         <v>766</v>
       </c>
-      <c r="AP135" t="s">
+      <c r="AS135" t="s">
         <v>767</v>
-      </c>
-      <c r="AS135" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="136" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>768</v>
+      </c>
+      <c r="B136" t="s">
         <v>769</v>
-      </c>
-      <c r="B136" t="s">
-        <v>770</v>
       </c>
       <c r="C136" t="s">
         <v>131</v>
@@ -14843,7 +14840,7 @@
         <v>63</v>
       </c>
       <c r="H136" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="I136" t="s">
         <v>326</v>
@@ -14870,7 +14867,7 @@
         <v>24</v>
       </c>
       <c r="Y136" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="AA136" t="s">
         <v>48</v>
@@ -14903,24 +14900,24 @@
         <v>186</v>
       </c>
       <c r="AN136" t="s">
+        <v>772</v>
+      </c>
+      <c r="AO136" t="s">
         <v>773</v>
       </c>
-      <c r="AO136" t="s">
+      <c r="AP136" t="s">
         <v>774</v>
       </c>
-      <c r="AP136" t="s">
+      <c r="AS136" t="s">
         <v>775</v>
       </c>
-      <c r="AS136" t="s">
+    </row>
+    <row r="137" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>768</v>
+      </c>
+      <c r="B137" t="s">
         <v>776</v>
-      </c>
-    </row>
-    <row r="137" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>769</v>
-      </c>
-      <c r="B137" t="s">
-        <v>777</v>
       </c>
       <c r="C137" t="s">
         <v>118</v>
@@ -14953,7 +14950,7 @@
         <v>24</v>
       </c>
       <c r="Y137" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="AB137" t="s">
         <v>70</v>
@@ -14962,21 +14959,21 @@
         <v>54</v>
       </c>
       <c r="AN137" t="s">
+        <v>778</v>
+      </c>
+      <c r="AO137" t="s">
         <v>779</v>
       </c>
-      <c r="AO137" t="s">
+      <c r="AP137" t="s">
         <v>780</v>
-      </c>
-      <c r="AP137" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="138" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B138" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C138" t="s">
         <v>118</v>
@@ -15015,7 +15012,7 @@
         <v>24</v>
       </c>
       <c r="Y138" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="AA138" t="s">
         <v>48</v>
@@ -15027,7 +15024,7 @@
         <v>48</v>
       </c>
       <c r="AE138" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AF138">
         <v>125</v>
@@ -15039,24 +15036,24 @@
         <v>54</v>
       </c>
       <c r="AN138" t="s">
+        <v>782</v>
+      </c>
+      <c r="AO138" t="s">
         <v>783</v>
       </c>
-      <c r="AO138" t="s">
+      <c r="AP138" t="s">
         <v>784</v>
       </c>
-      <c r="AP138" t="s">
+      <c r="AS138" t="s">
         <v>785</v>
-      </c>
-      <c r="AS138" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="139" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B139" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C139" t="s">
         <v>154</v>
@@ -15104,7 +15101,7 @@
         <v>24</v>
       </c>
       <c r="Y139" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="AA139" t="s">
         <v>48</v>
@@ -15116,7 +15113,7 @@
         <v>48</v>
       </c>
       <c r="AD139" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AE139">
         <v>118</v>
@@ -15131,24 +15128,24 @@
         <v>54</v>
       </c>
       <c r="AN139" t="s">
+        <v>789</v>
+      </c>
+      <c r="AO139" t="s">
         <v>790</v>
       </c>
-      <c r="AO139" t="s">
+      <c r="AP139" t="s">
         <v>791</v>
       </c>
-      <c r="AP139" t="s">
+      <c r="AS139" t="s">
         <v>792</v>
-      </c>
-      <c r="AS139" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="140" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B140" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="C140" t="s">
         <v>118</v>
@@ -15226,7 +15223,7 @@
         <v>48</v>
       </c>
       <c r="AD140" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="AE140">
         <v>118</v>
@@ -15244,24 +15241,24 @@
         <v>177</v>
       </c>
       <c r="AN140" t="s">
+        <v>795</v>
+      </c>
+      <c r="AO140" t="s">
         <v>796</v>
       </c>
-      <c r="AO140" t="s">
+      <c r="AP140" t="s">
         <v>797</v>
       </c>
-      <c r="AP140" t="s">
+      <c r="AS140" t="s">
         <v>798</v>
       </c>
-      <c r="AS140" t="s">
+    </row>
+    <row r="141" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>768</v>
+      </c>
+      <c r="B141" t="s">
         <v>799</v>
-      </c>
-    </row>
-    <row r="141" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>769</v>
-      </c>
-      <c r="B141" t="s">
-        <v>800</v>
       </c>
       <c r="C141" t="s">
         <v>118</v>
@@ -15279,7 +15276,7 @@
         <v>8</v>
       </c>
       <c r="H141" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I141">
         <v>16</v>
@@ -15318,7 +15315,7 @@
         <v>24</v>
       </c>
       <c r="Y141" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="AA141" t="s">
         <v>48</v>
@@ -15336,7 +15333,7 @@
         <v>252</v>
       </c>
       <c r="AF141" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="AG141">
         <v>125</v>
@@ -15354,21 +15351,21 @@
         <v>177</v>
       </c>
       <c r="AN141" t="s">
+        <v>801</v>
+      </c>
+      <c r="AO141" t="s">
         <v>802</v>
       </c>
-      <c r="AO141" t="s">
+      <c r="AP141" t="s">
         <v>803</v>
-      </c>
-      <c r="AP141" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="142" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B142" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C142" t="s">
         <v>118</v>
@@ -15404,7 +15401,7 @@
         <v>24</v>
       </c>
       <c r="Y142" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="AA142" t="s">
         <v>48</v>
@@ -15428,24 +15425,24 @@
         <v>54</v>
       </c>
       <c r="AN142" t="s">
+        <v>806</v>
+      </c>
+      <c r="AO142" t="s">
         <v>807</v>
       </c>
-      <c r="AO142" t="s">
+      <c r="AP142" t="s">
         <v>808</v>
       </c>
-      <c r="AP142" t="s">
+      <c r="AS142" t="s">
         <v>809</v>
-      </c>
-      <c r="AS142" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="143" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B143" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C143" t="s">
         <v>192</v>
@@ -15502,24 +15499,24 @@
         <v>54</v>
       </c>
       <c r="AN143" t="s">
+        <v>811</v>
+      </c>
+      <c r="AO143" t="s">
         <v>812</v>
       </c>
-      <c r="AO143" t="s">
+      <c r="AP143" t="s">
         <v>813</v>
       </c>
-      <c r="AP143" t="s">
+      <c r="AS143" t="s">
         <v>814</v>
-      </c>
-      <c r="AS143" t="s">
-        <v>815</v>
       </c>
     </row>
     <row r="144" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B144" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C144" t="s">
         <v>166</v>
@@ -15561,7 +15558,7 @@
         <v>48</v>
       </c>
       <c r="AG144" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AI144" t="s">
         <v>184</v>
@@ -15573,24 +15570,24 @@
         <v>177</v>
       </c>
       <c r="AN144" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AO144" t="s">
+        <v>816</v>
+      </c>
+      <c r="AP144" t="s">
         <v>817</v>
       </c>
-      <c r="AP144" t="s">
+      <c r="AS144" t="s">
         <v>818</v>
-      </c>
-      <c r="AS144" t="s">
-        <v>819</v>
       </c>
     </row>
     <row r="145" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B145" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C145" t="s">
         <v>166</v>
@@ -15608,7 +15605,7 @@
         <v>2</v>
       </c>
       <c r="H145" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="O145">
         <v>4</v>
@@ -15650,24 +15647,24 @@
         <v>54</v>
       </c>
       <c r="AN145" t="s">
+        <v>820</v>
+      </c>
+      <c r="AO145" t="s">
         <v>821</v>
       </c>
-      <c r="AO145" t="s">
+      <c r="AP145" t="s">
         <v>822</v>
       </c>
-      <c r="AP145" t="s">
+      <c r="AS145" t="s">
         <v>823</v>
-      </c>
-      <c r="AS145" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="146" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B146" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C146" t="s">
         <v>154</v>
@@ -15748,7 +15745,7 @@
         <v>74</v>
       </c>
       <c r="AE146" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AF146">
         <v>125</v>
@@ -15763,24 +15760,24 @@
         <v>54</v>
       </c>
       <c r="AN146" t="s">
+        <v>825</v>
+      </c>
+      <c r="AO146" t="s">
         <v>826</v>
       </c>
-      <c r="AO146" t="s">
+      <c r="AP146" t="s">
         <v>827</v>
       </c>
-      <c r="AP146" t="s">
+      <c r="AS146" t="s">
         <v>828</v>
       </c>
-      <c r="AS146" t="s">
+    </row>
+    <row r="147" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
         <v>829</v>
       </c>
-    </row>
-    <row r="147" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
+      <c r="B147" t="s">
         <v>830</v>
-      </c>
-      <c r="B147" t="s">
-        <v>831</v>
       </c>
       <c r="C147" t="s">
         <v>118</v>
@@ -15849,7 +15846,7 @@
         <v>48</v>
       </c>
       <c r="AD147" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="AE147">
         <v>136</v>
@@ -15870,21 +15867,21 @@
         <v>54</v>
       </c>
       <c r="AN147" t="s">
+        <v>832</v>
+      </c>
+      <c r="AO147" t="s">
         <v>833</v>
       </c>
-      <c r="AO147" t="s">
+      <c r="AP147" t="s">
         <v>834</v>
       </c>
-      <c r="AP147" t="s">
+    </row>
+    <row r="148" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
         <v>835</v>
       </c>
-    </row>
-    <row r="148" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
+      <c r="B148" t="s">
         <v>836</v>
-      </c>
-      <c r="B148" t="s">
-        <v>837</v>
       </c>
       <c r="C148" t="s">
         <v>192</v>
@@ -15929,7 +15926,7 @@
         <v>64</v>
       </c>
       <c r="AE148" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AF148" t="s">
         <v>223</v>
@@ -15941,18 +15938,18 @@
         <v>54</v>
       </c>
       <c r="AO148" t="s">
+        <v>837</v>
+      </c>
+      <c r="AP148" t="s">
         <v>838</v>
       </c>
-      <c r="AP148" t="s">
+    </row>
+    <row r="149" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>835</v>
+      </c>
+      <c r="B149" t="s">
         <v>839</v>
-      </c>
-    </row>
-    <row r="149" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>836</v>
-      </c>
-      <c r="B149" t="s">
-        <v>840</v>
       </c>
       <c r="C149" t="s">
         <v>166</v>
@@ -16018,18 +16015,18 @@
         <v>54</v>
       </c>
       <c r="AO149" t="s">
+        <v>840</v>
+      </c>
+      <c r="AP149" t="s">
         <v>841</v>
-      </c>
-      <c r="AP149" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="150" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>842</v>
+      </c>
+      <c r="B150" t="s">
         <v>843</v>
-      </c>
-      <c r="B150" t="s">
-        <v>844</v>
       </c>
       <c r="C150" t="s">
         <v>192</v>
@@ -16071,7 +16068,7 @@
         <v>48</v>
       </c>
       <c r="AD150" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AE150">
         <v>90</v>
@@ -16089,24 +16086,24 @@
         <v>157</v>
       </c>
       <c r="AN150" t="s">
+        <v>845</v>
+      </c>
+      <c r="AO150" t="s">
         <v>846</v>
       </c>
-      <c r="AO150" t="s">
+      <c r="AP150" t="s">
         <v>847</v>
       </c>
-      <c r="AP150" t="s">
+      <c r="AS150" t="s">
         <v>848</v>
-      </c>
-      <c r="AS150" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="151" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B151" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C151" t="s">
         <v>192</v>
@@ -16145,39 +16142,39 @@
         <v>48</v>
       </c>
       <c r="AD151" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AE151">
         <v>105</v>
       </c>
       <c r="AF151" t="s">
+        <v>851</v>
+      </c>
+      <c r="AH151" t="s">
         <v>852</v>
-      </c>
-      <c r="AH151" t="s">
-        <v>853</v>
       </c>
       <c r="AM151" t="s">
         <v>54</v>
       </c>
       <c r="AN151" t="s">
+        <v>853</v>
+      </c>
+      <c r="AO151" t="s">
         <v>854</v>
       </c>
-      <c r="AO151" t="s">
+      <c r="AP151" t="s">
         <v>855</v>
       </c>
-      <c r="AP151" t="s">
+      <c r="AS151" t="s">
         <v>856</v>
       </c>
-      <c r="AS151" t="s">
+    </row>
+    <row r="152" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>842</v>
+      </c>
+      <c r="B152" t="s">
         <v>857</v>
-      </c>
-    </row>
-    <row r="152" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
-        <v>843</v>
-      </c>
-      <c r="B152" t="s">
-        <v>858</v>
       </c>
       <c r="C152" t="s">
         <v>192</v>
@@ -16216,7 +16213,7 @@
         <v>49</v>
       </c>
       <c r="Z152" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="AA152" t="s">
         <v>48</v>
@@ -16231,7 +16228,7 @@
         <v>286</v>
       </c>
       <c r="AF152" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AH152" t="s">
         <v>77</v>
@@ -16243,21 +16240,21 @@
         <v>54</v>
       </c>
       <c r="AN152" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AO152" t="s">
+        <v>859</v>
+      </c>
+      <c r="AP152" t="s">
         <v>860</v>
       </c>
-      <c r="AP152" t="s">
+    </row>
+    <row r="153" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>842</v>
+      </c>
+      <c r="B153" t="s">
         <v>861</v>
-      </c>
-    </row>
-    <row r="153" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>843</v>
-      </c>
-      <c r="B153" t="s">
-        <v>862</v>
       </c>
       <c r="C153" t="s">
         <v>166</v>
@@ -16320,21 +16317,21 @@
         <v>54</v>
       </c>
       <c r="AN153" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AO153" t="s">
+        <v>862</v>
+      </c>
+      <c r="AP153" t="s">
         <v>863</v>
-      </c>
-      <c r="AP153" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="154" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B154" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C154" t="s">
         <v>271</v>
@@ -16385,39 +16382,39 @@
         <v>60</v>
       </c>
       <c r="AG154" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="AH154" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AI154" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="AK154" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AM154" t="s">
         <v>54</v>
       </c>
       <c r="AN154" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="AO154" t="s">
+        <v>865</v>
+      </c>
+      <c r="AP154" t="s">
         <v>866</v>
       </c>
-      <c r="AP154" t="s">
+      <c r="AS154" t="s">
         <v>867</v>
       </c>
-      <c r="AS154" t="s">
+    </row>
+    <row r="155" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>842</v>
+      </c>
+      <c r="B155" t="s">
         <v>868</v>
-      </c>
-    </row>
-    <row r="155" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>843</v>
-      </c>
-      <c r="B155" t="s">
-        <v>869</v>
       </c>
       <c r="C155" t="s">
         <v>271</v>
@@ -16465,7 +16462,7 @@
         <v>48</v>
       </c>
       <c r="AD155" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="AE155">
         <v>96</v>
@@ -16480,21 +16477,21 @@
         <v>54</v>
       </c>
       <c r="AN155" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="AO155" t="s">
+        <v>870</v>
+      </c>
+      <c r="AP155" t="s">
         <v>871</v>
-      </c>
-      <c r="AP155" t="s">
-        <v>872</v>
       </c>
     </row>
     <row r="156" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B156" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="C156" t="s">
         <v>192</v>
@@ -16530,7 +16527,7 @@
         <v>49</v>
       </c>
       <c r="Z156" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AA156" t="s">
         <v>48</v>
@@ -16539,7 +16536,7 @@
         <v>48</v>
       </c>
       <c r="AD156" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="AE156">
         <v>106</v>
@@ -16551,30 +16548,30 @@
         <v>120</v>
       </c>
       <c r="AK156" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AM156" t="s">
         <v>54</v>
       </c>
       <c r="AN156" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="AO156" t="s">
+        <v>874</v>
+      </c>
+      <c r="AP156" t="s">
         <v>875</v>
       </c>
-      <c r="AP156" t="s">
+      <c r="AS156" t="s">
         <v>876</v>
       </c>
-      <c r="AS156" t="s">
+    </row>
+    <row r="157" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>842</v>
+      </c>
+      <c r="B157" t="s">
         <v>877</v>
-      </c>
-    </row>
-    <row r="157" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>843</v>
-      </c>
-      <c r="B157" t="s">
-        <v>878</v>
       </c>
       <c r="C157" t="s">
         <v>47</v>
@@ -16619,16 +16616,16 @@
         <v>48</v>
       </c>
       <c r="AD157" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="AF157" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AH157" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="AI157" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="AK157" t="s">
         <v>162</v>
@@ -16637,21 +16634,21 @@
         <v>54</v>
       </c>
       <c r="AN157" t="s">
+        <v>879</v>
+      </c>
+      <c r="AO157" t="s">
         <v>880</v>
       </c>
-      <c r="AO157" t="s">
+      <c r="AP157" t="s">
         <v>881</v>
       </c>
-      <c r="AP157" t="s">
+    </row>
+    <row r="158" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>842</v>
+      </c>
+      <c r="B158" t="s">
         <v>882</v>
-      </c>
-    </row>
-    <row r="158" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>843</v>
-      </c>
-      <c r="B158" t="s">
-        <v>883</v>
       </c>
       <c r="C158" t="s">
         <v>47</v>
@@ -16699,13 +16696,13 @@
         <v>48</v>
       </c>
       <c r="AG158" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="AH158" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="AI158" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="AL158" t="s">
         <v>162</v>
@@ -16714,21 +16711,21 @@
         <v>54</v>
       </c>
       <c r="AN158" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="AO158" t="s">
+        <v>883</v>
+      </c>
+      <c r="AP158" t="s">
         <v>884</v>
       </c>
-      <c r="AP158" t="s">
+    </row>
+    <row r="159" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>842</v>
+      </c>
+      <c r="B159" t="s">
         <v>885</v>
-      </c>
-    </row>
-    <row r="159" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
-        <v>843</v>
-      </c>
-      <c r="B159" t="s">
-        <v>886</v>
       </c>
       <c r="C159" t="s">
         <v>47</v>
@@ -16770,13 +16767,13 @@
         <v>48</v>
       </c>
       <c r="AD159" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="AF159" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AG159" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="AK159" t="s">
         <v>162</v>
@@ -16785,21 +16782,21 @@
         <v>54</v>
       </c>
       <c r="AN159" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="AO159" t="s">
+        <v>886</v>
+      </c>
+      <c r="AP159" t="s">
         <v>887</v>
       </c>
-      <c r="AP159" t="s">
+    </row>
+    <row r="160" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
         <v>888</v>
       </c>
-    </row>
-    <row r="160" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
+      <c r="B160" t="s">
         <v>889</v>
-      </c>
-      <c r="B160" t="s">
-        <v>890</v>
       </c>
       <c r="C160" t="s">
         <v>131</v>
@@ -16862,13 +16859,13 @@
         <v>49</v>
       </c>
       <c r="Z160" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AC160" t="s">
         <v>48</v>
       </c>
       <c r="AD160" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AE160">
         <v>116</v>
@@ -16889,18 +16886,18 @@
         <v>54</v>
       </c>
       <c r="AO160" t="s">
+        <v>890</v>
+      </c>
+      <c r="AP160" t="s">
         <v>891</v>
       </c>
-      <c r="AP160" t="s">
+    </row>
+    <row r="161" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>888</v>
+      </c>
+      <c r="B161" t="s">
         <v>892</v>
-      </c>
-    </row>
-    <row r="161" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
-        <v>889</v>
-      </c>
-      <c r="B161" t="s">
-        <v>893</v>
       </c>
       <c r="C161" t="s">
         <v>131</v>
@@ -16951,7 +16948,7 @@
         <v>48</v>
       </c>
       <c r="AD161" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AE161">
         <v>116</v>
@@ -16972,18 +16969,18 @@
         <v>54</v>
       </c>
       <c r="AO161" t="s">
+        <v>893</v>
+      </c>
+      <c r="AP161" t="s">
         <v>894</v>
-      </c>
-      <c r="AP161" t="s">
-        <v>895</v>
       </c>
     </row>
     <row r="162" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B162" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C162" t="s">
         <v>131</v>
@@ -17049,7 +17046,7 @@
         <v>48</v>
       </c>
       <c r="AD162" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AE162">
         <v>116</v>
@@ -17070,21 +17067,21 @@
         <v>54</v>
       </c>
       <c r="AO162" t="s">
+        <v>896</v>
+      </c>
+      <c r="AP162" t="s">
         <v>897</v>
       </c>
-      <c r="AP162" t="s">
+      <c r="AS162" t="s">
         <v>898</v>
-      </c>
-      <c r="AS162" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="163" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B163" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C163" t="s">
         <v>131</v>
@@ -17150,13 +17147,13 @@
         <v>48</v>
       </c>
       <c r="AD163" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AE163" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AF163" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AH163" t="s">
         <v>169</v>
@@ -17171,21 +17168,21 @@
         <v>54</v>
       </c>
       <c r="AO163" t="s">
+        <v>900</v>
+      </c>
+      <c r="AP163" t="s">
         <v>901</v>
       </c>
-      <c r="AP163" t="s">
+      <c r="AS163" t="s">
         <v>902</v>
       </c>
-      <c r="AS163" t="s">
+    </row>
+    <row r="164" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
         <v>903</v>
       </c>
-    </row>
-    <row r="164" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
+      <c r="B164" t="s">
         <v>904</v>
-      </c>
-      <c r="B164" t="s">
-        <v>905</v>
       </c>
       <c r="C164" t="s">
         <v>154</v>
@@ -17221,18 +17218,18 @@
         <v>54</v>
       </c>
       <c r="AO164" t="s">
+        <v>905</v>
+      </c>
+      <c r="AP164" t="s">
         <v>906</v>
-      </c>
-      <c r="AP164" t="s">
-        <v>907</v>
       </c>
     </row>
     <row r="165" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B165" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C165" t="s">
         <v>47</v>
@@ -17271,27 +17268,27 @@
         <v>102</v>
       </c>
       <c r="AJ165" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AM165" t="s">
         <v>54</v>
       </c>
       <c r="AO165" t="s">
+        <v>909</v>
+      </c>
+      <c r="AP165" t="s">
         <v>910</v>
       </c>
-      <c r="AP165" t="s">
+      <c r="AS165" t="s">
         <v>911</v>
-      </c>
-      <c r="AS165" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="166" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
+        <v>912</v>
+      </c>
+      <c r="B166" t="s">
         <v>913</v>
-      </c>
-      <c r="B166" t="s">
-        <v>914</v>
       </c>
       <c r="C166" t="s">
         <v>118</v>
@@ -17342,7 +17339,7 @@
         <v>49</v>
       </c>
       <c r="AB166" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="AC166" t="s">
         <v>48</v>
@@ -17360,21 +17357,21 @@
         <v>54</v>
       </c>
       <c r="AO166" t="s">
+        <v>915</v>
+      </c>
+      <c r="AP166" t="s">
         <v>916</v>
       </c>
-      <c r="AP166" t="s">
+      <c r="AS166" t="s">
         <v>917</v>
-      </c>
-      <c r="AS166" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="167" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B167" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C167" t="s">
         <v>118</v>
@@ -17407,39 +17404,39 @@
         <v>49</v>
       </c>
       <c r="AB167" t="s">
+        <v>919</v>
+      </c>
+      <c r="AC167" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE167" t="s">
         <v>920</v>
       </c>
-      <c r="AC167" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE167" t="s">
-        <v>921</v>
-      </c>
       <c r="AF167" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AI167" t="s">
         <v>156</v>
       </c>
       <c r="AM167" t="s">
+        <v>921</v>
+      </c>
+      <c r="AO167" t="s">
         <v>922</v>
       </c>
-      <c r="AO167" t="s">
+      <c r="AP167" t="s">
         <v>923</v>
       </c>
-      <c r="AP167" t="s">
+      <c r="AS167" t="s">
         <v>924</v>
-      </c>
-      <c r="AS167" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="168" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B168" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C168" t="s">
         <v>154</v>
@@ -17499,7 +17496,7 @@
         <v>48</v>
       </c>
       <c r="AD168" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="AE168">
         <v>117</v>
@@ -17508,10 +17505,10 @@
         <v>118</v>
       </c>
       <c r="AH168" t="s">
+        <v>927</v>
+      </c>
+      <c r="AI168" t="s">
         <v>928</v>
-      </c>
-      <c r="AI168" t="s">
-        <v>929</v>
       </c>
       <c r="AK168">
         <v>-117</v>
@@ -17520,21 +17517,21 @@
         <v>54</v>
       </c>
       <c r="AO168" t="s">
+        <v>929</v>
+      </c>
+      <c r="AP168" t="s">
         <v>930</v>
       </c>
-      <c r="AP168" t="s">
+      <c r="AS168" t="s">
         <v>931</v>
       </c>
-      <c r="AS168" t="s">
+    </row>
+    <row r="169" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>912</v>
+      </c>
+      <c r="B169" t="s">
         <v>932</v>
-      </c>
-    </row>
-    <row r="169" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
-        <v>913</v>
-      </c>
-      <c r="B169" t="s">
-        <v>933</v>
       </c>
       <c r="C169" t="s">
         <v>154</v>
@@ -17552,27 +17549,27 @@
         <v>24</v>
       </c>
       <c r="Y169" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="AM169" t="s">
         <v>54</v>
       </c>
       <c r="AN169" t="s">
+        <v>934</v>
+      </c>
+      <c r="AO169" t="s">
         <v>935</v>
       </c>
-      <c r="AO169" t="s">
+      <c r="AP169" t="s">
         <v>936</v>
       </c>
-      <c r="AP169" t="s">
+    </row>
+    <row r="170" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>912</v>
+      </c>
+      <c r="B170" t="s">
         <v>937</v>
-      </c>
-    </row>
-    <row r="170" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
-        <v>913</v>
-      </c>
-      <c r="B170" t="s">
-        <v>938</v>
       </c>
       <c r="C170" t="s">
         <v>131</v>
@@ -17590,7 +17587,7 @@
         <v>8</v>
       </c>
       <c r="H170" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I170">
         <v>16</v>
@@ -17632,7 +17629,7 @@
         <v>49</v>
       </c>
       <c r="Z170" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="AA170" t="s">
         <v>48</v>
@@ -17644,13 +17641,13 @@
         <v>48</v>
       </c>
       <c r="AD170" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="AE170">
         <v>118</v>
       </c>
       <c r="AF170" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="AI170" t="s">
         <v>184</v>
@@ -17659,21 +17656,21 @@
         <v>54</v>
       </c>
       <c r="AN170" t="s">
+        <v>941</v>
+      </c>
+      <c r="AO170" t="s">
         <v>942</v>
       </c>
-      <c r="AO170" t="s">
+      <c r="AP170" t="s">
         <v>943</v>
-      </c>
-      <c r="AP170" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="171" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B171" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="C171" t="s">
         <v>118</v>
@@ -17757,10 +17754,10 @@
         <v>214</v>
       </c>
       <c r="AE171" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AF171" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AK171" t="s">
         <v>162</v>
@@ -17769,21 +17766,21 @@
         <v>54</v>
       </c>
       <c r="AO171" t="s">
+        <v>945</v>
+      </c>
+      <c r="AP171" t="s">
         <v>946</v>
       </c>
-      <c r="AP171" t="s">
+      <c r="AS171" t="s">
         <v>947</v>
       </c>
-      <c r="AS171" t="s">
+    </row>
+    <row r="172" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>912</v>
+      </c>
+      <c r="B172" t="s">
         <v>948</v>
-      </c>
-    </row>
-    <row r="172" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>913</v>
-      </c>
-      <c r="B172" t="s">
-        <v>949</v>
       </c>
       <c r="C172" t="s">
         <v>131</v>
@@ -17801,7 +17798,7 @@
         <v>8</v>
       </c>
       <c r="H172" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I172">
         <v>16</v>
@@ -17843,7 +17840,7 @@
         <v>49</v>
       </c>
       <c r="Z172" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="AA172" t="s">
         <v>48</v>
@@ -17858,33 +17855,33 @@
         <v>75</v>
       </c>
       <c r="AE172" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="AF172" t="s">
         <v>252</v>
       </c>
       <c r="AK172" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="AM172" t="s">
         <v>54</v>
       </c>
       <c r="AN172" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="AO172" t="s">
+        <v>951</v>
+      </c>
+      <c r="AP172" t="s">
         <v>952</v>
-      </c>
-      <c r="AP172" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="173" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B173" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="C173" t="s">
         <v>131</v>
@@ -17965,27 +17962,27 @@
         <v>184</v>
       </c>
       <c r="AK173" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="AM173" t="s">
         <v>54</v>
       </c>
       <c r="AO173" t="s">
+        <v>954</v>
+      </c>
+      <c r="AP173" t="s">
         <v>955</v>
       </c>
-      <c r="AP173" t="s">
+      <c r="AS173" t="s">
         <v>956</v>
       </c>
-      <c r="AS173" t="s">
+    </row>
+    <row r="174" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>912</v>
+      </c>
+      <c r="B174" t="s">
         <v>957</v>
-      </c>
-    </row>
-    <row r="174" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
-        <v>913</v>
-      </c>
-      <c r="B174" t="s">
-        <v>958</v>
       </c>
       <c r="C174" t="s">
         <v>131</v>
@@ -18024,16 +18021,16 @@
         <v>24</v>
       </c>
       <c r="Y174" t="s">
+        <v>958</v>
+      </c>
+      <c r="Z174" t="s">
         <v>959</v>
       </c>
-      <c r="Z174" t="s">
+      <c r="AB174" t="s">
         <v>960</v>
       </c>
-      <c r="AB174" t="s">
+      <c r="AC174" t="s">
         <v>961</v>
-      </c>
-      <c r="AC174" t="s">
-        <v>962</v>
       </c>
       <c r="AD174">
         <v>75</v>
@@ -18048,27 +18045,27 @@
         <v>232</v>
       </c>
       <c r="AI174" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AM174" t="s">
         <v>54</v>
       </c>
       <c r="AN174" t="s">
+        <v>962</v>
+      </c>
+      <c r="AO174" t="s">
         <v>963</v>
       </c>
-      <c r="AO174" t="s">
+      <c r="AP174" t="s">
         <v>964</v>
-      </c>
-      <c r="AP174" t="s">
-        <v>965</v>
       </c>
     </row>
     <row r="175" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
+        <v>965</v>
+      </c>
+      <c r="B175" t="s">
         <v>966</v>
-      </c>
-      <c r="B175" t="s">
-        <v>967</v>
       </c>
       <c r="C175" t="s">
         <v>192</v>
@@ -18107,7 +18104,7 @@
         <v>48</v>
       </c>
       <c r="AD175" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="AE175">
         <v>104</v>
@@ -18116,7 +18113,7 @@
         <v>112</v>
       </c>
       <c r="AH175" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="AK175">
         <v>-128</v>
@@ -18125,24 +18122,24 @@
         <v>54</v>
       </c>
       <c r="AN175" t="s">
+        <v>968</v>
+      </c>
+      <c r="AO175" t="s">
         <v>969</v>
       </c>
-      <c r="AO175" t="s">
+      <c r="AP175" t="s">
         <v>970</v>
       </c>
-      <c r="AP175" t="s">
+      <c r="AS175" t="s">
         <v>971</v>
-      </c>
-      <c r="AS175" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="176" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B176" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C176" t="s">
         <v>192</v>
@@ -18169,33 +18166,33 @@
         <v>48</v>
       </c>
       <c r="AD176" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="AE176">
         <v>100</v>
       </c>
       <c r="AM176" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AN176" t="s">
+        <v>974</v>
+      </c>
+      <c r="AO176" t="s">
         <v>975</v>
       </c>
-      <c r="AO176" t="s">
+      <c r="AP176" t="s">
         <v>976</v>
       </c>
-      <c r="AP176" t="s">
+      <c r="AS176" t="s">
         <v>977</v>
       </c>
-      <c r="AS176" t="s">
+    </row>
+    <row r="177" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>965</v>
+      </c>
+      <c r="B177" t="s">
         <v>978</v>
-      </c>
-    </row>
-    <row r="177" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
-        <v>966</v>
-      </c>
-      <c r="B177" t="s">
-        <v>979</v>
       </c>
       <c r="C177" t="s">
         <v>271</v>
@@ -18237,7 +18234,7 @@
         <v>48</v>
       </c>
       <c r="AD177" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="AL177">
         <v>-131.5</v>
@@ -18246,21 +18243,21 @@
         <v>54</v>
       </c>
       <c r="AN177" t="s">
+        <v>980</v>
+      </c>
+      <c r="AO177" t="s">
         <v>981</v>
       </c>
-      <c r="AO177" t="s">
+      <c r="AP177" t="s">
         <v>982</v>
       </c>
-      <c r="AP177" t="s">
+    </row>
+    <row r="178" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>965</v>
+      </c>
+      <c r="B178" t="s">
         <v>983</v>
-      </c>
-    </row>
-    <row r="178" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
-        <v>966</v>
-      </c>
-      <c r="B178" t="s">
-        <v>984</v>
       </c>
       <c r="C178" t="s">
         <v>271</v>
@@ -18275,7 +18272,7 @@
         <v>4</v>
       </c>
       <c r="H178" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="N178">
         <v>2</v>
@@ -18305,7 +18302,7 @@
         <v>48</v>
       </c>
       <c r="AD178" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="AL178">
         <v>-131.5</v>
@@ -18314,21 +18311,21 @@
         <v>54</v>
       </c>
       <c r="AN178" t="s">
+        <v>984</v>
+      </c>
+      <c r="AO178" t="s">
         <v>985</v>
       </c>
-      <c r="AO178" t="s">
+      <c r="AP178" t="s">
         <v>986</v>
       </c>
-      <c r="AP178" t="s">
+    </row>
+    <row r="179" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>965</v>
+      </c>
+      <c r="B179" t="s">
         <v>987</v>
-      </c>
-    </row>
-    <row r="179" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
-        <v>966</v>
-      </c>
-      <c r="B179" t="s">
-        <v>988</v>
       </c>
       <c r="C179" t="s">
         <v>271</v>
@@ -18370,33 +18367,33 @@
         <v>48</v>
       </c>
       <c r="AD179" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="AG179" t="s">
         <v>286</v>
       </c>
       <c r="AK179" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="AM179" t="s">
         <v>54</v>
       </c>
       <c r="AN179" t="s">
+        <v>989</v>
+      </c>
+      <c r="AO179" t="s">
         <v>990</v>
       </c>
-      <c r="AO179" t="s">
+      <c r="AP179" t="s">
         <v>991</v>
       </c>
-      <c r="AP179" t="s">
+    </row>
+    <row r="180" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
         <v>992</v>
       </c>
-    </row>
-    <row r="180" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
+      <c r="B180" t="s">
         <v>993</v>
-      </c>
-      <c r="B180" t="s">
-        <v>994</v>
       </c>
       <c r="C180" t="s">
         <v>271</v>
@@ -18444,21 +18441,21 @@
         <v>177</v>
       </c>
       <c r="AN180" t="s">
+        <v>994</v>
+      </c>
+      <c r="AO180" t="s">
         <v>995</v>
       </c>
-      <c r="AO180" t="s">
+      <c r="AP180" t="s">
         <v>996</v>
       </c>
-      <c r="AP180" t="s">
+    </row>
+    <row r="181" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>992</v>
+      </c>
+      <c r="B181" t="s">
         <v>997</v>
-      </c>
-    </row>
-    <row r="181" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>993</v>
-      </c>
-      <c r="B181" t="s">
-        <v>998</v>
       </c>
       <c r="C181" t="s">
         <v>271</v>
@@ -18509,21 +18506,21 @@
         <v>54</v>
       </c>
       <c r="AN181" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="AO181" t="s">
+        <v>998</v>
+      </c>
+      <c r="AP181" t="s">
         <v>999</v>
       </c>
-      <c r="AP181" t="s">
+    </row>
+    <row r="182" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>992</v>
+      </c>
+      <c r="B182" t="s">
         <v>1000</v>
-      </c>
-    </row>
-    <row r="182" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
-        <v>993</v>
-      </c>
-      <c r="B182" t="s">
-        <v>1001</v>
       </c>
       <c r="C182" t="s">
         <v>271</v>
@@ -18553,7 +18550,7 @@
         <v>24</v>
       </c>
       <c r="Y182" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="Z182" t="s">
         <v>69</v>
@@ -18571,18 +18568,18 @@
         <v>54</v>
       </c>
       <c r="AO182" t="s">
+        <v>1002</v>
+      </c>
+      <c r="AP182" t="s">
         <v>1003</v>
       </c>
-      <c r="AP182" t="s">
+    </row>
+    <row r="183" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>992</v>
+      </c>
+      <c r="B183" t="s">
         <v>1004</v>
-      </c>
-    </row>
-    <row r="183" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
-        <v>993</v>
-      </c>
-      <c r="B183" t="s">
-        <v>1005</v>
       </c>
       <c r="C183" t="s">
         <v>271</v>
@@ -18624,21 +18621,21 @@
         <v>48</v>
       </c>
       <c r="AM183" t="s">
+        <v>1005</v>
+      </c>
+      <c r="AO183" t="s">
         <v>1006</v>
       </c>
-      <c r="AO183" t="s">
+      <c r="AP183" t="s">
         <v>1007</v>
       </c>
-      <c r="AP183" t="s">
+    </row>
+    <row r="184" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>992</v>
+      </c>
+      <c r="B184" t="s">
         <v>1008</v>
-      </c>
-    </row>
-    <row r="184" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>993</v>
-      </c>
-      <c r="B184" t="s">
-        <v>1009</v>
       </c>
       <c r="C184" t="s">
         <v>271</v>
@@ -18689,21 +18686,21 @@
         <v>186</v>
       </c>
       <c r="AN184" t="s">
+        <v>1009</v>
+      </c>
+      <c r="AO184" t="s">
         <v>1010</v>
       </c>
-      <c r="AO184" t="s">
+      <c r="AP184" t="s">
         <v>1011</v>
-      </c>
-      <c r="AP184" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="185" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B185" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C185" t="s">
         <v>192</v>
@@ -18745,30 +18742,30 @@
         <v>48</v>
       </c>
       <c r="AG185" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="AM185" t="s">
         <v>177</v>
       </c>
       <c r="AN185" t="s">
+        <v>1013</v>
+      </c>
+      <c r="AO185" t="s">
         <v>1014</v>
       </c>
-      <c r="AO185" t="s">
+      <c r="AP185" t="s">
         <v>1015</v>
       </c>
-      <c r="AP185" t="s">
+      <c r="AS185" t="s">
         <v>1016</v>
       </c>
-      <c r="AS185" t="s">
+    </row>
+    <row r="186" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>992</v>
+      </c>
+      <c r="B186" t="s">
         <v>1017</v>
-      </c>
-    </row>
-    <row r="186" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
-        <v>993</v>
-      </c>
-      <c r="B186" t="s">
-        <v>1018</v>
       </c>
       <c r="C186" t="s">
         <v>166</v>
@@ -18816,27 +18813,27 @@
         <v>48</v>
       </c>
       <c r="AG186" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="AM186" t="s">
         <v>177</v>
       </c>
       <c r="AN186" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="AO186" t="s">
+        <v>1018</v>
+      </c>
+      <c r="AP186" t="s">
         <v>1019</v>
       </c>
-      <c r="AP186" t="s">
+    </row>
+    <row r="187" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>992</v>
+      </c>
+      <c r="B187" t="s">
         <v>1020</v>
-      </c>
-    </row>
-    <row r="187" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>993</v>
-      </c>
-      <c r="B187" t="s">
-        <v>1021</v>
       </c>
       <c r="C187" t="s">
         <v>166</v>
@@ -18881,27 +18878,27 @@
         <v>48</v>
       </c>
       <c r="AG187" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="AM187" t="s">
         <v>177</v>
       </c>
       <c r="AN187" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="AO187" t="s">
+        <v>1021</v>
+      </c>
+      <c r="AP187" t="s">
         <v>1022</v>
       </c>
-      <c r="AP187" t="s">
+    </row>
+    <row r="188" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
         <v>1023</v>
       </c>
-    </row>
-    <row r="188" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
+      <c r="B188" t="s">
         <v>1024</v>
-      </c>
-      <c r="B188" t="s">
-        <v>1025</v>
       </c>
       <c r="C188" t="s">
         <v>271</v>
@@ -18934,24 +18931,24 @@
         <v>48</v>
       </c>
       <c r="AD188" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="AM188" t="s">
         <v>272</v>
       </c>
       <c r="AO188" t="s">
+        <v>1025</v>
+      </c>
+      <c r="AP188" t="s">
         <v>1026</v>
       </c>
-      <c r="AP188" t="s">
+    </row>
+    <row r="189" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
         <v>1027</v>
       </c>
-    </row>
-    <row r="189" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
+      <c r="B189" t="s">
         <v>1028</v>
-      </c>
-      <c r="B189" t="s">
-        <v>1029</v>
       </c>
       <c r="C189" t="s">
         <v>47</v>
@@ -18975,7 +18972,7 @@
         <v>2</v>
       </c>
       <c r="O189" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="P189">
         <v>1</v>
@@ -18999,33 +18996,33 @@
         <v>48</v>
       </c>
       <c r="AD189" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="AH189" t="s">
         <v>99</v>
       </c>
       <c r="AI189" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="AL189" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AM189" t="s">
         <v>54</v>
       </c>
       <c r="AO189" t="s">
+        <v>1030</v>
+      </c>
+      <c r="AP189" t="s">
         <v>1031</v>
-      </c>
-      <c r="AP189" t="s">
-        <v>1032</v>
       </c>
     </row>
     <row r="190" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B190" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="C190" t="s">
         <v>47</v>
@@ -19070,30 +19067,30 @@
         <v>48</v>
       </c>
       <c r="AD190" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="AL190" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AM190" t="s">
         <v>54</v>
       </c>
       <c r="AO190" t="s">
+        <v>1033</v>
+      </c>
+      <c r="AP190" t="s">
         <v>1034</v>
       </c>
-      <c r="AP190" t="s">
+      <c r="AS190" t="s">
         <v>1035</v>
       </c>
-      <c r="AS190" t="s">
+    </row>
+    <row r="191" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B191" t="s">
         <v>1036</v>
-      </c>
-    </row>
-    <row r="191" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
-        <v>1028</v>
-      </c>
-      <c r="B191" t="s">
-        <v>1037</v>
       </c>
       <c r="C191" t="s">
         <v>47</v>
@@ -19117,7 +19114,7 @@
         <v>2</v>
       </c>
       <c r="O191" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="P191">
         <v>1</v>
@@ -19141,30 +19138,30 @@
         <v>48</v>
       </c>
       <c r="AD191" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="AH191" t="s">
         <v>58</v>
       </c>
       <c r="AL191" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AM191" t="s">
         <v>54</v>
       </c>
       <c r="AO191" t="s">
+        <v>1037</v>
+      </c>
+      <c r="AP191" t="s">
         <v>1038</v>
-      </c>
-      <c r="AP191" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="192" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B192" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C192" t="s">
         <v>47</v>
@@ -19212,10 +19209,10 @@
         <v>48</v>
       </c>
       <c r="AD192" t="s">
+        <v>1040</v>
+      </c>
+      <c r="AH192" t="s">
         <v>1041</v>
-      </c>
-      <c r="AH192" t="s">
-        <v>1042</v>
       </c>
       <c r="AL192">
         <v>-128</v>
@@ -19224,21 +19221,21 @@
         <v>54</v>
       </c>
       <c r="AO192" t="s">
+        <v>1042</v>
+      </c>
+      <c r="AP192" t="s">
         <v>1043</v>
       </c>
-      <c r="AP192" t="s">
+      <c r="AS192" t="s">
         <v>1044</v>
       </c>
-      <c r="AS192" t="s">
+    </row>
+    <row r="193" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
         <v>1045</v>
       </c>
-    </row>
-    <row r="193" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
+      <c r="B193" t="s">
         <v>1046</v>
-      </c>
-      <c r="B193" t="s">
-        <v>1047</v>
       </c>
       <c r="C193" t="s">
         <v>47</v>
@@ -19277,7 +19274,7 @@
         <v>48</v>
       </c>
       <c r="AD193" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="AE193">
         <v>117</v>
@@ -19298,18 +19295,18 @@
         <v>54</v>
       </c>
       <c r="AO193" t="s">
+        <v>1048</v>
+      </c>
+      <c r="AP193" t="s">
         <v>1049</v>
       </c>
-      <c r="AP193" t="s">
+    </row>
+    <row r="194" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B194" t="s">
         <v>1050</v>
-      </c>
-    </row>
-    <row r="194" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
-        <v>1046</v>
-      </c>
-      <c r="B194" t="s">
-        <v>1051</v>
       </c>
       <c r="C194" t="s">
         <v>192</v>
@@ -19351,7 +19348,7 @@
         <v>48</v>
       </c>
       <c r="AD194" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="AE194">
         <v>113</v>
@@ -19366,21 +19363,21 @@
         <v>177</v>
       </c>
       <c r="AN194" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AO194" t="s">
         <v>1053</v>
       </c>
-      <c r="AO194" t="s">
+      <c r="AP194" t="s">
         <v>1054</v>
-      </c>
-      <c r="AP194" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="195" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B195" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="C195" t="s">
         <v>166</v>
@@ -19422,7 +19419,7 @@
         <v>32</v>
       </c>
       <c r="Y195" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="Z195" t="s">
         <v>48</v>
@@ -19437,10 +19434,10 @@
         <v>48</v>
       </c>
       <c r="AD195" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="AG195" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AK195">
         <v>-130.5</v>
@@ -19449,24 +19446,24 @@
         <v>54</v>
       </c>
       <c r="AN195" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="AO195" t="s">
+        <v>1058</v>
+      </c>
+      <c r="AP195" t="s">
         <v>1059</v>
       </c>
-      <c r="AP195" t="s">
+      <c r="AS195" t="s">
         <v>1060</v>
       </c>
-      <c r="AS195" t="s">
+    </row>
+    <row r="196" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B196" t="s">
         <v>1061</v>
-      </c>
-    </row>
-    <row r="196" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>1046</v>
-      </c>
-      <c r="B196" t="s">
-        <v>1062</v>
       </c>
       <c r="C196" t="s">
         <v>131</v>
@@ -19532,7 +19529,7 @@
         <v>49</v>
       </c>
       <c r="Z196" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AA196" t="s">
         <v>48</v>
@@ -19562,21 +19559,21 @@
         <v>54</v>
       </c>
       <c r="AN196" t="s">
+        <v>1062</v>
+      </c>
+      <c r="AO196" t="s">
         <v>1063</v>
       </c>
-      <c r="AO196" t="s">
+      <c r="AP196" t="s">
         <v>1064</v>
-      </c>
-      <c r="AP196" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="197" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B197" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="C197" t="s">
         <v>166</v>
@@ -19618,7 +19615,7 @@
         <v>48</v>
       </c>
       <c r="AD197" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="AE197">
         <v>116.5</v>
@@ -19633,24 +19630,24 @@
         <v>54</v>
       </c>
       <c r="AN197" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="AO197" t="s">
+        <v>1067</v>
+      </c>
+      <c r="AP197" t="s">
         <v>1068</v>
       </c>
-      <c r="AP197" t="s">
+      <c r="AS197" t="s">
         <v>1069</v>
       </c>
-      <c r="AS197" t="s">
+    </row>
+    <row r="198" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B198" t="s">
         <v>1070</v>
-      </c>
-    </row>
-    <row r="198" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
-        <v>1046</v>
-      </c>
-      <c r="B198" t="s">
-        <v>1071</v>
       </c>
       <c r="C198" t="s">
         <v>166</v>
@@ -19698,7 +19695,7 @@
         <v>48</v>
       </c>
       <c r="AD198" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="AE198">
         <v>116.5</v>
@@ -19719,21 +19716,21 @@
         <v>54</v>
       </c>
       <c r="AN198" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="AO198" t="s">
+        <v>1071</v>
+      </c>
+      <c r="AP198" t="s">
         <v>1072</v>
       </c>
-      <c r="AP198" t="s">
+    </row>
+    <row r="199" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B199" t="s">
         <v>1073</v>
-      </c>
-    </row>
-    <row r="199" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>1046</v>
-      </c>
-      <c r="B199" t="s">
-        <v>1074</v>
       </c>
       <c r="C199" t="s">
         <v>131</v>
@@ -19754,18 +19751,18 @@
         <v>54</v>
       </c>
       <c r="AO199" t="s">
+        <v>1074</v>
+      </c>
+      <c r="AP199" t="s">
         <v>1075</v>
       </c>
-      <c r="AP199" t="s">
+    </row>
+    <row r="200" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
         <v>1076</v>
       </c>
-    </row>
-    <row r="200" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
+      <c r="B200" t="s">
         <v>1077</v>
-      </c>
-      <c r="B200" t="s">
-        <v>1078</v>
       </c>
       <c r="C200" t="s">
         <v>271</v>
@@ -19816,30 +19813,30 @@
         <v>66.5</v>
       </c>
       <c r="AH200" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="AL200" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AM200" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AN200" t="s">
+        <v>1078</v>
+      </c>
+      <c r="AO200" t="s">
         <v>1079</v>
       </c>
-      <c r="AO200" t="s">
+      <c r="AP200" t="s">
         <v>1080</v>
       </c>
-      <c r="AP200" t="s">
+    </row>
+    <row r="201" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B201" t="s">
         <v>1081</v>
-      </c>
-    </row>
-    <row r="201" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
-        <v>1077</v>
-      </c>
-      <c r="B201" t="s">
-        <v>1082</v>
       </c>
       <c r="C201" t="s">
         <v>47</v>
@@ -19881,22 +19878,22 @@
         <v>49</v>
       </c>
       <c r="Z201" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AA201" t="s">
         <v>48</v>
       </c>
       <c r="AB201" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AC201" t="s">
         <v>48</v>
       </c>
       <c r="AD201" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AG201" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AH201" t="s">
         <v>313</v>
@@ -19908,18 +19905,18 @@
         <v>54</v>
       </c>
       <c r="AO201" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AP201" t="s">
         <v>1084</v>
       </c>
-      <c r="AP201" t="s">
+    </row>
+    <row r="202" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B202" t="s">
         <v>1085</v>
-      </c>
-    </row>
-    <row r="202" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
-        <v>1077</v>
-      </c>
-      <c r="B202" t="s">
-        <v>1086</v>
       </c>
       <c r="C202" t="s">
         <v>47</v>
@@ -19961,36 +19958,36 @@
         <v>48</v>
       </c>
       <c r="AB202" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="AC202" t="s">
         <v>48</v>
       </c>
       <c r="AD202" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AH202" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="AL202" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AM202" t="s">
         <v>54</v>
       </c>
       <c r="AO202" t="s">
+        <v>1087</v>
+      </c>
+      <c r="AP202" t="s">
         <v>1088</v>
       </c>
-      <c r="AP202" t="s">
+    </row>
+    <row r="203" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B203" t="s">
         <v>1089</v>
-      </c>
-    </row>
-    <row r="203" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
-        <v>1077</v>
-      </c>
-      <c r="B203" t="s">
-        <v>1090</v>
       </c>
       <c r="C203" t="s">
         <v>47</v>
@@ -20011,7 +20008,7 @@
         <v>2</v>
       </c>
       <c r="O203" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="P203">
         <v>1</v>
@@ -20035,10 +20032,10 @@
         <v>48</v>
       </c>
       <c r="AD203" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AH203" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="AL203" t="s">
         <v>162</v>
@@ -20047,18 +20044,18 @@
         <v>54</v>
       </c>
       <c r="AO203" t="s">
+        <v>1091</v>
+      </c>
+      <c r="AP203" t="s">
         <v>1092</v>
       </c>
-      <c r="AP203" t="s">
+    </row>
+    <row r="204" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B204" t="s">
         <v>1093</v>
-      </c>
-    </row>
-    <row r="204" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
-        <v>1077</v>
-      </c>
-      <c r="B204" t="s">
-        <v>1094</v>
       </c>
       <c r="C204" t="s">
         <v>47</v>
@@ -20109,10 +20106,10 @@
         <v>48</v>
       </c>
       <c r="AD204" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AH204" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="AK204">
         <v>-128</v>
@@ -20121,18 +20118,18 @@
         <v>186</v>
       </c>
       <c r="AO204" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AP204" t="s">
         <v>1096</v>
       </c>
-      <c r="AP204" t="s">
+    </row>
+    <row r="205" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B205" t="s">
         <v>1097</v>
-      </c>
-    </row>
-    <row r="205" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
-        <v>1077</v>
-      </c>
-      <c r="B205" t="s">
-        <v>1098</v>
       </c>
       <c r="C205" t="s">
         <v>154</v>
@@ -20165,27 +20162,27 @@
         <v>48</v>
       </c>
       <c r="AG205" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AJ205" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="AM205" t="s">
         <v>186</v>
       </c>
       <c r="AO205" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AP205" t="s">
         <v>1099</v>
       </c>
-      <c r="AP205" t="s">
+    </row>
+    <row r="206" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B206" t="s">
         <v>1100</v>
-      </c>
-    </row>
-    <row r="206" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
-        <v>1077</v>
-      </c>
-      <c r="B206" t="s">
-        <v>1101</v>
       </c>
       <c r="C206" t="s">
         <v>166</v>
@@ -20233,7 +20230,7 @@
         <v>56</v>
       </c>
       <c r="AJ206" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AK206">
         <v>-125</v>
@@ -20242,18 +20239,18 @@
         <v>177</v>
       </c>
       <c r="AO206" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AP206" t="s">
         <v>1102</v>
-      </c>
-      <c r="AP206" t="s">
-        <v>1103</v>
       </c>
     </row>
     <row r="207" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B207" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C207" t="s">
         <v>192</v>
@@ -20301,10 +20298,10 @@
         <v>258</v>
       </c>
       <c r="AH207" t="s">
+        <v>1104</v>
+      </c>
+      <c r="AI207" t="s">
         <v>1105</v>
-      </c>
-      <c r="AI207" t="s">
-        <v>1106</v>
       </c>
       <c r="AL207" t="s">
         <v>162</v>
@@ -20313,24 +20310,24 @@
         <v>177</v>
       </c>
       <c r="AN207" t="s">
+        <v>1106</v>
+      </c>
+      <c r="AO207" t="s">
         <v>1107</v>
       </c>
-      <c r="AO207" t="s">
+      <c r="AP207" t="s">
         <v>1108</v>
       </c>
-      <c r="AP207" t="s">
+      <c r="AS207" t="s">
         <v>1109</v>
       </c>
-      <c r="AS207" t="s">
+    </row>
+    <row r="208" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B208" t="s">
         <v>1110</v>
-      </c>
-    </row>
-    <row r="208" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
-        <v>1077</v>
-      </c>
-      <c r="B208" t="s">
-        <v>1111</v>
       </c>
       <c r="C208" t="s">
         <v>192</v>
@@ -20387,10 +20384,10 @@
         <v>52</v>
       </c>
       <c r="AH208" t="s">
+        <v>1104</v>
+      </c>
+      <c r="AI208" t="s">
         <v>1105</v>
-      </c>
-      <c r="AI208" t="s">
-        <v>1106</v>
       </c>
       <c r="AL208" t="s">
         <v>162</v>
@@ -20399,21 +20396,21 @@
         <v>54</v>
       </c>
       <c r="AN208" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="AO208" t="s">
+        <v>1111</v>
+      </c>
+      <c r="AP208" t="s">
         <v>1112</v>
       </c>
-      <c r="AP208" t="s">
+    </row>
+    <row r="209" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
         <v>1113</v>
       </c>
-    </row>
-    <row r="209" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
+      <c r="B209" t="s">
         <v>1114</v>
-      </c>
-      <c r="B209" t="s">
-        <v>1115</v>
       </c>
       <c r="C209" t="s">
         <v>166</v>
@@ -20449,13 +20446,13 @@
         <v>119</v>
       </c>
       <c r="AB209" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="AC209" t="s">
         <v>48</v>
       </c>
       <c r="AD209" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AF209">
         <v>115</v>
@@ -20470,24 +20467,24 @@
         <v>143</v>
       </c>
       <c r="AM209" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AN209" t="s">
         <v>1117</v>
       </c>
-      <c r="AN209" t="s">
+      <c r="AO209" t="s">
         <v>1118</v>
       </c>
-      <c r="AO209" t="s">
+      <c r="AP209" t="s">
         <v>1119</v>
       </c>
-      <c r="AP209" t="s">
+    </row>
+    <row r="210" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B210" t="s">
         <v>1120</v>
-      </c>
-    </row>
-    <row r="210" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B210" t="s">
-        <v>1121</v>
       </c>
       <c r="C210" t="s">
         <v>118</v>
@@ -20529,22 +20526,22 @@
         <v>24</v>
       </c>
       <c r="Y210" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AA210" t="s">
         <v>48</v>
       </c>
       <c r="AB210" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="AC210" t="s">
         <v>48</v>
       </c>
       <c r="AD210" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AE210" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AF210">
         <v>129</v>
@@ -20553,27 +20550,27 @@
         <v>144</v>
       </c>
       <c r="AJ210" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AM210" t="s">
         <v>54</v>
       </c>
       <c r="AN210" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AO210" t="s">
         <v>1122</v>
       </c>
-      <c r="AO210" t="s">
+      <c r="AP210" t="s">
         <v>1123</v>
       </c>
-      <c r="AP210" t="s">
+    </row>
+    <row r="211" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B211" t="s">
         <v>1124</v>
-      </c>
-    </row>
-    <row r="211" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B211" t="s">
-        <v>1125</v>
       </c>
       <c r="C211" t="s">
         <v>118</v>
@@ -20615,22 +20612,22 @@
         <v>24</v>
       </c>
       <c r="Y211" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AA211" t="s">
         <v>48</v>
       </c>
       <c r="AB211" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="AC211" t="s">
         <v>48</v>
       </c>
       <c r="AD211" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AE211" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AF211">
         <v>129</v>
@@ -20639,27 +20636,27 @@
         <v>144</v>
       </c>
       <c r="AJ211" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AM211" t="s">
         <v>54</v>
       </c>
       <c r="AN211" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="AO211" t="s">
+        <v>1125</v>
+      </c>
+      <c r="AP211" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="212" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B212" t="s">
         <v>1126</v>
-      </c>
-      <c r="AP211" t="s">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="212" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B212" t="s">
-        <v>1127</v>
       </c>
       <c r="C212" t="s">
         <v>131</v>
@@ -20689,10 +20686,10 @@
         <v>24</v>
       </c>
       <c r="Y212" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AB212" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="AC212" t="s">
         <v>48</v>
@@ -20710,21 +20707,21 @@
         <v>54</v>
       </c>
       <c r="AN212" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AO212" t="s">
         <v>1128</v>
       </c>
-      <c r="AO212" t="s">
+      <c r="AP212" t="s">
         <v>1129</v>
-      </c>
-      <c r="AP212" t="s">
-        <v>1130</v>
       </c>
     </row>
     <row r="213" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B213" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="C213" t="s">
         <v>131</v>
@@ -20733,7 +20730,7 @@
         <v>4999</v>
       </c>
       <c r="E213" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="M213">
         <v>1</v>
@@ -20751,10 +20748,10 @@
         <v>24</v>
       </c>
       <c r="Y213" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="AB213" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="AC213" t="s">
         <v>48</v>
@@ -20769,24 +20766,24 @@
         <v>54</v>
       </c>
       <c r="AN213" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="AO213" t="s">
+        <v>1132</v>
+      </c>
+      <c r="AP213" t="s">
         <v>1133</v>
       </c>
-      <c r="AP213" t="s">
+      <c r="AS213" t="s">
         <v>1134</v>
       </c>
-      <c r="AS213" t="s">
+    </row>
+    <row r="214" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B214" t="s">
         <v>1135</v>
-      </c>
-    </row>
-    <row r="214" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B214" t="s">
-        <v>1136</v>
       </c>
       <c r="C214" t="s">
         <v>118</v>
@@ -20840,42 +20837,42 @@
         <v>24</v>
       </c>
       <c r="Y214" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AB214" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="AC214" t="s">
         <v>48</v>
       </c>
       <c r="AD214" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AF214">
         <v>129</v>
       </c>
       <c r="AI214" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="AM214" t="s">
         <v>54</v>
       </c>
       <c r="AN214" t="s">
+        <v>1137</v>
+      </c>
+      <c r="AO214" t="s">
         <v>1138</v>
       </c>
-      <c r="AO214" t="s">
+      <c r="AP214" t="s">
         <v>1139</v>
       </c>
-      <c r="AP214" t="s">
+    </row>
+    <row r="215" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B215" t="s">
         <v>1140</v>
-      </c>
-    </row>
-    <row r="215" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B215" t="s">
-        <v>1141</v>
       </c>
       <c r="C215" t="s">
         <v>118</v>
@@ -20932,19 +20929,19 @@
         <v>24</v>
       </c>
       <c r="Y215" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AB215" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="AC215" t="s">
         <v>48</v>
       </c>
       <c r="AD215" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AE215" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AF215">
         <v>130</v>
@@ -20953,27 +20950,27 @@
         <v>144</v>
       </c>
       <c r="AI215" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="AM215" t="s">
         <v>54</v>
       </c>
       <c r="AN215" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="AO215" t="s">
+        <v>1141</v>
+      </c>
+      <c r="AP215" t="s">
         <v>1142</v>
       </c>
-      <c r="AP215" t="s">
+    </row>
+    <row r="216" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B216" t="s">
         <v>1143</v>
-      </c>
-    </row>
-    <row r="216" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B216" t="s">
-        <v>1144</v>
       </c>
       <c r="C216" t="s">
         <v>131</v>
@@ -21027,19 +21024,19 @@
         <v>24</v>
       </c>
       <c r="Y216" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AB216" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="AC216" t="s">
         <v>48</v>
       </c>
       <c r="AD216" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AE216" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AF216">
         <v>130</v>
@@ -21048,27 +21045,27 @@
         <v>144</v>
       </c>
       <c r="AI216" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="AM216" t="s">
         <v>54</v>
       </c>
       <c r="AN216" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="AO216" t="s">
+        <v>1144</v>
+      </c>
+      <c r="AP216" t="s">
         <v>1145</v>
       </c>
-      <c r="AP216" t="s">
+    </row>
+    <row r="217" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B217" t="s">
         <v>1146</v>
-      </c>
-    </row>
-    <row r="217" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B217" t="s">
-        <v>1147</v>
       </c>
       <c r="C217" t="s">
         <v>131</v>
@@ -21080,7 +21077,7 @@
         <v>8</v>
       </c>
       <c r="F217" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G217">
         <v>8</v>
@@ -21125,19 +21122,19 @@
         <v>24</v>
       </c>
       <c r="Y217" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AB217" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="AC217" t="s">
         <v>48</v>
       </c>
       <c r="AD217" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AE217" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AF217">
         <v>130</v>
@@ -21146,27 +21143,27 @@
         <v>144</v>
       </c>
       <c r="AI217" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="AM217" t="s">
         <v>54</v>
       </c>
       <c r="AN217" t="s">
+        <v>1147</v>
+      </c>
+      <c r="AO217" t="s">
         <v>1148</v>
       </c>
-      <c r="AO217" t="s">
+      <c r="AP217" t="s">
         <v>1149</v>
       </c>
-      <c r="AP217" t="s">
+    </row>
+    <row r="218" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B218" t="s">
         <v>1150</v>
-      </c>
-    </row>
-    <row r="218" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B218" t="s">
-        <v>1151</v>
       </c>
       <c r="C218" t="s">
         <v>192</v>
@@ -21199,7 +21196,7 @@
         <v>49</v>
       </c>
       <c r="Z218" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AA218" t="s">
         <v>48</v>
@@ -21214,33 +21211,33 @@
         <v>95</v>
       </c>
       <c r="AH218" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AI218" t="s">
         <v>1152</v>
       </c>
-      <c r="AI218" t="s">
-        <v>1153</v>
-      </c>
       <c r="AK218" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AM218" t="s">
         <v>54</v>
       </c>
       <c r="AN218" t="s">
+        <v>1153</v>
+      </c>
+      <c r="AO218" t="s">
         <v>1154</v>
       </c>
-      <c r="AO218" t="s">
+      <c r="AP218" t="s">
         <v>1155</v>
       </c>
-      <c r="AP218" t="s">
+    </row>
+    <row r="219" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B219" t="s">
         <v>1156</v>
-      </c>
-    </row>
-    <row r="219" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B219" t="s">
-        <v>1157</v>
       </c>
       <c r="C219" t="s">
         <v>166</v>
@@ -21294,33 +21291,33 @@
         <v>52</v>
       </c>
       <c r="AH219" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AI219" t="s">
         <v>1152</v>
       </c>
-      <c r="AI219" t="s">
-        <v>1153</v>
-      </c>
       <c r="AK219" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AM219" t="s">
         <v>177</v>
       </c>
       <c r="AN219" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="AO219" t="s">
+        <v>1157</v>
+      </c>
+      <c r="AP219" t="s">
         <v>1158</v>
       </c>
-      <c r="AP219" t="s">
+    </row>
+    <row r="220" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B220" t="s">
         <v>1159</v>
-      </c>
-    </row>
-    <row r="220" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B220" t="s">
-        <v>1160</v>
       </c>
       <c r="C220" t="s">
         <v>192</v>
@@ -21374,33 +21371,33 @@
         <v>110</v>
       </c>
       <c r="AH220" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="AI220" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="AK220" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AM220" t="s">
         <v>177</v>
       </c>
       <c r="AN220" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="AO220" t="s">
+        <v>1161</v>
+      </c>
+      <c r="AP220" t="s">
         <v>1162</v>
-      </c>
-      <c r="AP220" t="s">
-        <v>1163</v>
       </c>
     </row>
     <row r="221" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B221" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="C221" t="s">
         <v>166</v>
@@ -21451,36 +21448,36 @@
         <v>52</v>
       </c>
       <c r="AH221" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AI221" t="s">
         <v>1152</v>
       </c>
-      <c r="AI221" t="s">
-        <v>1153</v>
-      </c>
       <c r="AK221" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AM221" t="s">
         <v>177</v>
       </c>
       <c r="AN221" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="AO221" t="s">
+        <v>1164</v>
+      </c>
+      <c r="AP221" t="s">
         <v>1165</v>
       </c>
-      <c r="AP221" t="s">
+      <c r="AS221" t="s">
         <v>1166</v>
       </c>
-      <c r="AS221" t="s">
+    </row>
+    <row r="222" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B222" t="s">
         <v>1167</v>
-      </c>
-    </row>
-    <row r="222" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B222" t="s">
-        <v>1168</v>
       </c>
       <c r="C222" t="s">
         <v>166</v>
@@ -21537,33 +21534,33 @@
         <v>52</v>
       </c>
       <c r="AH222" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AI222" t="s">
         <v>1152</v>
       </c>
-      <c r="AI222" t="s">
-        <v>1153</v>
-      </c>
       <c r="AK222" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AM222" t="s">
         <v>177</v>
       </c>
       <c r="AN222" t="s">
+        <v>1168</v>
+      </c>
+      <c r="AO222" t="s">
         <v>1169</v>
       </c>
-      <c r="AO222" t="s">
+      <c r="AP222" t="s">
         <v>1170</v>
       </c>
-      <c r="AP222" t="s">
+    </row>
+    <row r="223" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B223" t="s">
         <v>1171</v>
-      </c>
-    </row>
-    <row r="223" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B223" t="s">
-        <v>1172</v>
       </c>
       <c r="C223" t="s">
         <v>166</v>
@@ -21626,33 +21623,33 @@
         <v>52</v>
       </c>
       <c r="AH223" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AI223" t="s">
         <v>1152</v>
       </c>
-      <c r="AI223" t="s">
-        <v>1153</v>
-      </c>
       <c r="AK223" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AM223" t="s">
         <v>54</v>
       </c>
       <c r="AN223" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="AO223" t="s">
         <v>277</v>
       </c>
       <c r="AP223" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="224" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B224" t="s">
         <v>1173</v>
-      </c>
-    </row>
-    <row r="224" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B224" t="s">
-        <v>1174</v>
       </c>
       <c r="C224" t="s">
         <v>166</v>
@@ -21706,30 +21703,30 @@
         <v>110</v>
       </c>
       <c r="AH224" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AI224" t="s">
         <v>1152</v>
       </c>
-      <c r="AI224" t="s">
-        <v>1153</v>
-      </c>
       <c r="AK224" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AM224" t="s">
         <v>177</v>
       </c>
       <c r="AO224" t="s">
+        <v>1174</v>
+      </c>
+      <c r="AP224" t="s">
         <v>1175</v>
       </c>
-      <c r="AP224" t="s">
+    </row>
+    <row r="225" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B225" t="s">
         <v>1176</v>
-      </c>
-    </row>
-    <row r="225" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B225" t="s">
-        <v>1177</v>
       </c>
       <c r="C225" t="s">
         <v>154</v>
@@ -21774,7 +21771,7 @@
         <v>137</v>
       </c>
       <c r="V225" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="W225">
         <v>192</v>
@@ -21807,30 +21804,30 @@
         <v>119</v>
       </c>
       <c r="AH225" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AI225" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="AM225" t="s">
         <v>186</v>
       </c>
       <c r="AN225" t="s">
+        <v>1178</v>
+      </c>
+      <c r="AO225" t="s">
         <v>1179</v>
       </c>
-      <c r="AO225" t="s">
+      <c r="AP225" t="s">
         <v>1180</v>
       </c>
-      <c r="AP225" t="s">
+    </row>
+    <row r="226" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
         <v>1181</v>
       </c>
-    </row>
-    <row r="226" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
+      <c r="B226" t="s">
         <v>1182</v>
-      </c>
-      <c r="B226" t="s">
-        <v>1183</v>
       </c>
       <c r="C226" t="s">
         <v>271</v>
@@ -21881,21 +21878,21 @@
         <v>177</v>
       </c>
       <c r="AN226" t="s">
+        <v>1183</v>
+      </c>
+      <c r="AO226" t="s">
         <v>1184</v>
       </c>
-      <c r="AO226" t="s">
+      <c r="AP226" t="s">
         <v>1185</v>
       </c>
-      <c r="AP226" t="s">
+    </row>
+    <row r="227" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B227" t="s">
         <v>1186</v>
-      </c>
-    </row>
-    <row r="227" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A227" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B227" t="s">
-        <v>1187</v>
       </c>
       <c r="C227" t="s">
         <v>271</v>
@@ -21946,21 +21943,21 @@
         <v>177</v>
       </c>
       <c r="AN227" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="AO227" t="s">
+        <v>1187</v>
+      </c>
+      <c r="AP227" t="s">
         <v>1188</v>
       </c>
-      <c r="AP227" t="s">
+    </row>
+    <row r="228" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B228" t="s">
         <v>1189</v>
-      </c>
-    </row>
-    <row r="228" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B228" t="s">
-        <v>1190</v>
       </c>
       <c r="C228" t="s">
         <v>271</v>
@@ -22011,21 +22008,21 @@
         <v>177</v>
       </c>
       <c r="AN228" t="s">
+        <v>1190</v>
+      </c>
+      <c r="AO228" t="s">
         <v>1191</v>
       </c>
-      <c r="AO228" t="s">
+      <c r="AP228" t="s">
         <v>1192</v>
       </c>
-      <c r="AP228" t="s">
+    </row>
+    <row r="229" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B229" t="s">
         <v>1193</v>
-      </c>
-    </row>
-    <row r="229" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A229" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B229" t="s">
-        <v>1194</v>
       </c>
       <c r="C229" t="s">
         <v>47</v>
@@ -22034,13 +22031,13 @@
         <v>326</v>
       </c>
       <c r="F229" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="N229" t="s">
         <v>63</v>
       </c>
       <c r="O229" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="P229" t="s">
         <v>137</v>
@@ -22049,10 +22046,10 @@
         <v>48</v>
       </c>
       <c r="W229" t="s">
+        <v>1195</v>
+      </c>
+      <c r="X229" t="s">
         <v>1196</v>
-      </c>
-      <c r="X229" t="s">
-        <v>1197</v>
       </c>
       <c r="Y229" t="s">
         <v>49</v>
@@ -22064,39 +22061,39 @@
         <v>70</v>
       </c>
       <c r="AD229" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="AF229" t="s">
         <v>52</v>
       </c>
       <c r="AG229" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AJ229" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="AL229" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AM229" t="s">
         <v>54</v>
       </c>
       <c r="AN229" t="s">
+        <v>1197</v>
+      </c>
+      <c r="AO229" t="s">
         <v>1198</v>
       </c>
-      <c r="AO229" t="s">
+      <c r="AP229" t="s">
         <v>1199</v>
       </c>
-      <c r="AP229" t="s">
+    </row>
+    <row r="230" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B230" t="s">
         <v>1200</v>
-      </c>
-    </row>
-    <row r="230" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A230" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B230" t="s">
-        <v>1201</v>
       </c>
       <c r="C230" t="s">
         <v>47</v>
@@ -22141,21 +22138,21 @@
         <v>54</v>
       </c>
       <c r="AN230" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="AO230" t="s">
+        <v>1201</v>
+      </c>
+      <c r="AP230" t="s">
         <v>1202</v>
       </c>
-      <c r="AP230" t="s">
+    </row>
+    <row r="231" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B231" t="s">
         <v>1203</v>
-      </c>
-    </row>
-    <row r="231" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A231" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B231" t="s">
-        <v>1204</v>
       </c>
       <c r="C231" t="s">
         <v>47</v>
@@ -22200,7 +22197,7 @@
         <v>48</v>
       </c>
       <c r="AJ231" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AL231" t="s">
         <v>162</v>
@@ -22209,18 +22206,18 @@
         <v>54</v>
       </c>
       <c r="AO231" t="s">
+        <v>1204</v>
+      </c>
+      <c r="AP231" t="s">
         <v>1205</v>
       </c>
-      <c r="AP231" t="s">
+    </row>
+    <row r="232" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B232" t="s">
         <v>1206</v>
-      </c>
-    </row>
-    <row r="232" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A232" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B232" t="s">
-        <v>1207</v>
       </c>
       <c r="C232" t="s">
         <v>47</v>
@@ -22271,21 +22268,21 @@
         <v>54</v>
       </c>
       <c r="AN232" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="AO232" t="s">
+        <v>1207</v>
+      </c>
+      <c r="AP232" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="233" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B233" t="s">
         <v>1208</v>
-      </c>
-      <c r="AP232" t="s">
-        <v>1206</v>
-      </c>
-    </row>
-    <row r="233" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B233" t="s">
-        <v>1209</v>
       </c>
       <c r="C233" t="s">
         <v>47</v>
@@ -22330,7 +22327,7 @@
         <v>48</v>
       </c>
       <c r="AJ233" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AL233" t="s">
         <v>162</v>
@@ -22339,18 +22336,18 @@
         <v>54</v>
       </c>
       <c r="AO233" t="s">
+        <v>1209</v>
+      </c>
+      <c r="AP233" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="234" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B234" t="s">
         <v>1210</v>
-      </c>
-      <c r="AP233" t="s">
-        <v>1206</v>
-      </c>
-    </row>
-    <row r="234" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B234" t="s">
-        <v>1211</v>
       </c>
       <c r="C234" t="s">
         <v>47</v>
@@ -22398,10 +22395,10 @@
         <v>48</v>
       </c>
       <c r="AD234" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="AG234" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="AJ234" t="s">
         <v>53</v>
@@ -22413,21 +22410,21 @@
         <v>54</v>
       </c>
       <c r="AN234" t="s">
+        <v>1212</v>
+      </c>
+      <c r="AO234" t="s">
         <v>1213</v>
       </c>
-      <c r="AO234" t="s">
+      <c r="AP234" t="s">
         <v>1214</v>
       </c>
-      <c r="AP234" t="s">
+    </row>
+    <row r="235" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B235" t="s">
         <v>1215</v>
-      </c>
-    </row>
-    <row r="235" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A235" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B235" t="s">
-        <v>1216</v>
       </c>
       <c r="C235" t="s">
         <v>47</v>
@@ -22475,10 +22472,10 @@
         <v>48</v>
       </c>
       <c r="AD235" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="AF235" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="AJ235" t="s">
         <v>53</v>
@@ -22490,18 +22487,18 @@
         <v>54</v>
       </c>
       <c r="AO235" t="s">
+        <v>1216</v>
+      </c>
+      <c r="AP235" t="s">
         <v>1217</v>
       </c>
-      <c r="AP235" t="s">
+    </row>
+    <row r="236" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B236" t="s">
         <v>1218</v>
-      </c>
-    </row>
-    <row r="236" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B236" t="s">
-        <v>1219</v>
       </c>
       <c r="C236" t="s">
         <v>47</v>
@@ -22549,10 +22546,10 @@
         <v>48</v>
       </c>
       <c r="AD236" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="AG236" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="AJ236" t="s">
         <v>53</v>
@@ -22564,18 +22561,18 @@
         <v>54</v>
       </c>
       <c r="AO236" t="s">
+        <v>1219</v>
+      </c>
+      <c r="AP236" t="s">
         <v>1220</v>
       </c>
-      <c r="AP236" t="s">
+    </row>
+    <row r="237" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B237" t="s">
         <v>1221</v>
-      </c>
-    </row>
-    <row r="237" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A237" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B237" t="s">
-        <v>1222</v>
       </c>
       <c r="C237" t="s">
         <v>47</v>
@@ -22623,10 +22620,10 @@
         <v>48</v>
       </c>
       <c r="AD237" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="AF237" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="AJ237" t="s">
         <v>53</v>
@@ -22638,21 +22635,21 @@
         <v>54</v>
       </c>
       <c r="AN237" t="s">
+        <v>1222</v>
+      </c>
+      <c r="AO237" t="s">
         <v>1223</v>
       </c>
-      <c r="AO237" t="s">
+      <c r="AP237" t="s">
         <v>1224</v>
       </c>
-      <c r="AP237" t="s">
+    </row>
+    <row r="238" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B238" t="s">
         <v>1225</v>
-      </c>
-    </row>
-    <row r="238" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A238" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B238" t="s">
-        <v>1226</v>
       </c>
       <c r="C238" t="s">
         <v>118</v>
@@ -22682,7 +22679,7 @@
         <v>24</v>
       </c>
       <c r="Y238" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="AF238" t="s">
         <v>252</v>
@@ -22694,21 +22691,21 @@
         <v>54</v>
       </c>
       <c r="AN238" t="s">
+        <v>1227</v>
+      </c>
+      <c r="AO238" t="s">
         <v>1228</v>
       </c>
-      <c r="AO238" t="s">
+      <c r="AP238" t="s">
         <v>1229</v>
       </c>
-      <c r="AP238" t="s">
+    </row>
+    <row r="239" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B239" t="s">
         <v>1230</v>
-      </c>
-    </row>
-    <row r="239" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A239" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B239" t="s">
-        <v>1231</v>
       </c>
       <c r="C239" t="s">
         <v>192</v>
@@ -22771,21 +22768,21 @@
         <v>54</v>
       </c>
       <c r="AN239" t="s">
+        <v>1231</v>
+      </c>
+      <c r="AO239" t="s">
         <v>1232</v>
       </c>
-      <c r="AO239" t="s">
+      <c r="AP239" t="s">
         <v>1233</v>
       </c>
-      <c r="AP239" t="s">
+    </row>
+    <row r="240" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B240" t="s">
         <v>1234</v>
-      </c>
-    </row>
-    <row r="240" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A240" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B240" t="s">
-        <v>1235</v>
       </c>
       <c r="C240" t="s">
         <v>192</v>
@@ -22845,21 +22842,21 @@
         <v>54</v>
       </c>
       <c r="AN240" t="s">
+        <v>1231</v>
+      </c>
+      <c r="AO240" t="s">
         <v>1232</v>
       </c>
-      <c r="AO240" t="s">
-        <v>1233</v>
-      </c>
       <c r="AP240" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="241" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="B241" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="C241" t="s">
         <v>166</v>
@@ -22892,7 +22889,7 @@
         <v>32</v>
       </c>
       <c r="Y241" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="AB241" t="s">
         <v>70</v>
@@ -22907,10 +22904,10 @@
         <v>125</v>
       </c>
       <c r="AH241" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="AI241" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="AK241" t="s">
         <v>162</v>
@@ -22919,24 +22916,24 @@
         <v>54</v>
       </c>
       <c r="AN241" t="s">
+        <v>1239</v>
+      </c>
+      <c r="AO241" t="s">
         <v>1240</v>
       </c>
-      <c r="AO241" t="s">
+      <c r="AP241" t="s">
         <v>1241</v>
       </c>
-      <c r="AP241" t="s">
+      <c r="AS241" t="s">
         <v>1242</v>
       </c>
-      <c r="AS241" t="s">
+    </row>
+    <row r="242" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B242" t="s">
         <v>1243</v>
-      </c>
-    </row>
-    <row r="242" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A242" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B242" t="s">
-        <v>1244</v>
       </c>
       <c r="C242" t="s">
         <v>166</v>
@@ -22969,7 +22966,7 @@
         <v>32</v>
       </c>
       <c r="Y242" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="Z242" t="s">
         <v>167</v>
@@ -22999,21 +22996,21 @@
         <v>54</v>
       </c>
       <c r="AN242" t="s">
+        <v>1245</v>
+      </c>
+      <c r="AO242" t="s">
         <v>1246</v>
       </c>
-      <c r="AO242" t="s">
+      <c r="AP242" t="s">
         <v>1247</v>
       </c>
-      <c r="AP242" t="s">
+    </row>
+    <row r="243" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B243" t="s">
         <v>1248</v>
-      </c>
-    </row>
-    <row r="243" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A243" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B243" t="s">
-        <v>1249</v>
       </c>
       <c r="C243" t="s">
         <v>166</v>
@@ -23046,7 +23043,7 @@
         <v>32</v>
       </c>
       <c r="Y243" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="AB243" t="s">
         <v>70</v>
@@ -23061,10 +23058,10 @@
         <v>125</v>
       </c>
       <c r="AH243" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="AI243" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="AK243" t="s">
         <v>162</v>
@@ -23073,21 +23070,21 @@
         <v>54</v>
       </c>
       <c r="AN243" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="AO243" t="s">
+        <v>1249</v>
+      </c>
+      <c r="AP243" t="s">
         <v>1250</v>
       </c>
-      <c r="AP243" t="s">
+    </row>
+    <row r="244" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B244" t="s">
         <v>1251</v>
-      </c>
-    </row>
-    <row r="244" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A244" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B244" t="s">
-        <v>1252</v>
       </c>
       <c r="C244" t="s">
         <v>166</v>
@@ -23123,7 +23120,7 @@
         <v>32</v>
       </c>
       <c r="Y244" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="Z244" t="s">
         <v>167</v>
@@ -23135,7 +23132,7 @@
         <v>70</v>
       </c>
       <c r="AC244" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="AD244">
         <v>54</v>
@@ -23156,21 +23153,21 @@
         <v>54</v>
       </c>
       <c r="AN244" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="AO244" t="s">
+        <v>1253</v>
+      </c>
+      <c r="AP244" t="s">
         <v>1254</v>
       </c>
-      <c r="AP244" t="s">
+    </row>
+    <row r="245" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B245" t="s">
         <v>1255</v>
-      </c>
-    </row>
-    <row r="245" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A245" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B245" t="s">
-        <v>1256</v>
       </c>
       <c r="C245" t="s">
         <v>154</v>
@@ -23203,7 +23200,7 @@
         <v>32</v>
       </c>
       <c r="Y245" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="AB245" t="s">
         <v>70</v>
@@ -23218,10 +23215,10 @@
         <v>125</v>
       </c>
       <c r="AH245" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="AI245" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="AK245" t="s">
         <v>162</v>
@@ -23230,21 +23227,21 @@
         <v>54</v>
       </c>
       <c r="AN245" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="AO245" t="s">
+        <v>1256</v>
+      </c>
+      <c r="AP245" t="s">
         <v>1257</v>
       </c>
-      <c r="AP245" t="s">
+    </row>
+    <row r="246" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B246" t="s">
         <v>1258</v>
-      </c>
-    </row>
-    <row r="246" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A246" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B246" t="s">
-        <v>1259</v>
       </c>
       <c r="C246" t="s">
         <v>271</v>
@@ -23295,21 +23292,21 @@
         <v>54</v>
       </c>
       <c r="AN246" t="s">
+        <v>1259</v>
+      </c>
+      <c r="AO246" t="s">
         <v>1260</v>
       </c>
-      <c r="AO246" t="s">
+      <c r="AP246" t="s">
         <v>1261</v>
       </c>
-      <c r="AP246" t="s">
+    </row>
+    <row r="247" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B247" t="s">
         <v>1262</v>
-      </c>
-    </row>
-    <row r="247" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A247" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B247" t="s">
-        <v>1263</v>
       </c>
       <c r="C247" t="s">
         <v>271</v>
@@ -23354,18 +23351,18 @@
         <v>54</v>
       </c>
       <c r="AO247" t="s">
+        <v>1263</v>
+      </c>
+      <c r="AP247" t="s">
         <v>1264</v>
-      </c>
-      <c r="AP247" t="s">
-        <v>1265</v>
       </c>
     </row>
     <row r="248" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B248" t="s">
         <v>1266</v>
-      </c>
-      <c r="B248" t="s">
-        <v>1267</v>
       </c>
       <c r="C248" t="s">
         <v>192</v>
@@ -23410,30 +23407,30 @@
         <v>48</v>
       </c>
       <c r="AD248" t="s">
+        <v>1267</v>
+      </c>
+      <c r="AK248" t="s">
         <v>1268</v>
-      </c>
-      <c r="AK248" t="s">
-        <v>1269</v>
       </c>
       <c r="AM248" t="s">
         <v>157</v>
       </c>
       <c r="AO248" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="AP248" t="s">
+        <v>1269</v>
+      </c>
+      <c r="AS248" t="s">
         <v>1270</v>
       </c>
-      <c r="AS248" t="s">
+    </row>
+    <row r="249" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B249" t="s">
         <v>1271</v>
-      </c>
-    </row>
-    <row r="249" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A249" t="s">
-        <v>1266</v>
-      </c>
-      <c r="B249" t="s">
-        <v>1272</v>
       </c>
       <c r="C249" t="s">
         <v>192</v>
@@ -23475,27 +23472,27 @@
         <v>48</v>
       </c>
       <c r="AD249" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="AK249">
         <v>-120</v>
       </c>
       <c r="AM249" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AO249" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="AP249" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="250" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="B250" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="C250" t="s">
         <v>192</v>
@@ -23537,30 +23534,30 @@
         <v>48</v>
       </c>
       <c r="AD250" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="AK250" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="AM250" t="s">
         <v>157</v>
       </c>
       <c r="AO250" t="s">
+        <v>1275</v>
+      </c>
+      <c r="AP250" t="s">
+        <v>1269</v>
+      </c>
+      <c r="AS250" t="s">
         <v>1276</v>
       </c>
-      <c r="AP250" t="s">
-        <v>1270</v>
-      </c>
-      <c r="AS250" t="s">
+    </row>
+    <row r="251" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B251" t="s">
         <v>1277</v>
-      </c>
-    </row>
-    <row r="251" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A251" t="s">
-        <v>1266</v>
-      </c>
-      <c r="B251" t="s">
-        <v>1278</v>
       </c>
       <c r="C251" t="s">
         <v>47</v>
@@ -23608,7 +23605,7 @@
         <v>70</v>
       </c>
       <c r="AD251" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="AK251" t="s">
         <v>162</v>
@@ -23617,18 +23614,18 @@
         <v>54</v>
       </c>
       <c r="AO251" t="s">
+        <v>1279</v>
+      </c>
+      <c r="AP251" t="s">
         <v>1280</v>
       </c>
-      <c r="AP251" t="s">
+    </row>
+    <row r="252" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B252" t="s">
         <v>1281</v>
-      </c>
-    </row>
-    <row r="252" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A252" t="s">
-        <v>1266</v>
-      </c>
-      <c r="B252" t="s">
-        <v>1282</v>
       </c>
       <c r="C252" t="s">
         <v>47</v>
@@ -23685,18 +23682,18 @@
         <v>177</v>
       </c>
       <c r="AO252" t="s">
+        <v>1282</v>
+      </c>
+      <c r="AP252" t="s">
         <v>1283</v>
       </c>
-      <c r="AP252" t="s">
+    </row>
+    <row r="253" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B253" t="s">
         <v>1284</v>
-      </c>
-    </row>
-    <row r="253" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A253" t="s">
-        <v>1266</v>
-      </c>
-      <c r="B253" t="s">
-        <v>1285</v>
       </c>
       <c r="C253" t="s">
         <v>47</v>
@@ -23744,27 +23741,27 @@
         <v>48</v>
       </c>
       <c r="AD253" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="AK253">
         <v>-128</v>
       </c>
       <c r="AM253" t="s">
+        <v>1285</v>
+      </c>
+      <c r="AO253" t="s">
         <v>1286</v>
       </c>
-      <c r="AO253" t="s">
+      <c r="AP253" t="s">
         <v>1287</v>
       </c>
-      <c r="AP253" t="s">
+    </row>
+    <row r="254" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B254" t="s">
         <v>1288</v>
-      </c>
-    </row>
-    <row r="254" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A254" t="s">
-        <v>1266</v>
-      </c>
-      <c r="B254" t="s">
-        <v>1289</v>
       </c>
       <c r="C254" t="s">
         <v>47</v>
@@ -23815,24 +23812,24 @@
         <v>48</v>
       </c>
       <c r="AK254" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="AM254" t="s">
         <v>157</v>
       </c>
       <c r="AO254" t="s">
+        <v>1289</v>
+      </c>
+      <c r="AP254" t="s">
         <v>1290</v>
       </c>
-      <c r="AP254" t="s">
+    </row>
+    <row r="255" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B255" t="s">
         <v>1291</v>
-      </c>
-    </row>
-    <row r="255" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
-        <v>1266</v>
-      </c>
-      <c r="B255" t="s">
-        <v>1292</v>
       </c>
       <c r="C255" t="s">
         <v>47</v>
@@ -23877,27 +23874,27 @@
         <v>70</v>
       </c>
       <c r="AD255" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AK255" t="s">
         <v>1293</v>
-      </c>
-      <c r="AK255" t="s">
-        <v>1294</v>
       </c>
       <c r="AM255" t="s">
         <v>186</v>
       </c>
       <c r="AO255" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AP255" t="s">
         <v>1295</v>
       </c>
-      <c r="AP255" t="s">
+    </row>
+    <row r="256" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B256" t="s">
         <v>1296</v>
-      </c>
-    </row>
-    <row r="256" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
-        <v>1266</v>
-      </c>
-      <c r="B256" t="s">
-        <v>1297</v>
       </c>
       <c r="C256" t="s">
         <v>47</v>
@@ -23942,27 +23939,27 @@
         <v>48</v>
       </c>
       <c r="AD256" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="AK256">
         <v>-128</v>
       </c>
       <c r="AM256" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="AO256" t="s">
+        <v>1297</v>
+      </c>
+      <c r="AP256" t="s">
         <v>1298</v>
       </c>
-      <c r="AP256" t="s">
+    </row>
+    <row r="257" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B257" t="s">
         <v>1299</v>
-      </c>
-    </row>
-    <row r="257" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A257" t="s">
-        <v>1266</v>
-      </c>
-      <c r="B257" t="s">
-        <v>1300</v>
       </c>
       <c r="C257" t="s">
         <v>47</v>
@@ -24013,21 +24010,21 @@
         <v>-120</v>
       </c>
       <c r="AM257" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AO257" t="s">
+        <v>1300</v>
+      </c>
+      <c r="AP257" t="s">
         <v>1301</v>
       </c>
-      <c r="AP257" t="s">
+    </row>
+    <row r="258" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B258" t="s">
         <v>1302</v>
-      </c>
-    </row>
-    <row r="258" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A258" t="s">
-        <v>1266</v>
-      </c>
-      <c r="B258" t="s">
-        <v>1303</v>
       </c>
       <c r="C258" t="s">
         <v>271</v>
@@ -24063,18 +24060,18 @@
         <v>157</v>
       </c>
       <c r="AO258" t="s">
+        <v>1303</v>
+      </c>
+      <c r="AP258" t="s">
         <v>1304</v>
       </c>
-      <c r="AP258" t="s">
+    </row>
+    <row r="259" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B259" t="s">
         <v>1305</v>
-      </c>
-    </row>
-    <row r="259" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A259" t="s">
-        <v>1266</v>
-      </c>
-      <c r="B259" t="s">
-        <v>1306</v>
       </c>
       <c r="C259" t="s">
         <v>271</v>
@@ -24107,27 +24104,27 @@
         <v>48</v>
       </c>
       <c r="AD259" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="AK259">
         <v>-125</v>
       </c>
       <c r="AM259" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AO259" t="s">
+        <v>1307</v>
+      </c>
+      <c r="AP259" t="s">
         <v>1308</v>
       </c>
-      <c r="AP259" t="s">
+    </row>
+    <row r="260" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B260" t="s">
         <v>1309</v>
-      </c>
-    </row>
-    <row r="260" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A260" t="s">
-        <v>1266</v>
-      </c>
-      <c r="B260" t="s">
-        <v>1310</v>
       </c>
       <c r="C260" t="s">
         <v>271</v>
@@ -24163,24 +24160,24 @@
         <v>70</v>
       </c>
       <c r="AK260" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="AM260" t="s">
         <v>54</v>
       </c>
       <c r="AO260" t="s">
+        <v>1311</v>
+      </c>
+      <c r="AP260" t="s">
         <v>1312</v>
-      </c>
-      <c r="AP260" t="s">
-        <v>1313</v>
       </c>
     </row>
     <row r="261" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="B261" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="C261" t="s">
         <v>192</v>
@@ -24231,13 +24228,13 @@
         <v>177</v>
       </c>
       <c r="AO261" t="s">
+        <v>1314</v>
+      </c>
+      <c r="AP261" t="s">
         <v>1315</v>
       </c>
-      <c r="AP261" t="s">
+      <c r="AS261" t="s">
         <v>1316</v>
-      </c>
-      <c r="AS261" t="s">
-        <v>1317</v>
       </c>
     </row>
   </sheetData>
@@ -24259,7 +24256,7 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -24312,7 +24309,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="B8">
         <v>216</v>

--- a/data/audio_interfaces.xlsx
+++ b/data/audio_interfaces.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3754" uniqueCount="1319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3736" uniqueCount="1315">
   <si>
     <t>Brand</t>
   </si>
@@ -1022,9 +1022,6 @@
     <t>AT-UMX3</t>
   </si>
   <si>
-    <t>192</t>
-  </si>
-  <si>
     <t>+19 to +60</t>
   </si>
   <si>
@@ -3600,15 +3597,6 @@
   </si>
   <si>
     <t>DM3</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>32</t>
   </si>
   <si>
     <t>Cubase AI, VST Rack Elements</t>
@@ -8431,7 +8419,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="51" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>332</v>
       </c>
@@ -8444,29 +8432,29 @@
       <c r="D51">
         <v>159</v>
       </c>
-      <c r="E51" t="s">
-        <v>137</v>
-      </c>
-      <c r="F51" t="s">
-        <v>137</v>
-      </c>
-      <c r="G51" t="s">
-        <v>63</v>
-      </c>
-      <c r="H51" t="s">
-        <v>137</v>
-      </c>
-      <c r="P51" t="s">
-        <v>137</v>
+      <c r="E51">
+        <v>1</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51">
+        <v>2</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+      <c r="P51">
+        <v>1</v>
       </c>
       <c r="V51" t="s">
         <v>48</v>
       </c>
-      <c r="W51" t="s">
-        <v>334</v>
-      </c>
-      <c r="X51" t="s">
-        <v>76</v>
+      <c r="W51">
+        <v>192</v>
+      </c>
+      <c r="X51">
+        <v>24</v>
       </c>
       <c r="Y51" t="s">
         <v>49</v>
@@ -8478,24 +8466,24 @@
         <v>48</v>
       </c>
       <c r="AD51" t="s">
+        <v>334</v>
+      </c>
+      <c r="AM51" t="s">
         <v>335</v>
       </c>
-      <c r="AM51" t="s">
+      <c r="AO51" t="s">
         <v>336</v>
       </c>
-      <c r="AO51" t="s">
+      <c r="AP51" t="s">
         <v>337</v>
-      </c>
-      <c r="AP51" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="52" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>338</v>
+      </c>
+      <c r="B52" t="s">
         <v>339</v>
-      </c>
-      <c r="B52" t="s">
-        <v>340</v>
       </c>
       <c r="C52" t="s">
         <v>154</v>
@@ -8594,21 +8582,21 @@
         <v>54</v>
       </c>
       <c r="AN52" t="s">
+        <v>340</v>
+      </c>
+      <c r="AO52" t="s">
         <v>341</v>
       </c>
-      <c r="AO52" t="s">
+      <c r="AP52" t="s">
         <v>342</v>
-      </c>
-      <c r="AP52" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="53" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B53" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C53" t="s">
         <v>131</v>
@@ -8659,7 +8647,7 @@
         <v>32</v>
       </c>
       <c r="Y53" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AB53" t="s">
         <v>70</v>
@@ -8674,10 +8662,10 @@
         <v>120</v>
       </c>
       <c r="AH53" t="s">
+        <v>345</v>
+      </c>
+      <c r="AI53" t="s">
         <v>346</v>
-      </c>
-      <c r="AI53" t="s">
-        <v>347</v>
       </c>
       <c r="AK53">
         <v>-129</v>
@@ -8686,21 +8674,21 @@
         <v>209</v>
       </c>
       <c r="AN53" t="s">
+        <v>347</v>
+      </c>
+      <c r="AO53" t="s">
         <v>348</v>
       </c>
-      <c r="AO53" t="s">
+      <c r="AP53" t="s">
         <v>349</v>
-      </c>
-      <c r="AP53" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="54" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B54" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C54" t="s">
         <v>131</v>
@@ -8745,7 +8733,7 @@
         <v>32</v>
       </c>
       <c r="Y54" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AE54">
         <v>126</v>
@@ -8754,10 +8742,10 @@
         <v>120</v>
       </c>
       <c r="AH54" t="s">
+        <v>345</v>
+      </c>
+      <c r="AI54" t="s">
         <v>346</v>
-      </c>
-      <c r="AI54" t="s">
-        <v>347</v>
       </c>
       <c r="AK54">
         <v>-129</v>
@@ -8766,21 +8754,21 @@
         <v>209</v>
       </c>
       <c r="AN54" t="s">
+        <v>351</v>
+      </c>
+      <c r="AO54" t="s">
         <v>352</v>
       </c>
-      <c r="AO54" t="s">
+      <c r="AP54" t="s">
         <v>353</v>
-      </c>
-      <c r="AP54" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="55" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B55" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C55" t="s">
         <v>131</v>
@@ -8798,13 +8786,13 @@
         <v>24</v>
       </c>
       <c r="Y55" t="s">
+        <v>355</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD55" t="s">
         <v>356</v>
-      </c>
-      <c r="AC55" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD55" t="s">
-        <v>357</v>
       </c>
       <c r="AE55">
         <v>126</v>
@@ -8813,7 +8801,7 @@
         <v>128</v>
       </c>
       <c r="AH55" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AI55" t="s">
         <v>184</v>
@@ -8825,18 +8813,18 @@
         <v>54</v>
       </c>
       <c r="AO55" t="s">
+        <v>358</v>
+      </c>
+      <c r="AP55" t="s">
         <v>359</v>
-      </c>
-      <c r="AP55" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="56" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C56" t="s">
         <v>131</v>
@@ -8881,10 +8869,10 @@
         <v>24</v>
       </c>
       <c r="Y56" t="s">
+        <v>361</v>
+      </c>
+      <c r="AB56" t="s">
         <v>362</v>
-      </c>
-      <c r="AB56" t="s">
-        <v>363</v>
       </c>
       <c r="AC56" t="s">
         <v>48</v>
@@ -8899,7 +8887,7 @@
         <v>128</v>
       </c>
       <c r="AH56" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AK56">
         <v>-133</v>
@@ -8908,18 +8896,18 @@
         <v>54</v>
       </c>
       <c r="AO56" t="s">
+        <v>363</v>
+      </c>
+      <c r="AP56" t="s">
         <v>364</v>
-      </c>
-      <c r="AP56" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="57" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>365</v>
+      </c>
+      <c r="B57" t="s">
         <v>366</v>
-      </c>
-      <c r="B57" t="s">
-        <v>367</v>
       </c>
       <c r="C57" t="s">
         <v>47</v>
@@ -8967,10 +8955,10 @@
         <v>48</v>
       </c>
       <c r="AD57" t="s">
+        <v>367</v>
+      </c>
+      <c r="AG57" t="s">
         <v>368</v>
-      </c>
-      <c r="AG57" t="s">
-        <v>369</v>
       </c>
       <c r="AH57" t="s">
         <v>58</v>
@@ -8979,21 +8967,21 @@
         <v>225</v>
       </c>
       <c r="AM57" t="s">
+        <v>369</v>
+      </c>
+      <c r="AO57" t="s">
         <v>370</v>
       </c>
-      <c r="AO57" t="s">
+      <c r="AP57" t="s">
         <v>371</v>
-      </c>
-      <c r="AP57" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="58" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B58" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C58" t="s">
         <v>192</v>
@@ -9026,7 +9014,7 @@
         <v>24</v>
       </c>
       <c r="Y58" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AC58" t="s">
         <v>48</v>
@@ -9038,18 +9026,18 @@
         <v>54</v>
       </c>
       <c r="AO58" t="s">
+        <v>374</v>
+      </c>
+      <c r="AP58" t="s">
         <v>375</v>
-      </c>
-      <c r="AP58" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="59" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B59" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C59" t="s">
         <v>166</v>
@@ -9115,27 +9103,27 @@
         <v>48</v>
       </c>
       <c r="AG59" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AM59" t="s">
         <v>54</v>
       </c>
       <c r="AO59" t="s">
+        <v>378</v>
+      </c>
+      <c r="AP59" t="s">
         <v>379</v>
       </c>
-      <c r="AP59" t="s">
+      <c r="AS59" t="s">
         <v>380</v>
-      </c>
-      <c r="AS59" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="60" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B60" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C60" t="s">
         <v>192</v>
@@ -9177,21 +9165,21 @@
         <v>54</v>
       </c>
       <c r="AO60" t="s">
+        <v>382</v>
+      </c>
+      <c r="AP60" t="s">
         <v>383</v>
       </c>
-      <c r="AP60" t="s">
+      <c r="AS60" t="s">
         <v>384</v>
-      </c>
-      <c r="AS60" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="61" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B61" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C61" t="s">
         <v>192</v>
@@ -9239,21 +9227,21 @@
         <v>54</v>
       </c>
       <c r="AO61" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AP61" t="s">
+        <v>386</v>
+      </c>
+      <c r="AS61" t="s">
         <v>387</v>
-      </c>
-      <c r="AS61" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="62" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B62" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C62" t="s">
         <v>192</v>
@@ -9295,21 +9283,21 @@
         <v>54</v>
       </c>
       <c r="AO62" t="s">
+        <v>389</v>
+      </c>
+      <c r="AP62" t="s">
         <v>390</v>
       </c>
-      <c r="AP62" t="s">
+      <c r="AS62" t="s">
         <v>391</v>
-      </c>
-      <c r="AS62" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="63" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B63" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C63" t="s">
         <v>192</v>
@@ -9354,21 +9342,21 @@
         <v>54</v>
       </c>
       <c r="AO63" t="s">
+        <v>393</v>
+      </c>
+      <c r="AP63" t="s">
         <v>394</v>
       </c>
-      <c r="AP63" t="s">
+      <c r="AS63" t="s">
         <v>395</v>
-      </c>
-      <c r="AS63" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="64" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B64" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C64" t="s">
         <v>47</v>
@@ -9410,7 +9398,7 @@
         <v>48</v>
       </c>
       <c r="AD64" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AH64" t="s">
         <v>107</v>
@@ -9422,18 +9410,18 @@
         <v>54</v>
       </c>
       <c r="AO64" t="s">
+        <v>398</v>
+      </c>
+      <c r="AP64" t="s">
         <v>399</v>
-      </c>
-      <c r="AP64" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="65" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B65" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C65" t="s">
         <v>47</v>
@@ -9472,7 +9460,7 @@
         <v>48</v>
       </c>
       <c r="AD65" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AH65" t="s">
         <v>107</v>
@@ -9484,18 +9472,18 @@
         <v>54</v>
       </c>
       <c r="AO65" t="s">
+        <v>401</v>
+      </c>
+      <c r="AP65" t="s">
         <v>402</v>
-      </c>
-      <c r="AP65" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="66" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B66" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C66" t="s">
         <v>271</v>
@@ -9531,30 +9519,30 @@
         <v>48</v>
       </c>
       <c r="AD66" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AH66" t="s">
+        <v>404</v>
+      </c>
+      <c r="AK66" t="s">
         <v>405</v>
-      </c>
-      <c r="AK66" t="s">
-        <v>406</v>
       </c>
       <c r="AM66" t="s">
         <v>54</v>
       </c>
       <c r="AO66" t="s">
+        <v>406</v>
+      </c>
+      <c r="AP66" t="s">
         <v>407</v>
-      </c>
-      <c r="AP66" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="67" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B67" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C67" t="s">
         <v>271</v>
@@ -9572,7 +9560,7 @@
         <v>2</v>
       </c>
       <c r="O67" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P67">
         <v>1</v>
@@ -9593,22 +9581,22 @@
         <v>48</v>
       </c>
       <c r="AD67" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AH67" t="s">
+        <v>404</v>
+      </c>
+      <c r="AK67" t="s">
         <v>405</v>
-      </c>
-      <c r="AK67" t="s">
-        <v>406</v>
       </c>
       <c r="AM67" t="s">
         <v>54</v>
       </c>
       <c r="AO67" t="s">
+        <v>410</v>
+      </c>
+      <c r="AP67" t="s">
         <v>411</v>
-      </c>
-      <c r="AP67" t="s">
-        <v>412</v>
       </c>
       <c r="AR67" t="s">
         <v>63</v>
@@ -9616,10 +9604,10 @@
     </row>
     <row r="68" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>412</v>
+      </c>
+      <c r="B68" t="s">
         <v>413</v>
-      </c>
-      <c r="B68" t="s">
-        <v>414</v>
       </c>
       <c r="C68" t="s">
         <v>154</v>
@@ -9634,7 +9622,7 @@
         <v>4</v>
       </c>
       <c r="G68" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H68">
         <v>4</v>
@@ -9691,30 +9679,30 @@
         <v>109</v>
       </c>
       <c r="AH68" t="s">
+        <v>415</v>
+      </c>
+      <c r="AI68" t="s">
         <v>416</v>
-      </c>
-      <c r="AI68" t="s">
-        <v>417</v>
       </c>
       <c r="AM68" t="s">
         <v>54</v>
       </c>
       <c r="AN68" t="s">
+        <v>417</v>
+      </c>
+      <c r="AO68" t="s">
         <v>418</v>
       </c>
-      <c r="AO68" t="s">
+      <c r="AP68" t="s">
         <v>419</v>
-      </c>
-      <c r="AP68" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="69" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B69" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C69" t="s">
         <v>166</v>
@@ -9783,24 +9771,24 @@
         <v>54</v>
       </c>
       <c r="AN69" t="s">
+        <v>421</v>
+      </c>
+      <c r="AO69" t="s">
         <v>422</v>
       </c>
-      <c r="AO69" t="s">
+      <c r="AP69" t="s">
         <v>423</v>
       </c>
-      <c r="AP69" t="s">
+      <c r="AS69" t="s">
         <v>424</v>
-      </c>
-      <c r="AS69" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="70" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B70" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C70" t="s">
         <v>166</v>
@@ -9848,7 +9836,7 @@
         <v>48</v>
       </c>
       <c r="AD70" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AE70">
         <v>112</v>
@@ -9857,33 +9845,33 @@
         <v>106</v>
       </c>
       <c r="AH70" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AI70" t="s">
         <v>107</v>
       </c>
       <c r="AM70" t="s">
+        <v>428</v>
+      </c>
+      <c r="AN70" t="s">
         <v>429</v>
       </c>
-      <c r="AN70" t="s">
+      <c r="AO70" t="s">
         <v>430</v>
       </c>
-      <c r="AO70" t="s">
+      <c r="AP70" t="s">
         <v>431</v>
       </c>
-      <c r="AP70" t="s">
+      <c r="AS70" t="s">
         <v>432</v>
-      </c>
-      <c r="AS70" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="71" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>433</v>
+      </c>
+      <c r="B71" t="s">
         <v>434</v>
-      </c>
-      <c r="B71" t="s">
-        <v>435</v>
       </c>
       <c r="C71" t="s">
         <v>271</v>
@@ -9931,24 +9919,24 @@
         <v>48</v>
       </c>
       <c r="AD71" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AM71" t="s">
         <v>177</v>
       </c>
       <c r="AO71" t="s">
+        <v>436</v>
+      </c>
+      <c r="AP71" t="s">
         <v>437</v>
-      </c>
-      <c r="AP71" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="72" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B72" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C72" t="s">
         <v>271</v>
@@ -9996,24 +9984,24 @@
         <v>48</v>
       </c>
       <c r="AD72" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AM72" t="s">
         <v>54</v>
       </c>
       <c r="AO72" t="s">
+        <v>439</v>
+      </c>
+      <c r="AP72" t="s">
         <v>440</v>
-      </c>
-      <c r="AP72" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="73" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>441</v>
+      </c>
+      <c r="B73" t="s">
         <v>442</v>
-      </c>
-      <c r="B73" t="s">
-        <v>443</v>
       </c>
       <c r="C73" t="s">
         <v>118</v>
@@ -10061,7 +10049,7 @@
         <v>167</v>
       </c>
       <c r="AC73" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AE73">
         <v>121</v>
@@ -10082,21 +10070,21 @@
         <v>54</v>
       </c>
       <c r="AO73" t="s">
+        <v>444</v>
+      </c>
+      <c r="AP73" t="s">
         <v>445</v>
       </c>
-      <c r="AP73" t="s">
+      <c r="AS73" t="s">
         <v>446</v>
-      </c>
-      <c r="AS73" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="74" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>447</v>
+      </c>
+      <c r="B74" t="s">
         <v>448</v>
-      </c>
-      <c r="B74" t="s">
-        <v>449</v>
       </c>
       <c r="C74" t="s">
         <v>271</v>
@@ -10132,7 +10120,7 @@
         <v>48</v>
       </c>
       <c r="AD74" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AE74">
         <v>135</v>
@@ -10144,21 +10132,21 @@
         <v>54</v>
       </c>
       <c r="AN74" t="s">
+        <v>450</v>
+      </c>
+      <c r="AO74" t="s">
         <v>451</v>
       </c>
-      <c r="AO74" t="s">
+      <c r="AP74" t="s">
         <v>452</v>
-      </c>
-      <c r="AP74" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="75" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B75" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C75" t="s">
         <v>271</v>
@@ -10212,21 +10200,21 @@
         <v>54</v>
       </c>
       <c r="AN75" t="s">
+        <v>454</v>
+      </c>
+      <c r="AO75" t="s">
         <v>455</v>
       </c>
-      <c r="AO75" t="s">
+      <c r="AP75" t="s">
         <v>456</v>
-      </c>
-      <c r="AP75" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="76" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>457</v>
+      </c>
+      <c r="B76" t="s">
         <v>458</v>
-      </c>
-      <c r="B76" t="s">
-        <v>459</v>
       </c>
       <c r="C76" t="s">
         <v>131</v>
@@ -10307,27 +10295,27 @@
         <v>77</v>
       </c>
       <c r="AK76" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AM76" t="s">
         <v>54</v>
       </c>
       <c r="AN76" t="s">
+        <v>460</v>
+      </c>
+      <c r="AO76" t="s">
         <v>461</v>
       </c>
-      <c r="AO76" t="s">
+      <c r="AP76" t="s">
         <v>462</v>
-      </c>
-      <c r="AP76" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="77" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B77" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C77" t="s">
         <v>118</v>
@@ -10414,21 +10402,21 @@
         <v>54</v>
       </c>
       <c r="AN77" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AO77" t="s">
+        <v>464</v>
+      </c>
+      <c r="AP77" t="s">
         <v>465</v>
-      </c>
-      <c r="AP77" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="78" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B78" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C78" t="s">
         <v>166</v>
@@ -10482,7 +10470,7 @@
         <v>75</v>
       </c>
       <c r="AG78" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AI78" t="s">
         <v>77</v>
@@ -10491,27 +10479,27 @@
         <v>77</v>
       </c>
       <c r="AL78" t="s">
+        <v>468</v>
+      </c>
+      <c r="AM78" t="s">
         <v>469</v>
       </c>
-      <c r="AM78" t="s">
+      <c r="AN78" t="s">
         <v>470</v>
       </c>
-      <c r="AN78" t="s">
+      <c r="AO78" t="s">
         <v>471</v>
       </c>
-      <c r="AO78" t="s">
+      <c r="AP78" t="s">
         <v>472</v>
-      </c>
-      <c r="AP78" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="79" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B79" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C79" t="s">
         <v>192</v>
@@ -10577,21 +10565,21 @@
         <v>54</v>
       </c>
       <c r="AN79" t="s">
+        <v>474</v>
+      </c>
+      <c r="AO79" t="s">
         <v>475</v>
       </c>
-      <c r="AO79" t="s">
+      <c r="AP79" t="s">
         <v>476</v>
-      </c>
-      <c r="AP79" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="80" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B80" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C80" t="s">
         <v>192</v>
@@ -10648,27 +10636,27 @@
         <v>77</v>
       </c>
       <c r="AL80" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AM80" t="s">
         <v>54</v>
       </c>
       <c r="AN80" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AO80" t="s">
+        <v>479</v>
+      </c>
+      <c r="AP80" t="s">
         <v>480</v>
-      </c>
-      <c r="AP80" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="81" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>481</v>
+      </c>
+      <c r="B81" t="s">
         <v>482</v>
-      </c>
-      <c r="B81" t="s">
-        <v>483</v>
       </c>
       <c r="C81" t="s">
         <v>118</v>
@@ -10704,42 +10692,42 @@
         <v>24</v>
       </c>
       <c r="Y81" t="s">
+        <v>483</v>
+      </c>
+      <c r="Z81" t="s">
         <v>484</v>
       </c>
-      <c r="Z81" t="s">
+      <c r="AC81" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF81" t="s">
         <v>485</v>
       </c>
-      <c r="AC81" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF81" t="s">
-        <v>486</v>
-      </c>
       <c r="AG81" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AI81" t="s">
         <v>77</v>
       </c>
       <c r="AJ81" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AM81" t="s">
         <v>54</v>
       </c>
       <c r="AO81" t="s">
+        <v>486</v>
+      </c>
+      <c r="AP81" t="s">
         <v>487</v>
-      </c>
-      <c r="AP81" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="82" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>488</v>
+      </c>
+      <c r="B82" t="s">
         <v>489</v>
-      </c>
-      <c r="B82" t="s">
-        <v>490</v>
       </c>
       <c r="C82" t="s">
         <v>154</v>
@@ -10793,7 +10781,7 @@
         <v>48</v>
       </c>
       <c r="AD82" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AE82">
         <v>118</v>
@@ -10814,21 +10802,21 @@
         <v>54</v>
       </c>
       <c r="AN82" t="s">
+        <v>491</v>
+      </c>
+      <c r="AO82" t="s">
         <v>492</v>
       </c>
-      <c r="AO82" t="s">
+      <c r="AP82" t="s">
         <v>493</v>
-      </c>
-      <c r="AP82" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="83" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B83" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C83" t="s">
         <v>154</v>
@@ -10891,7 +10879,7 @@
         <v>48</v>
       </c>
       <c r="AD83" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AE83">
         <v>118</v>
@@ -10912,21 +10900,21 @@
         <v>54</v>
       </c>
       <c r="AN83" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AO83" t="s">
+        <v>495</v>
+      </c>
+      <c r="AP83" t="s">
         <v>496</v>
-      </c>
-      <c r="AP83" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="84" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B84" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C84" t="s">
         <v>118</v>
@@ -10989,7 +10977,7 @@
         <v>24</v>
       </c>
       <c r="Y84" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="Z84" t="s">
         <v>48</v>
@@ -10998,7 +10986,7 @@
         <v>48</v>
       </c>
       <c r="AD84" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AE84">
         <v>118</v>
@@ -11019,24 +11007,24 @@
         <v>54</v>
       </c>
       <c r="AN84" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AO84" t="s">
+        <v>499</v>
+      </c>
+      <c r="AP84" t="s">
         <v>500</v>
       </c>
-      <c r="AP84" t="s">
+      <c r="AS84" t="s">
         <v>501</v>
-      </c>
-      <c r="AS84" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="85" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B85" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C85" t="s">
         <v>118</v>
@@ -11063,7 +11051,7 @@
         <v>24</v>
       </c>
       <c r="Y85" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AC85" t="s">
         <v>48</v>
@@ -11081,18 +11069,18 @@
         <v>54</v>
       </c>
       <c r="AO85" t="s">
+        <v>504</v>
+      </c>
+      <c r="AP85" t="s">
         <v>505</v>
-      </c>
-      <c r="AP85" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="86" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B86" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C86" t="s">
         <v>118</v>
@@ -11119,24 +11107,24 @@
         <v>24</v>
       </c>
       <c r="Y86" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AM86" t="s">
         <v>54</v>
       </c>
       <c r="AO86" t="s">
+        <v>507</v>
+      </c>
+      <c r="AP86" t="s">
         <v>508</v>
-      </c>
-      <c r="AP86" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="87" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B87" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C87" t="s">
         <v>131</v>
@@ -11157,16 +11145,16 @@
         <v>24</v>
       </c>
       <c r="Y87" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AD87" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AE87" t="s">
         <v>252</v>
       </c>
       <c r="AH87" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AK87" t="s">
         <v>225</v>
@@ -11175,18 +11163,18 @@
         <v>54</v>
       </c>
       <c r="AO87" t="s">
+        <v>512</v>
+      </c>
+      <c r="AP87" t="s">
         <v>513</v>
-      </c>
-      <c r="AP87" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="88" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B88" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C88" t="s">
         <v>166</v>
@@ -11264,10 +11252,10 @@
         <v>48</v>
       </c>
       <c r="AD88" t="s">
+        <v>515</v>
+      </c>
+      <c r="AE88" t="s">
         <v>516</v>
-      </c>
-      <c r="AE88" t="s">
-        <v>517</v>
       </c>
       <c r="AF88" t="s">
         <v>150</v>
@@ -11279,33 +11267,33 @@
         <v>77</v>
       </c>
       <c r="AI88" t="s">
+        <v>517</v>
+      </c>
+      <c r="AK88" t="s">
         <v>518</v>
-      </c>
-      <c r="AK88" t="s">
-        <v>519</v>
       </c>
       <c r="AM88" t="s">
         <v>54</v>
       </c>
       <c r="AN88" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AO88" t="s">
+        <v>519</v>
+      </c>
+      <c r="AP88" t="s">
         <v>520</v>
       </c>
-      <c r="AP88" t="s">
+      <c r="AS88" t="s">
         <v>521</v>
-      </c>
-      <c r="AS88" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="89" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B89" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C89" t="s">
         <v>154</v>
@@ -11386,30 +11374,30 @@
         <v>77</v>
       </c>
       <c r="AI89" t="s">
+        <v>517</v>
+      </c>
+      <c r="AK89" t="s">
         <v>518</v>
-      </c>
-      <c r="AK89" t="s">
-        <v>519</v>
       </c>
       <c r="AM89" t="s">
         <v>54</v>
       </c>
       <c r="AN89" t="s">
+        <v>523</v>
+      </c>
+      <c r="AO89" t="s">
         <v>524</v>
       </c>
-      <c r="AO89" t="s">
+      <c r="AP89" t="s">
         <v>525</v>
-      </c>
-      <c r="AP89" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="90" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B90" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C90" t="s">
         <v>154</v>
@@ -11490,33 +11478,33 @@
         <v>77</v>
       </c>
       <c r="AI90" t="s">
+        <v>517</v>
+      </c>
+      <c r="AK90" t="s">
         <v>518</v>
-      </c>
-      <c r="AK90" t="s">
-        <v>519</v>
       </c>
       <c r="AM90" t="s">
         <v>54</v>
       </c>
       <c r="AN90" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AO90" t="s">
+        <v>527</v>
+      </c>
+      <c r="AP90" t="s">
         <v>528</v>
       </c>
-      <c r="AP90" t="s">
+      <c r="AS90" t="s">
         <v>529</v>
-      </c>
-      <c r="AS90" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="91" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B91" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C91" t="s">
         <v>166</v>
@@ -11558,48 +11546,48 @@
         <v>48</v>
       </c>
       <c r="AD91" t="s">
+        <v>515</v>
+      </c>
+      <c r="AE91" t="s">
         <v>516</v>
       </c>
-      <c r="AE91" t="s">
-        <v>517</v>
-      </c>
       <c r="AF91" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AG91" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AH91" t="s">
         <v>77</v>
       </c>
       <c r="AI91" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AK91" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AM91" t="s">
         <v>177</v>
       </c>
       <c r="AN91" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AO91" t="s">
+        <v>533</v>
+      </c>
+      <c r="AP91" t="s">
         <v>534</v>
       </c>
-      <c r="AP91" t="s">
+      <c r="AS91" t="s">
         <v>535</v>
-      </c>
-      <c r="AS91" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="92" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B92" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C92" t="s">
         <v>166</v>
@@ -11653,45 +11641,45 @@
         <v>48</v>
       </c>
       <c r="AD92" t="s">
+        <v>515</v>
+      </c>
+      <c r="AE92" t="s">
         <v>516</v>
       </c>
-      <c r="AE92" t="s">
-        <v>517</v>
-      </c>
       <c r="AF92" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AH92" t="s">
         <v>77</v>
       </c>
       <c r="AI92" t="s">
+        <v>517</v>
+      </c>
+      <c r="AK92" t="s">
         <v>518</v>
-      </c>
-      <c r="AK92" t="s">
-        <v>519</v>
       </c>
       <c r="AM92" t="s">
         <v>54</v>
       </c>
       <c r="AN92" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AO92" t="s">
+        <v>537</v>
+      </c>
+      <c r="AP92" t="s">
         <v>538</v>
       </c>
-      <c r="AP92" t="s">
+      <c r="AS92" t="s">
         <v>539</v>
-      </c>
-      <c r="AS92" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="93" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B93" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C93" t="s">
         <v>192</v>
@@ -11736,7 +11724,7 @@
         <v>48</v>
       </c>
       <c r="AD93" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AE93">
         <v>113</v>
@@ -11745,10 +11733,10 @@
         <v>120</v>
       </c>
       <c r="AH93" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AI93" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AK93">
         <v>-127</v>
@@ -11757,24 +11745,24 @@
         <v>54</v>
       </c>
       <c r="AN93" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AO93" t="s">
+        <v>542</v>
+      </c>
+      <c r="AP93" t="s">
         <v>543</v>
       </c>
-      <c r="AP93" t="s">
+      <c r="AS93" t="s">
         <v>544</v>
-      </c>
-      <c r="AS93" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="94" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B94" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C94" t="s">
         <v>271</v>
@@ -11822,21 +11810,21 @@
         <v>54</v>
       </c>
       <c r="AN94" t="s">
+        <v>546</v>
+      </c>
+      <c r="AO94" t="s">
         <v>547</v>
       </c>
-      <c r="AO94" t="s">
+      <c r="AP94" t="s">
         <v>548</v>
-      </c>
-      <c r="AP94" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="95" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B95" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C95" t="s">
         <v>271</v>
@@ -11893,21 +11881,21 @@
         <v>54</v>
       </c>
       <c r="AN95" t="s">
+        <v>550</v>
+      </c>
+      <c r="AO95" t="s">
         <v>551</v>
       </c>
-      <c r="AO95" t="s">
+      <c r="AP95" t="s">
         <v>552</v>
-      </c>
-      <c r="AP95" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="96" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>553</v>
+      </c>
+      <c r="B96" t="s">
         <v>554</v>
-      </c>
-      <c r="B96" t="s">
-        <v>555</v>
       </c>
       <c r="C96" t="s">
         <v>154</v>
@@ -11943,16 +11931,16 @@
         <v>49</v>
       </c>
       <c r="Z96" t="s">
+        <v>555</v>
+      </c>
+      <c r="AA96" t="s">
         <v>556</v>
-      </c>
-      <c r="AA96" t="s">
-        <v>557</v>
       </c>
       <c r="AB96" t="s">
         <v>70</v>
       </c>
       <c r="AC96" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AD96">
         <v>70</v>
@@ -11970,21 +11958,21 @@
         <v>54</v>
       </c>
       <c r="AN96" t="s">
+        <v>558</v>
+      </c>
+      <c r="AO96" t="s">
         <v>559</v>
       </c>
-      <c r="AO96" t="s">
+      <c r="AP96" t="s">
         <v>560</v>
-      </c>
-      <c r="AP96" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="97" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B97" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C97" t="s">
         <v>154</v>
@@ -12005,7 +11993,7 @@
         <v>2</v>
       </c>
       <c r="I97" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="N97">
         <v>4</v>
@@ -12014,7 +12002,7 @@
         <v>2</v>
       </c>
       <c r="Q97" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="V97" t="s">
         <v>48</v>
@@ -12029,36 +12017,36 @@
         <v>213</v>
       </c>
       <c r="Z97" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AC97" t="s">
         <v>48</v>
       </c>
       <c r="AD97" t="s">
+        <v>563</v>
+      </c>
+      <c r="AE97" t="s">
+        <v>516</v>
+      </c>
+      <c r="AL97" t="s">
         <v>564</v>
-      </c>
-      <c r="AE97" t="s">
-        <v>517</v>
-      </c>
-      <c r="AL97" t="s">
-        <v>565</v>
       </c>
       <c r="AM97" t="s">
         <v>54</v>
       </c>
       <c r="AO97" t="s">
+        <v>565</v>
+      </c>
+      <c r="AP97" t="s">
         <v>566</v>
-      </c>
-      <c r="AP97" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="98" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B98" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C98" t="s">
         <v>154</v>
@@ -12097,16 +12085,16 @@
         <v>49</v>
       </c>
       <c r="Z98" t="s">
+        <v>555</v>
+      </c>
+      <c r="AA98" t="s">
         <v>556</v>
-      </c>
-      <c r="AA98" t="s">
-        <v>557</v>
       </c>
       <c r="AB98" t="s">
         <v>70</v>
       </c>
       <c r="AC98" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AD98">
         <v>70</v>
@@ -12124,21 +12112,21 @@
         <v>54</v>
       </c>
       <c r="AN98" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AO98" t="s">
+        <v>568</v>
+      </c>
+      <c r="AP98" t="s">
         <v>569</v>
-      </c>
-      <c r="AP98" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="99" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>570</v>
+      </c>
+      <c r="B99" t="s">
         <v>571</v>
-      </c>
-      <c r="B99" t="s">
-        <v>572</v>
       </c>
       <c r="C99" t="s">
         <v>166</v>
@@ -12189,7 +12177,7 @@
         <v>117</v>
       </c>
       <c r="AG99" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AH99" t="s">
         <v>143</v>
@@ -12201,21 +12189,21 @@
         <v>54</v>
       </c>
       <c r="AN99" t="s">
+        <v>572</v>
+      </c>
+      <c r="AO99" t="s">
         <v>573</v>
       </c>
-      <c r="AO99" t="s">
+      <c r="AP99" t="s">
         <v>574</v>
-      </c>
-      <c r="AP99" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="100" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B100" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C100" t="s">
         <v>192</v>
@@ -12260,16 +12248,16 @@
         <v>48</v>
       </c>
       <c r="AD100" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AE100">
         <v>108</v>
       </c>
       <c r="AG100" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AI100" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AJ100" t="s">
         <v>232</v>
@@ -12278,21 +12266,21 @@
         <v>54</v>
       </c>
       <c r="AN100" t="s">
+        <v>578</v>
+      </c>
+      <c r="AO100" t="s">
         <v>579</v>
       </c>
-      <c r="AO100" t="s">
+      <c r="AP100" t="s">
         <v>580</v>
-      </c>
-      <c r="AP100" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="101" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B101" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C101" t="s">
         <v>192</v>
@@ -12337,7 +12325,7 @@
         <v>48</v>
       </c>
       <c r="AE101" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AF101" t="s">
         <v>286</v>
@@ -12352,21 +12340,21 @@
         <v>54</v>
       </c>
       <c r="AN101" t="s">
+        <v>582</v>
+      </c>
+      <c r="AO101" t="s">
         <v>583</v>
       </c>
-      <c r="AO101" t="s">
+      <c r="AP101" t="s">
         <v>584</v>
-      </c>
-      <c r="AP101" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="102" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B102" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C102" t="s">
         <v>192</v>
@@ -12405,24 +12393,24 @@
         <v>97</v>
       </c>
       <c r="AM102" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AN102" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AO102" t="s">
+        <v>586</v>
+      </c>
+      <c r="AP102" t="s">
         <v>587</v>
-      </c>
-      <c r="AP102" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="103" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B103" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C103" t="s">
         <v>192</v>
@@ -12458,7 +12446,7 @@
         <v>49</v>
       </c>
       <c r="Z103" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AA103" t="s">
         <v>48</v>
@@ -12470,30 +12458,30 @@
         <v>50</v>
       </c>
       <c r="AG103" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AK103" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AM103" t="s">
         <v>157</v>
       </c>
       <c r="AN103" t="s">
+        <v>591</v>
+      </c>
+      <c r="AO103" t="s">
         <v>592</v>
       </c>
-      <c r="AO103" t="s">
+      <c r="AP103" t="s">
         <v>593</v>
-      </c>
-      <c r="AP103" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="104" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B104" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C104" t="s">
         <v>192</v>
@@ -12532,27 +12520,27 @@
         <v>48</v>
       </c>
       <c r="AD104" t="s">
+        <v>595</v>
+      </c>
+      <c r="AM104" t="s">
+        <v>428</v>
+      </c>
+      <c r="AN104" t="s">
+        <v>582</v>
+      </c>
+      <c r="AO104" t="s">
         <v>596</v>
       </c>
-      <c r="AM104" t="s">
-        <v>429</v>
-      </c>
-      <c r="AN104" t="s">
-        <v>583</v>
-      </c>
-      <c r="AO104" t="s">
+      <c r="AP104" t="s">
         <v>597</v>
-      </c>
-      <c r="AP104" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="105" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B105" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C105" t="s">
         <v>47</v>
@@ -12585,48 +12573,48 @@
         <v>24</v>
       </c>
       <c r="Y105" t="s">
+        <v>599</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA105" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC105" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE105" t="s">
         <v>600</v>
       </c>
-      <c r="Z105" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA105" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC105" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE105" t="s">
+      <c r="AG105" t="s">
         <v>601</v>
       </c>
-      <c r="AG105" t="s">
+      <c r="AM105" t="s">
+        <v>428</v>
+      </c>
+      <c r="AN105" t="s">
         <v>602</v>
       </c>
-      <c r="AM105" t="s">
-        <v>429</v>
-      </c>
-      <c r="AN105" t="s">
+      <c r="AO105" t="s">
         <v>603</v>
       </c>
-      <c r="AO105" t="s">
+      <c r="AP105" t="s">
         <v>604</v>
-      </c>
-      <c r="AP105" t="s">
-        <v>605</v>
       </c>
       <c r="AQ105" t="s">
         <v>63</v>
       </c>
       <c r="AS105" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="106" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B106" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C106" t="s">
         <v>271</v>
@@ -12647,7 +12635,7 @@
         <v>24</v>
       </c>
       <c r="Y106" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AA106" t="s">
         <v>48</v>
@@ -12656,24 +12644,24 @@
         <v>48</v>
       </c>
       <c r="AM106" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AN106" t="s">
+        <v>607</v>
+      </c>
+      <c r="AO106" t="s">
         <v>608</v>
       </c>
-      <c r="AO106" t="s">
+      <c r="AP106" t="s">
         <v>609</v>
-      </c>
-      <c r="AP106" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="107" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B107" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C107" t="s">
         <v>271</v>
@@ -12709,7 +12697,7 @@
         <v>24</v>
       </c>
       <c r="Y107" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AA107" t="s">
         <v>48</v>
@@ -12718,27 +12706,27 @@
         <v>48</v>
       </c>
       <c r="AD107" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AM107" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AN107" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AO107" t="s">
+        <v>611</v>
+      </c>
+      <c r="AP107" t="s">
         <v>612</v>
-      </c>
-      <c r="AP107" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="108" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>613</v>
+      </c>
+      <c r="B108" t="s">
         <v>614</v>
-      </c>
-      <c r="B108" t="s">
-        <v>615</v>
       </c>
       <c r="C108" t="s">
         <v>192</v>
@@ -12777,7 +12765,7 @@
         <v>48</v>
       </c>
       <c r="AB108" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AC108" t="s">
         <v>48</v>
@@ -12786,27 +12774,27 @@
         <v>258</v>
       </c>
       <c r="AG108" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AM108" t="s">
         <v>157</v>
       </c>
       <c r="AN108" t="s">
+        <v>617</v>
+      </c>
+      <c r="AO108" t="s">
         <v>618</v>
       </c>
-      <c r="AO108" t="s">
+      <c r="AP108" t="s">
         <v>619</v>
-      </c>
-      <c r="AP108" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="109" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B109" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C109" t="s">
         <v>166</v>
@@ -12842,7 +12830,7 @@
         <v>49</v>
       </c>
       <c r="Z109" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AA109" t="s">
         <v>48</v>
@@ -12860,7 +12848,7 @@
         <v>109.5</v>
       </c>
       <c r="AH109" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AI109" t="s">
         <v>282</v>
@@ -12869,21 +12857,21 @@
         <v>54</v>
       </c>
       <c r="AN109" t="s">
+        <v>623</v>
+      </c>
+      <c r="AO109" t="s">
         <v>624</v>
       </c>
-      <c r="AO109" t="s">
+      <c r="AP109" t="s">
         <v>625</v>
-      </c>
-      <c r="AP109" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="110" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>626</v>
+      </c>
+      <c r="B110" t="s">
         <v>627</v>
-      </c>
-      <c r="B110" t="s">
-        <v>628</v>
       </c>
       <c r="C110" t="s">
         <v>271</v>
@@ -12934,10 +12922,10 @@
         <v>77</v>
       </c>
       <c r="AI110" t="s">
+        <v>628</v>
+      </c>
+      <c r="AK110" t="s">
         <v>629</v>
-      </c>
-      <c r="AK110" t="s">
-        <v>630</v>
       </c>
       <c r="AL110">
         <v>-126.8</v>
@@ -12946,21 +12934,21 @@
         <v>177</v>
       </c>
       <c r="AN110" t="s">
+        <v>630</v>
+      </c>
+      <c r="AO110" t="s">
         <v>631</v>
       </c>
-      <c r="AO110" t="s">
+      <c r="AP110" t="s">
         <v>632</v>
-      </c>
-      <c r="AP110" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="111" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B111" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C111" t="s">
         <v>271</v>
@@ -13005,7 +12993,7 @@
         <v>48</v>
       </c>
       <c r="AD111" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AE111">
         <v>100</v>
@@ -13026,21 +13014,21 @@
         <v>157</v>
       </c>
       <c r="AN111" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AO111" t="s">
+        <v>635</v>
+      </c>
+      <c r="AP111" t="s">
         <v>636</v>
-      </c>
-      <c r="AP111" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="112" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>637</v>
+      </c>
+      <c r="B112" t="s">
         <v>638</v>
-      </c>
-      <c r="B112" t="s">
-        <v>639</v>
       </c>
       <c r="C112" t="s">
         <v>131</v>
@@ -13049,7 +13037,7 @@
         <v>4600</v>
       </c>
       <c r="E112" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G112">
         <v>16</v>
@@ -13058,7 +13046,7 @@
         <v>63</v>
       </c>
       <c r="M112" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="N112">
         <v>16</v>
@@ -13070,10 +13058,10 @@
         <v>63</v>
       </c>
       <c r="U112" t="s">
+        <v>639</v>
+      </c>
+      <c r="V112" t="s">
         <v>640</v>
-      </c>
-      <c r="V112" t="s">
-        <v>641</v>
       </c>
       <c r="W112">
         <v>192</v>
@@ -13082,13 +13070,13 @@
         <v>24</v>
       </c>
       <c r="Y112" t="s">
+        <v>641</v>
+      </c>
+      <c r="AC112" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD112" t="s">
         <v>642</v>
-      </c>
-      <c r="AC112" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD112" t="s">
-        <v>643</v>
       </c>
       <c r="AE112">
         <v>119</v>
@@ -13097,7 +13085,7 @@
         <v>120</v>
       </c>
       <c r="AH112" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AI112" t="s">
         <v>169</v>
@@ -13109,18 +13097,18 @@
         <v>54</v>
       </c>
       <c r="AO112" t="s">
+        <v>644</v>
+      </c>
+      <c r="AP112" t="s">
         <v>645</v>
-      </c>
-      <c r="AP112" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="113" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B113" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C113" t="s">
         <v>131</v>
@@ -13129,13 +13117,13 @@
         <v>3600</v>
       </c>
       <c r="E113" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G113">
         <v>8</v>
       </c>
       <c r="M113" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="N113">
         <v>8</v>
@@ -13144,10 +13132,10 @@
         <v>2</v>
       </c>
       <c r="U113" t="s">
+        <v>639</v>
+      </c>
+      <c r="V113" t="s">
         <v>640</v>
-      </c>
-      <c r="V113" t="s">
-        <v>641</v>
       </c>
       <c r="W113">
         <v>192</v>
@@ -13156,13 +13144,13 @@
         <v>24</v>
       </c>
       <c r="Y113" t="s">
+        <v>641</v>
+      </c>
+      <c r="AC113" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD113" t="s">
         <v>642</v>
-      </c>
-      <c r="AC113" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD113" t="s">
-        <v>643</v>
       </c>
       <c r="AE113">
         <v>119</v>
@@ -13171,7 +13159,7 @@
         <v>120</v>
       </c>
       <c r="AH113" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AI113" t="s">
         <v>169</v>
@@ -13183,18 +13171,18 @@
         <v>54</v>
       </c>
       <c r="AO113" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="AP113" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="114" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B114" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C114" t="s">
         <v>131</v>
@@ -13206,7 +13194,7 @@
         <v>2</v>
       </c>
       <c r="I114" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="K114" t="s">
         <v>137</v>
@@ -13221,7 +13209,7 @@
         <v>1</v>
       </c>
       <c r="Q114" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="S114" t="s">
         <v>137</v>
@@ -13236,7 +13224,7 @@
         <v>24</v>
       </c>
       <c r="Y114" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AC114" t="s">
         <v>48</v>
@@ -13248,30 +13236,30 @@
         <v>127</v>
       </c>
       <c r="AH114" t="s">
+        <v>651</v>
+      </c>
+      <c r="AI114" t="s">
         <v>652</v>
-      </c>
-      <c r="AI114" t="s">
-        <v>653</v>
       </c>
       <c r="AM114" t="s">
         <v>54</v>
       </c>
       <c r="AO114" t="s">
+        <v>653</v>
+      </c>
+      <c r="AP114" t="s">
         <v>654</v>
       </c>
-      <c r="AP114" t="s">
+      <c r="AS114" t="s">
         <v>655</v>
-      </c>
-      <c r="AS114" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="115" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B115" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C115" t="s">
         <v>118</v>
@@ -13328,16 +13316,16 @@
         <v>24</v>
       </c>
       <c r="Y115" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AA115" t="s">
+        <v>657</v>
+      </c>
+      <c r="AC115" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD115" t="s">
         <v>658</v>
-      </c>
-      <c r="AC115" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD115" t="s">
-        <v>659</v>
       </c>
       <c r="AE115">
         <v>119</v>
@@ -13346,7 +13334,7 @@
         <v>120</v>
       </c>
       <c r="AH115" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AI115" t="s">
         <v>176</v>
@@ -13358,21 +13346,21 @@
         <v>54</v>
       </c>
       <c r="AN115" t="s">
+        <v>660</v>
+      </c>
+      <c r="AO115" t="s">
         <v>661</v>
       </c>
-      <c r="AO115" t="s">
+      <c r="AP115" t="s">
         <v>662</v>
-      </c>
-      <c r="AP115" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="116" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>663</v>
+      </c>
+      <c r="B116" t="s">
         <v>664</v>
-      </c>
-      <c r="B116" t="s">
-        <v>665</v>
       </c>
       <c r="C116" t="s">
         <v>166</v>
@@ -13417,7 +13405,7 @@
         <v>48</v>
       </c>
       <c r="AD116" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AE116">
         <v>113</v>
@@ -13426,7 +13414,7 @@
         <v>95</v>
       </c>
       <c r="AH116" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AI116" t="s">
         <v>53</v>
@@ -13438,21 +13426,21 @@
         <v>54</v>
       </c>
       <c r="AN116" t="s">
+        <v>667</v>
+      </c>
+      <c r="AO116" t="s">
         <v>668</v>
       </c>
-      <c r="AO116" t="s">
+      <c r="AP116" t="s">
         <v>669</v>
-      </c>
-      <c r="AP116" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="117" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B117" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C117" t="s">
         <v>192</v>
@@ -13494,19 +13482,19 @@
         <v>48</v>
       </c>
       <c r="AD117" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="AE117">
         <v>104</v>
       </c>
       <c r="AG117" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="AH117" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AI117" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AK117">
         <v>-128</v>
@@ -13515,24 +13503,24 @@
         <v>54</v>
       </c>
       <c r="AN117" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="AO117" t="s">
+        <v>673</v>
+      </c>
+      <c r="AP117" t="s">
         <v>674</v>
       </c>
-      <c r="AP117" t="s">
+      <c r="AS117" t="s">
         <v>675</v>
-      </c>
-      <c r="AS117" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="118" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B118" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C118" t="s">
         <v>192</v>
@@ -13580,16 +13568,16 @@
         <v>237</v>
       </c>
       <c r="AE118" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AF118" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AH118" t="s">
         <v>53</v>
       </c>
       <c r="AI118" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AK118" t="s">
         <v>162</v>
@@ -13598,24 +13586,24 @@
         <v>54</v>
       </c>
       <c r="AN118" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="AO118" t="s">
+        <v>678</v>
+      </c>
+      <c r="AP118" t="s">
         <v>679</v>
       </c>
-      <c r="AP118" t="s">
+      <c r="AS118" t="s">
         <v>680</v>
-      </c>
-      <c r="AS118" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="119" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B119" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C119" t="s">
         <v>166</v>
@@ -13666,7 +13654,7 @@
         <v>60</v>
       </c>
       <c r="AF119" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="AG119">
         <v>104</v>
@@ -13675,30 +13663,30 @@
         <v>77</v>
       </c>
       <c r="AI119" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AL119" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="AM119" t="s">
         <v>54</v>
       </c>
       <c r="AN119" t="s">
+        <v>684</v>
+      </c>
+      <c r="AO119" t="s">
         <v>685</v>
       </c>
-      <c r="AO119" t="s">
+      <c r="AP119" t="s">
         <v>686</v>
-      </c>
-      <c r="AP119" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="120" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B120" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C120" t="s">
         <v>192</v>
@@ -13734,10 +13722,10 @@
         <v>48</v>
       </c>
       <c r="AD120" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="AH120" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AK120" t="s">
         <v>162</v>
@@ -13746,24 +13734,24 @@
         <v>54</v>
       </c>
       <c r="AN120" t="s">
+        <v>689</v>
+      </c>
+      <c r="AO120" t="s">
         <v>690</v>
       </c>
-      <c r="AO120" t="s">
+      <c r="AP120" t="s">
         <v>691</v>
       </c>
-      <c r="AP120" t="s">
+      <c r="AS120" t="s">
         <v>692</v>
-      </c>
-      <c r="AS120" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="121" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B121" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C121" t="s">
         <v>192</v>
@@ -13802,10 +13790,10 @@
         <v>48</v>
       </c>
       <c r="AD121" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="AH121" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AI121" t="s">
         <v>53</v>
@@ -13817,21 +13805,21 @@
         <v>272</v>
       </c>
       <c r="AN121" t="s">
+        <v>694</v>
+      </c>
+      <c r="AO121" t="s">
         <v>695</v>
       </c>
-      <c r="AO121" t="s">
+      <c r="AP121" t="s">
         <v>696</v>
-      </c>
-      <c r="AP121" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="122" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B122" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C122" t="s">
         <v>192</v>
@@ -13867,10 +13855,10 @@
         <v>48</v>
       </c>
       <c r="AD122" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="AH122" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AI122" t="s">
         <v>53</v>
@@ -13882,24 +13870,24 @@
         <v>177</v>
       </c>
       <c r="AN122" t="s">
+        <v>698</v>
+      </c>
+      <c r="AO122" t="s">
         <v>699</v>
       </c>
-      <c r="AO122" t="s">
+      <c r="AP122" t="s">
         <v>700</v>
       </c>
-      <c r="AP122" t="s">
+      <c r="AS122" t="s">
         <v>701</v>
-      </c>
-      <c r="AS122" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="123" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>702</v>
+      </c>
+      <c r="B123" t="s">
         <v>703</v>
-      </c>
-      <c r="B123" t="s">
-        <v>704</v>
       </c>
       <c r="C123" t="s">
         <v>166</v>
@@ -13947,7 +13935,7 @@
         <v>51</v>
       </c>
       <c r="AJ123" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AK123">
         <v>-125</v>
@@ -13956,24 +13944,24 @@
         <v>54</v>
       </c>
       <c r="AN123" t="s">
+        <v>705</v>
+      </c>
+      <c r="AO123" t="s">
         <v>706</v>
       </c>
-      <c r="AO123" t="s">
+      <c r="AP123" t="s">
         <v>707</v>
       </c>
-      <c r="AP123" t="s">
+      <c r="AS123" t="s">
         <v>708</v>
-      </c>
-      <c r="AS123" t="s">
-        <v>709</v>
       </c>
     </row>
     <row r="124" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B124" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C124" t="s">
         <v>166</v>
@@ -13997,7 +13985,7 @@
         <v>6</v>
       </c>
       <c r="O124" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="P124">
         <v>2</v>
@@ -14021,7 +14009,7 @@
         <v>51</v>
       </c>
       <c r="AJ124" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AK124">
         <v>-125</v>
@@ -14030,24 +14018,24 @@
         <v>54</v>
       </c>
       <c r="AN124" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AO124" t="s">
+        <v>710</v>
+      </c>
+      <c r="AP124" t="s">
         <v>711</v>
       </c>
-      <c r="AP124" t="s">
-        <v>712</v>
-      </c>
       <c r="AS124" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="125" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B125" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C125" t="s">
         <v>47</v>
@@ -14092,24 +14080,24 @@
         <v>48</v>
       </c>
       <c r="AD125" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="AM125" t="s">
         <v>54</v>
       </c>
       <c r="AO125" t="s">
+        <v>714</v>
+      </c>
+      <c r="AP125" t="s">
         <v>715</v>
-      </c>
-      <c r="AP125" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="126" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B126" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C126" t="s">
         <v>271</v>
@@ -14124,7 +14112,7 @@
         <v>2</v>
       </c>
       <c r="G126" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N126">
         <v>2</v>
@@ -14160,18 +14148,18 @@
         <v>54</v>
       </c>
       <c r="AO126" t="s">
+        <v>717</v>
+      </c>
+      <c r="AP126" t="s">
         <v>718</v>
-      </c>
-      <c r="AP126" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="127" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B127" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C127" t="s">
         <v>271</v>
@@ -14216,18 +14204,18 @@
         <v>157</v>
       </c>
       <c r="AO127" t="s">
+        <v>720</v>
+      </c>
+      <c r="AP127" t="s">
         <v>721</v>
-      </c>
-      <c r="AP127" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="128" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B128" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C128" t="s">
         <v>271</v>
@@ -14275,27 +14263,27 @@
         <v>51</v>
       </c>
       <c r="AG128" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AM128" t="s">
         <v>54</v>
       </c>
       <c r="AN128" t="s">
+        <v>724</v>
+      </c>
+      <c r="AO128" t="s">
         <v>725</v>
       </c>
-      <c r="AO128" t="s">
+      <c r="AP128" t="s">
         <v>726</v>
-      </c>
-      <c r="AP128" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="129" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B129" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C129" t="s">
         <v>47</v>
@@ -14343,7 +14331,7 @@
         <v>51</v>
       </c>
       <c r="AJ129" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AL129">
         <v>-128</v>
@@ -14352,21 +14340,21 @@
         <v>54</v>
       </c>
       <c r="AN129" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AO129" t="s">
+        <v>728</v>
+      </c>
+      <c r="AP129" t="s">
         <v>729</v>
-      </c>
-      <c r="AP129" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="130" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B130" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C130" t="s">
         <v>47</v>
@@ -14414,7 +14402,7 @@
         <v>60</v>
       </c>
       <c r="AJ130" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AL130" t="s">
         <v>162</v>
@@ -14423,24 +14411,24 @@
         <v>54</v>
       </c>
       <c r="AN130" t="s">
+        <v>732</v>
+      </c>
+      <c r="AO130" t="s">
         <v>733</v>
       </c>
-      <c r="AO130" t="s">
+      <c r="AP130" t="s">
         <v>734</v>
       </c>
-      <c r="AP130" t="s">
+      <c r="AS130" t="s">
         <v>735</v>
-      </c>
-      <c r="AS130" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="131" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B131" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C131" t="s">
         <v>47</v>
@@ -14461,7 +14449,7 @@
         <v>2</v>
       </c>
       <c r="O131" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="P131">
         <v>1</v>
@@ -14488,7 +14476,7 @@
         <v>51</v>
       </c>
       <c r="AJ131" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AL131">
         <v>-128</v>
@@ -14497,21 +14485,21 @@
         <v>54</v>
       </c>
       <c r="AN131" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AO131" t="s">
+        <v>737</v>
+      </c>
+      <c r="AP131" t="s">
         <v>738</v>
-      </c>
-      <c r="AP131" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="132" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B132" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C132" t="s">
         <v>47</v>
@@ -14559,7 +14547,7 @@
         <v>60</v>
       </c>
       <c r="AH132" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AL132" t="s">
         <v>162</v>
@@ -14568,21 +14556,21 @@
         <v>54</v>
       </c>
       <c r="AO132" t="s">
+        <v>740</v>
+      </c>
+      <c r="AP132" t="s">
         <v>741</v>
       </c>
-      <c r="AP132" t="s">
-        <v>742</v>
-      </c>
       <c r="AS132" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="133" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>742</v>
+      </c>
+      <c r="B133" t="s">
         <v>743</v>
-      </c>
-      <c r="B133" t="s">
-        <v>744</v>
       </c>
       <c r="C133" t="s">
         <v>131</v>
@@ -14621,16 +14609,16 @@
         <v>32</v>
       </c>
       <c r="Y133" t="s">
+        <v>744</v>
+      </c>
+      <c r="Z133" t="s">
         <v>745</v>
-      </c>
-      <c r="Z133" t="s">
-        <v>746</v>
       </c>
       <c r="AB133" t="s">
         <v>70</v>
       </c>
       <c r="AC133" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="AD133">
         <v>66</v>
@@ -14645,7 +14633,7 @@
         <v>302</v>
       </c>
       <c r="AI133" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AK133">
         <v>-128</v>
@@ -14654,24 +14642,24 @@
         <v>54</v>
       </c>
       <c r="AN133" t="s">
+        <v>747</v>
+      </c>
+      <c r="AO133" t="s">
         <v>748</v>
       </c>
-      <c r="AO133" t="s">
+      <c r="AP133" t="s">
         <v>749</v>
       </c>
-      <c r="AP133" t="s">
+      <c r="AS133" t="s">
         <v>750</v>
-      </c>
-      <c r="AS133" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="134" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>751</v>
+      </c>
+      <c r="B134" t="s">
         <v>752</v>
-      </c>
-      <c r="B134" t="s">
-        <v>753</v>
       </c>
       <c r="C134" t="s">
         <v>131</v>
@@ -14686,7 +14674,7 @@
         <v>63</v>
       </c>
       <c r="M134" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="N134">
         <v>8</v>
@@ -14695,7 +14683,7 @@
         <v>1</v>
       </c>
       <c r="U134" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="W134">
         <v>192</v>
@@ -14716,30 +14704,30 @@
         <v>70</v>
       </c>
       <c r="AC134" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="AM134" t="s">
         <v>54</v>
       </c>
       <c r="AN134" t="s">
+        <v>754</v>
+      </c>
+      <c r="AO134" t="s">
         <v>755</v>
       </c>
-      <c r="AO134" t="s">
+      <c r="AP134" t="s">
         <v>756</v>
       </c>
-      <c r="AP134" t="s">
+      <c r="AS134" t="s">
         <v>757</v>
-      </c>
-      <c r="AS134" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="135" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B135" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C135" t="s">
         <v>131</v>
@@ -14757,7 +14745,7 @@
         <v>2</v>
       </c>
       <c r="M135" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="N135">
         <v>8</v>
@@ -14766,7 +14754,7 @@
         <v>1</v>
       </c>
       <c r="U135" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="V135" t="s">
         <v>48</v>
@@ -14778,7 +14766,7 @@
         <v>24</v>
       </c>
       <c r="Y135" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="Z135" t="s">
         <v>167</v>
@@ -14787,10 +14775,10 @@
         <v>48</v>
       </c>
       <c r="AB135" t="s">
+        <v>760</v>
+      </c>
+      <c r="AC135" t="s">
         <v>761</v>
-      </c>
-      <c r="AC135" t="s">
-        <v>762</v>
       </c>
       <c r="AD135">
         <v>90</v>
@@ -14799,30 +14787,30 @@
         <v>252</v>
       </c>
       <c r="AL135" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="AM135" t="s">
         <v>54</v>
       </c>
       <c r="AN135" t="s">
+        <v>763</v>
+      </c>
+      <c r="AO135" t="s">
         <v>764</v>
       </c>
-      <c r="AO135" t="s">
+      <c r="AP135" t="s">
         <v>765</v>
       </c>
-      <c r="AP135" t="s">
+      <c r="AS135" t="s">
         <v>766</v>
-      </c>
-      <c r="AS135" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="136" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>767</v>
+      </c>
+      <c r="B136" t="s">
         <v>768</v>
-      </c>
-      <c r="B136" t="s">
-        <v>769</v>
       </c>
       <c r="C136" t="s">
         <v>131</v>
@@ -14840,7 +14828,7 @@
         <v>63</v>
       </c>
       <c r="H136" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I136" t="s">
         <v>326</v>
@@ -14867,7 +14855,7 @@
         <v>24</v>
       </c>
       <c r="Y136" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="AA136" t="s">
         <v>48</v>
@@ -14900,24 +14888,24 @@
         <v>186</v>
       </c>
       <c r="AN136" t="s">
+        <v>771</v>
+      </c>
+      <c r="AO136" t="s">
         <v>772</v>
       </c>
-      <c r="AO136" t="s">
+      <c r="AP136" t="s">
         <v>773</v>
       </c>
-      <c r="AP136" t="s">
+      <c r="AS136" t="s">
         <v>774</v>
-      </c>
-      <c r="AS136" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="137" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B137" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C137" t="s">
         <v>118</v>
@@ -14950,7 +14938,7 @@
         <v>24</v>
       </c>
       <c r="Y137" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="AB137" t="s">
         <v>70</v>
@@ -14959,21 +14947,21 @@
         <v>54</v>
       </c>
       <c r="AN137" t="s">
+        <v>777</v>
+      </c>
+      <c r="AO137" t="s">
         <v>778</v>
       </c>
-      <c r="AO137" t="s">
+      <c r="AP137" t="s">
         <v>779</v>
-      </c>
-      <c r="AP137" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="138" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B138" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C138" t="s">
         <v>118</v>
@@ -15012,7 +15000,7 @@
         <v>24</v>
       </c>
       <c r="Y138" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="AA138" t="s">
         <v>48</v>
@@ -15024,7 +15012,7 @@
         <v>48</v>
       </c>
       <c r="AE138" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AF138">
         <v>125</v>
@@ -15036,24 +15024,24 @@
         <v>54</v>
       </c>
       <c r="AN138" t="s">
+        <v>781</v>
+      </c>
+      <c r="AO138" t="s">
         <v>782</v>
       </c>
-      <c r="AO138" t="s">
+      <c r="AP138" t="s">
         <v>783</v>
       </c>
-      <c r="AP138" t="s">
+      <c r="AS138" t="s">
         <v>784</v>
-      </c>
-      <c r="AS138" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="139" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B139" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C139" t="s">
         <v>154</v>
@@ -15101,7 +15089,7 @@
         <v>24</v>
       </c>
       <c r="Y139" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AA139" t="s">
         <v>48</v>
@@ -15113,7 +15101,7 @@
         <v>48</v>
       </c>
       <c r="AD139" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="AE139">
         <v>118</v>
@@ -15128,24 +15116,24 @@
         <v>54</v>
       </c>
       <c r="AN139" t="s">
+        <v>788</v>
+      </c>
+      <c r="AO139" t="s">
         <v>789</v>
       </c>
-      <c r="AO139" t="s">
+      <c r="AP139" t="s">
         <v>790</v>
       </c>
-      <c r="AP139" t="s">
+      <c r="AS139" t="s">
         <v>791</v>
-      </c>
-      <c r="AS139" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="140" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B140" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C140" t="s">
         <v>118</v>
@@ -15223,7 +15211,7 @@
         <v>48</v>
       </c>
       <c r="AD140" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="AE140">
         <v>118</v>
@@ -15241,24 +15229,24 @@
         <v>177</v>
       </c>
       <c r="AN140" t="s">
+        <v>794</v>
+      </c>
+      <c r="AO140" t="s">
         <v>795</v>
       </c>
-      <c r="AO140" t="s">
+      <c r="AP140" t="s">
         <v>796</v>
       </c>
-      <c r="AP140" t="s">
+      <c r="AS140" t="s">
         <v>797</v>
-      </c>
-      <c r="AS140" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="141" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B141" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C141" t="s">
         <v>118</v>
@@ -15276,7 +15264,7 @@
         <v>8</v>
       </c>
       <c r="H141" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I141">
         <v>16</v>
@@ -15315,7 +15303,7 @@
         <v>24</v>
       </c>
       <c r="Y141" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="AA141" t="s">
         <v>48</v>
@@ -15333,7 +15321,7 @@
         <v>252</v>
       </c>
       <c r="AF141" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="AG141">
         <v>125</v>
@@ -15351,21 +15339,21 @@
         <v>177</v>
       </c>
       <c r="AN141" t="s">
+        <v>800</v>
+      </c>
+      <c r="AO141" t="s">
         <v>801</v>
       </c>
-      <c r="AO141" t="s">
+      <c r="AP141" t="s">
         <v>802</v>
-      </c>
-      <c r="AP141" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="142" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B142" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C142" t="s">
         <v>118</v>
@@ -15401,7 +15389,7 @@
         <v>24</v>
       </c>
       <c r="Y142" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="AA142" t="s">
         <v>48</v>
@@ -15425,24 +15413,24 @@
         <v>54</v>
       </c>
       <c r="AN142" t="s">
+        <v>805</v>
+      </c>
+      <c r="AO142" t="s">
         <v>806</v>
       </c>
-      <c r="AO142" t="s">
+      <c r="AP142" t="s">
         <v>807</v>
       </c>
-      <c r="AP142" t="s">
+      <c r="AS142" t="s">
         <v>808</v>
-      </c>
-      <c r="AS142" t="s">
-        <v>809</v>
       </c>
     </row>
     <row r="143" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B143" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C143" t="s">
         <v>192</v>
@@ -15499,24 +15487,24 @@
         <v>54</v>
       </c>
       <c r="AN143" t="s">
+        <v>810</v>
+      </c>
+      <c r="AO143" t="s">
         <v>811</v>
       </c>
-      <c r="AO143" t="s">
+      <c r="AP143" t="s">
         <v>812</v>
       </c>
-      <c r="AP143" t="s">
+      <c r="AS143" t="s">
         <v>813</v>
-      </c>
-      <c r="AS143" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="144" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B144" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C144" t="s">
         <v>166</v>
@@ -15558,7 +15546,7 @@
         <v>48</v>
       </c>
       <c r="AG144" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AI144" t="s">
         <v>184</v>
@@ -15570,24 +15558,24 @@
         <v>177</v>
       </c>
       <c r="AN144" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="AO144" t="s">
+        <v>815</v>
+      </c>
+      <c r="AP144" t="s">
         <v>816</v>
       </c>
-      <c r="AP144" t="s">
+      <c r="AS144" t="s">
         <v>817</v>
-      </c>
-      <c r="AS144" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="145" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B145" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C145" t="s">
         <v>166</v>
@@ -15605,7 +15593,7 @@
         <v>2</v>
       </c>
       <c r="H145" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="O145">
         <v>4</v>
@@ -15647,24 +15635,24 @@
         <v>54</v>
       </c>
       <c r="AN145" t="s">
+        <v>819</v>
+      </c>
+      <c r="AO145" t="s">
         <v>820</v>
       </c>
-      <c r="AO145" t="s">
+      <c r="AP145" t="s">
         <v>821</v>
       </c>
-      <c r="AP145" t="s">
+      <c r="AS145" t="s">
         <v>822</v>
-      </c>
-      <c r="AS145" t="s">
-        <v>823</v>
       </c>
     </row>
     <row r="146" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B146" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C146" t="s">
         <v>154</v>
@@ -15745,7 +15733,7 @@
         <v>74</v>
       </c>
       <c r="AE146" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AF146">
         <v>125</v>
@@ -15760,24 +15748,24 @@
         <v>54</v>
       </c>
       <c r="AN146" t="s">
+        <v>824</v>
+      </c>
+      <c r="AO146" t="s">
         <v>825</v>
       </c>
-      <c r="AO146" t="s">
+      <c r="AP146" t="s">
         <v>826</v>
       </c>
-      <c r="AP146" t="s">
+      <c r="AS146" t="s">
         <v>827</v>
-      </c>
-      <c r="AS146" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="147" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>828</v>
+      </c>
+      <c r="B147" t="s">
         <v>829</v>
-      </c>
-      <c r="B147" t="s">
-        <v>830</v>
       </c>
       <c r="C147" t="s">
         <v>118</v>
@@ -15846,7 +15834,7 @@
         <v>48</v>
       </c>
       <c r="AD147" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="AE147">
         <v>136</v>
@@ -15867,21 +15855,21 @@
         <v>54</v>
       </c>
       <c r="AN147" t="s">
+        <v>831</v>
+      </c>
+      <c r="AO147" t="s">
         <v>832</v>
       </c>
-      <c r="AO147" t="s">
+      <c r="AP147" t="s">
         <v>833</v>
-      </c>
-      <c r="AP147" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="148" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
+        <v>834</v>
+      </c>
+      <c r="B148" t="s">
         <v>835</v>
-      </c>
-      <c r="B148" t="s">
-        <v>836</v>
       </c>
       <c r="C148" t="s">
         <v>192</v>
@@ -15926,7 +15914,7 @@
         <v>64</v>
       </c>
       <c r="AE148" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AF148" t="s">
         <v>223</v>
@@ -15938,18 +15926,18 @@
         <v>54</v>
       </c>
       <c r="AO148" t="s">
+        <v>836</v>
+      </c>
+      <c r="AP148" t="s">
         <v>837</v>
-      </c>
-      <c r="AP148" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="149" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B149" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="C149" t="s">
         <v>166</v>
@@ -16015,18 +16003,18 @@
         <v>54</v>
       </c>
       <c r="AO149" t="s">
+        <v>839</v>
+      </c>
+      <c r="AP149" t="s">
         <v>840</v>
-      </c>
-      <c r="AP149" t="s">
-        <v>841</v>
       </c>
     </row>
     <row r="150" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>841</v>
+      </c>
+      <c r="B150" t="s">
         <v>842</v>
-      </c>
-      <c r="B150" t="s">
-        <v>843</v>
       </c>
       <c r="C150" t="s">
         <v>192</v>
@@ -16068,7 +16056,7 @@
         <v>48</v>
       </c>
       <c r="AD150" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AE150">
         <v>90</v>
@@ -16086,24 +16074,24 @@
         <v>157</v>
       </c>
       <c r="AN150" t="s">
+        <v>844</v>
+      </c>
+      <c r="AO150" t="s">
         <v>845</v>
       </c>
-      <c r="AO150" t="s">
+      <c r="AP150" t="s">
         <v>846</v>
       </c>
-      <c r="AP150" t="s">
+      <c r="AS150" t="s">
         <v>847</v>
-      </c>
-      <c r="AS150" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="151" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B151" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C151" t="s">
         <v>192</v>
@@ -16142,39 +16130,39 @@
         <v>48</v>
       </c>
       <c r="AD151" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AE151">
         <v>105</v>
       </c>
       <c r="AF151" t="s">
+        <v>850</v>
+      </c>
+      <c r="AH151" t="s">
         <v>851</v>
-      </c>
-      <c r="AH151" t="s">
-        <v>852</v>
       </c>
       <c r="AM151" t="s">
         <v>54</v>
       </c>
       <c r="AN151" t="s">
+        <v>852</v>
+      </c>
+      <c r="AO151" t="s">
         <v>853</v>
       </c>
-      <c r="AO151" t="s">
+      <c r="AP151" t="s">
         <v>854</v>
       </c>
-      <c r="AP151" t="s">
+      <c r="AS151" t="s">
         <v>855</v>
-      </c>
-      <c r="AS151" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="152" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B152" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C152" t="s">
         <v>192</v>
@@ -16213,7 +16201,7 @@
         <v>49</v>
       </c>
       <c r="Z152" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="AA152" t="s">
         <v>48</v>
@@ -16228,7 +16216,7 @@
         <v>286</v>
       </c>
       <c r="AF152" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AH152" t="s">
         <v>77</v>
@@ -16240,21 +16228,21 @@
         <v>54</v>
       </c>
       <c r="AN152" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AO152" t="s">
+        <v>858</v>
+      </c>
+      <c r="AP152" t="s">
         <v>859</v>
-      </c>
-      <c r="AP152" t="s">
-        <v>860</v>
       </c>
     </row>
     <row r="153" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B153" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C153" t="s">
         <v>166</v>
@@ -16317,21 +16305,21 @@
         <v>54</v>
       </c>
       <c r="AN153" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AO153" t="s">
+        <v>861</v>
+      </c>
+      <c r="AP153" t="s">
         <v>862</v>
-      </c>
-      <c r="AP153" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="154" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B154" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C154" t="s">
         <v>271</v>
@@ -16382,39 +16370,39 @@
         <v>60</v>
       </c>
       <c r="AG154" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AH154" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AI154" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AK154" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="AM154" t="s">
         <v>54</v>
       </c>
       <c r="AN154" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AO154" t="s">
+        <v>864</v>
+      </c>
+      <c r="AP154" t="s">
         <v>865</v>
       </c>
-      <c r="AP154" t="s">
+      <c r="AS154" t="s">
         <v>866</v>
-      </c>
-      <c r="AS154" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="155" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B155" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="C155" t="s">
         <v>271</v>
@@ -16462,7 +16450,7 @@
         <v>48</v>
       </c>
       <c r="AD155" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="AE155">
         <v>96</v>
@@ -16477,21 +16465,21 @@
         <v>54</v>
       </c>
       <c r="AN155" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AO155" t="s">
+        <v>869</v>
+      </c>
+      <c r="AP155" t="s">
         <v>870</v>
-      </c>
-      <c r="AP155" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="156" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B156" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C156" t="s">
         <v>192</v>
@@ -16527,7 +16515,7 @@
         <v>49</v>
       </c>
       <c r="Z156" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AA156" t="s">
         <v>48</v>
@@ -16536,7 +16524,7 @@
         <v>48</v>
       </c>
       <c r="AD156" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="AE156">
         <v>106</v>
@@ -16548,30 +16536,30 @@
         <v>120</v>
       </c>
       <c r="AK156" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="AM156" t="s">
         <v>54</v>
       </c>
       <c r="AN156" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AO156" t="s">
+        <v>873</v>
+      </c>
+      <c r="AP156" t="s">
         <v>874</v>
       </c>
-      <c r="AP156" t="s">
+      <c r="AS156" t="s">
         <v>875</v>
-      </c>
-      <c r="AS156" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="157" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B157" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C157" t="s">
         <v>47</v>
@@ -16616,16 +16604,16 @@
         <v>48</v>
       </c>
       <c r="AD157" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="AF157" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AH157" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AI157" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AK157" t="s">
         <v>162</v>
@@ -16634,21 +16622,21 @@
         <v>54</v>
       </c>
       <c r="AN157" t="s">
+        <v>878</v>
+      </c>
+      <c r="AO157" t="s">
         <v>879</v>
       </c>
-      <c r="AO157" t="s">
+      <c r="AP157" t="s">
         <v>880</v>
-      </c>
-      <c r="AP157" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="158" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B158" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C158" t="s">
         <v>47</v>
@@ -16696,13 +16684,13 @@
         <v>48</v>
       </c>
       <c r="AG158" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AH158" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AI158" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AL158" t="s">
         <v>162</v>
@@ -16711,21 +16699,21 @@
         <v>54</v>
       </c>
       <c r="AN158" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="AO158" t="s">
+        <v>882</v>
+      </c>
+      <c r="AP158" t="s">
         <v>883</v>
-      </c>
-      <c r="AP158" t="s">
-        <v>884</v>
       </c>
     </row>
     <row r="159" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B159" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C159" t="s">
         <v>47</v>
@@ -16767,13 +16755,13 @@
         <v>48</v>
       </c>
       <c r="AD159" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="AF159" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG159" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AK159" t="s">
         <v>162</v>
@@ -16782,21 +16770,21 @@
         <v>54</v>
       </c>
       <c r="AN159" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="AO159" t="s">
+        <v>885</v>
+      </c>
+      <c r="AP159" t="s">
         <v>886</v>
-      </c>
-      <c r="AP159" t="s">
-        <v>887</v>
       </c>
     </row>
     <row r="160" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>887</v>
+      </c>
+      <c r="B160" t="s">
         <v>888</v>
-      </c>
-      <c r="B160" t="s">
-        <v>889</v>
       </c>
       <c r="C160" t="s">
         <v>131</v>
@@ -16859,13 +16847,13 @@
         <v>49</v>
       </c>
       <c r="Z160" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AC160" t="s">
         <v>48</v>
       </c>
       <c r="AD160" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AE160">
         <v>116</v>
@@ -16886,18 +16874,18 @@
         <v>54</v>
       </c>
       <c r="AO160" t="s">
+        <v>889</v>
+      </c>
+      <c r="AP160" t="s">
         <v>890</v>
-      </c>
-      <c r="AP160" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="161" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B161" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C161" t="s">
         <v>131</v>
@@ -16948,7 +16936,7 @@
         <v>48</v>
       </c>
       <c r="AD161" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AE161">
         <v>116</v>
@@ -16969,18 +16957,18 @@
         <v>54</v>
       </c>
       <c r="AO161" t="s">
+        <v>892</v>
+      </c>
+      <c r="AP161" t="s">
         <v>893</v>
-      </c>
-      <c r="AP161" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="162" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B162" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C162" t="s">
         <v>131</v>
@@ -17046,7 +17034,7 @@
         <v>48</v>
       </c>
       <c r="AD162" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AE162">
         <v>116</v>
@@ -17067,21 +17055,21 @@
         <v>54</v>
       </c>
       <c r="AO162" t="s">
+        <v>895</v>
+      </c>
+      <c r="AP162" t="s">
         <v>896</v>
       </c>
-      <c r="AP162" t="s">
+      <c r="AS162" t="s">
         <v>897</v>
-      </c>
-      <c r="AS162" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="163" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B163" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C163" t="s">
         <v>131</v>
@@ -17147,13 +17135,13 @@
         <v>48</v>
       </c>
       <c r="AD163" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AE163" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AF163" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AH163" t="s">
         <v>169</v>
@@ -17168,21 +17156,21 @@
         <v>54</v>
       </c>
       <c r="AO163" t="s">
+        <v>899</v>
+      </c>
+      <c r="AP163" t="s">
         <v>900</v>
       </c>
-      <c r="AP163" t="s">
+      <c r="AS163" t="s">
         <v>901</v>
-      </c>
-      <c r="AS163" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="164" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
+        <v>902</v>
+      </c>
+      <c r="B164" t="s">
         <v>903</v>
-      </c>
-      <c r="B164" t="s">
-        <v>904</v>
       </c>
       <c r="C164" t="s">
         <v>154</v>
@@ -17218,18 +17206,18 @@
         <v>54</v>
       </c>
       <c r="AO164" t="s">
+        <v>904</v>
+      </c>
+      <c r="AP164" t="s">
         <v>905</v>
-      </c>
-      <c r="AP164" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="165" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B165" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C165" t="s">
         <v>47</v>
@@ -17268,27 +17256,27 @@
         <v>102</v>
       </c>
       <c r="AJ165" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="AM165" t="s">
         <v>54</v>
       </c>
       <c r="AO165" t="s">
+        <v>908</v>
+      </c>
+      <c r="AP165" t="s">
         <v>909</v>
       </c>
-      <c r="AP165" t="s">
+      <c r="AS165" t="s">
         <v>910</v>
-      </c>
-      <c r="AS165" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="166" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
+        <v>911</v>
+      </c>
+      <c r="B166" t="s">
         <v>912</v>
-      </c>
-      <c r="B166" t="s">
-        <v>913</v>
       </c>
       <c r="C166" t="s">
         <v>118</v>
@@ -17339,7 +17327,7 @@
         <v>49</v>
       </c>
       <c r="AB166" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="AC166" t="s">
         <v>48</v>
@@ -17357,21 +17345,21 @@
         <v>54</v>
       </c>
       <c r="AO166" t="s">
+        <v>914</v>
+      </c>
+      <c r="AP166" t="s">
         <v>915</v>
       </c>
-      <c r="AP166" t="s">
+      <c r="AS166" t="s">
         <v>916</v>
-      </c>
-      <c r="AS166" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="167" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B167" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C167" t="s">
         <v>118</v>
@@ -17404,39 +17392,39 @@
         <v>49</v>
       </c>
       <c r="AB167" t="s">
+        <v>918</v>
+      </c>
+      <c r="AC167" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE167" t="s">
         <v>919</v>
       </c>
-      <c r="AC167" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE167" t="s">
-        <v>920</v>
-      </c>
       <c r="AF167" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="AI167" t="s">
         <v>156</v>
       </c>
       <c r="AM167" t="s">
+        <v>920</v>
+      </c>
+      <c r="AO167" t="s">
         <v>921</v>
       </c>
-      <c r="AO167" t="s">
+      <c r="AP167" t="s">
         <v>922</v>
       </c>
-      <c r="AP167" t="s">
+      <c r="AS167" t="s">
         <v>923</v>
-      </c>
-      <c r="AS167" t="s">
-        <v>924</v>
       </c>
     </row>
     <row r="168" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B168" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C168" t="s">
         <v>154</v>
@@ -17496,7 +17484,7 @@
         <v>48</v>
       </c>
       <c r="AD168" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="AE168">
         <v>117</v>
@@ -17505,10 +17493,10 @@
         <v>118</v>
       </c>
       <c r="AH168" t="s">
+        <v>926</v>
+      </c>
+      <c r="AI168" t="s">
         <v>927</v>
-      </c>
-      <c r="AI168" t="s">
-        <v>928</v>
       </c>
       <c r="AK168">
         <v>-117</v>
@@ -17517,21 +17505,21 @@
         <v>54</v>
       </c>
       <c r="AO168" t="s">
+        <v>928</v>
+      </c>
+      <c r="AP168" t="s">
         <v>929</v>
       </c>
-      <c r="AP168" t="s">
+      <c r="AS168" t="s">
         <v>930</v>
-      </c>
-      <c r="AS168" t="s">
-        <v>931</v>
       </c>
     </row>
     <row r="169" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B169" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C169" t="s">
         <v>154</v>
@@ -17549,27 +17537,27 @@
         <v>24</v>
       </c>
       <c r="Y169" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="AM169" t="s">
         <v>54</v>
       </c>
       <c r="AN169" t="s">
+        <v>933</v>
+      </c>
+      <c r="AO169" t="s">
         <v>934</v>
       </c>
-      <c r="AO169" t="s">
+      <c r="AP169" t="s">
         <v>935</v>
-      </c>
-      <c r="AP169" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="170" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B170" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C170" t="s">
         <v>131</v>
@@ -17587,7 +17575,7 @@
         <v>8</v>
       </c>
       <c r="H170" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I170">
         <v>16</v>
@@ -17629,7 +17617,7 @@
         <v>49</v>
       </c>
       <c r="Z170" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="AA170" t="s">
         <v>48</v>
@@ -17641,13 +17629,13 @@
         <v>48</v>
       </c>
       <c r="AD170" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="AE170">
         <v>118</v>
       </c>
       <c r="AF170" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="AI170" t="s">
         <v>184</v>
@@ -17656,21 +17644,21 @@
         <v>54</v>
       </c>
       <c r="AN170" t="s">
+        <v>940</v>
+      </c>
+      <c r="AO170" t="s">
         <v>941</v>
       </c>
-      <c r="AO170" t="s">
+      <c r="AP170" t="s">
         <v>942</v>
-      </c>
-      <c r="AP170" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="171" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B171" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C171" t="s">
         <v>118</v>
@@ -17754,10 +17742,10 @@
         <v>214</v>
       </c>
       <c r="AE171" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AF171" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AK171" t="s">
         <v>162</v>
@@ -17766,21 +17754,21 @@
         <v>54</v>
       </c>
       <c r="AO171" t="s">
+        <v>944</v>
+      </c>
+      <c r="AP171" t="s">
         <v>945</v>
       </c>
-      <c r="AP171" t="s">
+      <c r="AS171" t="s">
         <v>946</v>
-      </c>
-      <c r="AS171" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="172" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B172" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C172" t="s">
         <v>131</v>
@@ -17798,7 +17786,7 @@
         <v>8</v>
       </c>
       <c r="H172" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I172">
         <v>16</v>
@@ -17840,7 +17828,7 @@
         <v>49</v>
       </c>
       <c r="Z172" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="AA172" t="s">
         <v>48</v>
@@ -17855,33 +17843,33 @@
         <v>75</v>
       </c>
       <c r="AE172" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="AF172" t="s">
         <v>252</v>
       </c>
       <c r="AK172" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="AM172" t="s">
         <v>54</v>
       </c>
       <c r="AN172" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="AO172" t="s">
+        <v>950</v>
+      </c>
+      <c r="AP172" t="s">
         <v>951</v>
-      </c>
-      <c r="AP172" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="173" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B173" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C173" t="s">
         <v>131</v>
@@ -17962,27 +17950,27 @@
         <v>184</v>
       </c>
       <c r="AK173" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="AM173" t="s">
         <v>54</v>
       </c>
       <c r="AO173" t="s">
+        <v>953</v>
+      </c>
+      <c r="AP173" t="s">
         <v>954</v>
       </c>
-      <c r="AP173" t="s">
+      <c r="AS173" t="s">
         <v>955</v>
-      </c>
-      <c r="AS173" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="174" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B174" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C174" t="s">
         <v>131</v>
@@ -18021,16 +18009,16 @@
         <v>24</v>
       </c>
       <c r="Y174" t="s">
+        <v>957</v>
+      </c>
+      <c r="Z174" t="s">
         <v>958</v>
       </c>
-      <c r="Z174" t="s">
+      <c r="AB174" t="s">
         <v>959</v>
       </c>
-      <c r="AB174" t="s">
+      <c r="AC174" t="s">
         <v>960</v>
-      </c>
-      <c r="AC174" t="s">
-        <v>961</v>
       </c>
       <c r="AD174">
         <v>75</v>
@@ -18045,27 +18033,27 @@
         <v>232</v>
       </c>
       <c r="AI174" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AM174" t="s">
         <v>54</v>
       </c>
       <c r="AN174" t="s">
+        <v>961</v>
+      </c>
+      <c r="AO174" t="s">
         <v>962</v>
       </c>
-      <c r="AO174" t="s">
+      <c r="AP174" t="s">
         <v>963</v>
-      </c>
-      <c r="AP174" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="175" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
+        <v>964</v>
+      </c>
+      <c r="B175" t="s">
         <v>965</v>
-      </c>
-      <c r="B175" t="s">
-        <v>966</v>
       </c>
       <c r="C175" t="s">
         <v>192</v>
@@ -18104,7 +18092,7 @@
         <v>48</v>
       </c>
       <c r="AD175" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="AE175">
         <v>104</v>
@@ -18113,7 +18101,7 @@
         <v>112</v>
       </c>
       <c r="AH175" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="AK175">
         <v>-128</v>
@@ -18122,24 +18110,24 @@
         <v>54</v>
       </c>
       <c r="AN175" t="s">
+        <v>967</v>
+      </c>
+      <c r="AO175" t="s">
         <v>968</v>
       </c>
-      <c r="AO175" t="s">
+      <c r="AP175" t="s">
         <v>969</v>
       </c>
-      <c r="AP175" t="s">
+      <c r="AS175" t="s">
         <v>970</v>
-      </c>
-      <c r="AS175" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="176" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B176" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C176" t="s">
         <v>192</v>
@@ -18166,33 +18154,33 @@
         <v>48</v>
       </c>
       <c r="AD176" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="AE176">
         <v>100</v>
       </c>
       <c r="AM176" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AN176" t="s">
+        <v>973</v>
+      </c>
+      <c r="AO176" t="s">
         <v>974</v>
       </c>
-      <c r="AO176" t="s">
+      <c r="AP176" t="s">
         <v>975</v>
       </c>
-      <c r="AP176" t="s">
+      <c r="AS176" t="s">
         <v>976</v>
-      </c>
-      <c r="AS176" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="177" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B177" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="C177" t="s">
         <v>271</v>
@@ -18234,7 +18222,7 @@
         <v>48</v>
       </c>
       <c r="AD177" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="AL177">
         <v>-131.5</v>
@@ -18243,21 +18231,21 @@
         <v>54</v>
       </c>
       <c r="AN177" t="s">
+        <v>979</v>
+      </c>
+      <c r="AO177" t="s">
         <v>980</v>
       </c>
-      <c r="AO177" t="s">
+      <c r="AP177" t="s">
         <v>981</v>
-      </c>
-      <c r="AP177" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="178" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B178" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C178" t="s">
         <v>271</v>
@@ -18272,7 +18260,7 @@
         <v>4</v>
       </c>
       <c r="H178" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="N178">
         <v>2</v>
@@ -18302,7 +18290,7 @@
         <v>48</v>
       </c>
       <c r="AD178" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="AL178">
         <v>-131.5</v>
@@ -18311,21 +18299,21 @@
         <v>54</v>
       </c>
       <c r="AN178" t="s">
+        <v>983</v>
+      </c>
+      <c r="AO178" t="s">
         <v>984</v>
       </c>
-      <c r="AO178" t="s">
+      <c r="AP178" t="s">
         <v>985</v>
-      </c>
-      <c r="AP178" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="179" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B179" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="C179" t="s">
         <v>271</v>
@@ -18367,33 +18355,33 @@
         <v>48</v>
       </c>
       <c r="AD179" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="AG179" t="s">
         <v>286</v>
       </c>
       <c r="AK179" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="AM179" t="s">
         <v>54</v>
       </c>
       <c r="AN179" t="s">
+        <v>988</v>
+      </c>
+      <c r="AO179" t="s">
         <v>989</v>
       </c>
-      <c r="AO179" t="s">
+      <c r="AP179" t="s">
         <v>990</v>
-      </c>
-      <c r="AP179" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="180" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
+        <v>991</v>
+      </c>
+      <c r="B180" t="s">
         <v>992</v>
-      </c>
-      <c r="B180" t="s">
-        <v>993</v>
       </c>
       <c r="C180" t="s">
         <v>271</v>
@@ -18441,21 +18429,21 @@
         <v>177</v>
       </c>
       <c r="AN180" t="s">
+        <v>993</v>
+      </c>
+      <c r="AO180" t="s">
         <v>994</v>
       </c>
-      <c r="AO180" t="s">
+      <c r="AP180" t="s">
         <v>995</v>
-      </c>
-      <c r="AP180" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="181" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B181" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="C181" t="s">
         <v>271</v>
@@ -18506,21 +18494,21 @@
         <v>54</v>
       </c>
       <c r="AN181" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AO181" t="s">
+        <v>997</v>
+      </c>
+      <c r="AP181" t="s">
         <v>998</v>
-      </c>
-      <c r="AP181" t="s">
-        <v>999</v>
       </c>
     </row>
     <row r="182" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B182" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="C182" t="s">
         <v>271</v>
@@ -18550,7 +18538,7 @@
         <v>24</v>
       </c>
       <c r="Y182" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="Z182" t="s">
         <v>69</v>
@@ -18568,18 +18556,18 @@
         <v>54</v>
       </c>
       <c r="AO182" t="s">
+        <v>1001</v>
+      </c>
+      <c r="AP182" t="s">
         <v>1002</v>
-      </c>
-      <c r="AP182" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="183" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B183" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C183" t="s">
         <v>271</v>
@@ -18621,21 +18609,21 @@
         <v>48</v>
       </c>
       <c r="AM183" t="s">
+        <v>1004</v>
+      </c>
+      <c r="AO183" t="s">
         <v>1005</v>
       </c>
-      <c r="AO183" t="s">
+      <c r="AP183" t="s">
         <v>1006</v>
-      </c>
-      <c r="AP183" t="s">
-        <v>1007</v>
       </c>
     </row>
     <row r="184" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B184" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C184" t="s">
         <v>271</v>
@@ -18686,21 +18674,21 @@
         <v>186</v>
       </c>
       <c r="AN184" t="s">
+        <v>1008</v>
+      </c>
+      <c r="AO184" t="s">
         <v>1009</v>
       </c>
-      <c r="AO184" t="s">
+      <c r="AP184" t="s">
         <v>1010</v>
-      </c>
-      <c r="AP184" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="185" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B185" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C185" t="s">
         <v>192</v>
@@ -18742,30 +18730,30 @@
         <v>48</v>
       </c>
       <c r="AG185" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="AM185" t="s">
         <v>177</v>
       </c>
       <c r="AN185" t="s">
+        <v>1012</v>
+      </c>
+      <c r="AO185" t="s">
         <v>1013</v>
       </c>
-      <c r="AO185" t="s">
+      <c r="AP185" t="s">
         <v>1014</v>
       </c>
-      <c r="AP185" t="s">
+      <c r="AS185" t="s">
         <v>1015</v>
-      </c>
-      <c r="AS185" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="186" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B186" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C186" t="s">
         <v>166</v>
@@ -18813,27 +18801,27 @@
         <v>48</v>
       </c>
       <c r="AG186" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="AM186" t="s">
         <v>177</v>
       </c>
       <c r="AN186" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="AO186" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AP186" t="s">
         <v>1018</v>
-      </c>
-      <c r="AP186" t="s">
-        <v>1019</v>
       </c>
     </row>
     <row r="187" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B187" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C187" t="s">
         <v>166</v>
@@ -18878,27 +18866,27 @@
         <v>48</v>
       </c>
       <c r="AG187" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="AM187" t="s">
         <v>177</v>
       </c>
       <c r="AN187" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="AO187" t="s">
+        <v>1020</v>
+      </c>
+      <c r="AP187" t="s">
         <v>1021</v>
-      </c>
-      <c r="AP187" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="188" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B188" t="s">
         <v>1023</v>
-      </c>
-      <c r="B188" t="s">
-        <v>1024</v>
       </c>
       <c r="C188" t="s">
         <v>271</v>
@@ -18931,24 +18919,24 @@
         <v>48</v>
       </c>
       <c r="AD188" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="AM188" t="s">
         <v>272</v>
       </c>
       <c r="AO188" t="s">
+        <v>1024</v>
+      </c>
+      <c r="AP188" t="s">
         <v>1025</v>
-      </c>
-      <c r="AP188" t="s">
-        <v>1026</v>
       </c>
     </row>
     <row r="189" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B189" t="s">
         <v>1027</v>
-      </c>
-      <c r="B189" t="s">
-        <v>1028</v>
       </c>
       <c r="C189" t="s">
         <v>47</v>
@@ -18972,7 +18960,7 @@
         <v>2</v>
       </c>
       <c r="O189" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P189">
         <v>1</v>
@@ -18996,33 +18984,33 @@
         <v>48</v>
       </c>
       <c r="AD189" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AH189" t="s">
         <v>99</v>
       </c>
       <c r="AI189" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AL189" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AM189" t="s">
         <v>54</v>
       </c>
       <c r="AO189" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AP189" t="s">
         <v>1030</v>
-      </c>
-      <c r="AP189" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="190" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B190" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C190" t="s">
         <v>47</v>
@@ -19067,30 +19055,30 @@
         <v>48</v>
       </c>
       <c r="AD190" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AL190" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AM190" t="s">
         <v>54</v>
       </c>
       <c r="AO190" t="s">
+        <v>1032</v>
+      </c>
+      <c r="AP190" t="s">
         <v>1033</v>
       </c>
-      <c r="AP190" t="s">
+      <c r="AS190" t="s">
         <v>1034</v>
-      </c>
-      <c r="AS190" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="191" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B191" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="C191" t="s">
         <v>47</v>
@@ -19114,7 +19102,7 @@
         <v>2</v>
       </c>
       <c r="O191" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P191">
         <v>1</v>
@@ -19138,30 +19126,30 @@
         <v>48</v>
       </c>
       <c r="AD191" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AH191" t="s">
         <v>58</v>
       </c>
       <c r="AL191" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AM191" t="s">
         <v>54</v>
       </c>
       <c r="AO191" t="s">
+        <v>1036</v>
+      </c>
+      <c r="AP191" t="s">
         <v>1037</v>
-      </c>
-      <c r="AP191" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="192" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B192" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C192" t="s">
         <v>47</v>
@@ -19209,10 +19197,10 @@
         <v>48</v>
       </c>
       <c r="AD192" t="s">
+        <v>1039</v>
+      </c>
+      <c r="AH192" t="s">
         <v>1040</v>
-      </c>
-      <c r="AH192" t="s">
-        <v>1041</v>
       </c>
       <c r="AL192">
         <v>-128</v>
@@ -19221,21 +19209,21 @@
         <v>54</v>
       </c>
       <c r="AO192" t="s">
+        <v>1041</v>
+      </c>
+      <c r="AP192" t="s">
         <v>1042</v>
       </c>
-      <c r="AP192" t="s">
+      <c r="AS192" t="s">
         <v>1043</v>
-      </c>
-      <c r="AS192" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="193" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B193" t="s">
         <v>1045</v>
-      </c>
-      <c r="B193" t="s">
-        <v>1046</v>
       </c>
       <c r="C193" t="s">
         <v>47</v>
@@ -19274,7 +19262,7 @@
         <v>48</v>
       </c>
       <c r="AD193" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="AE193">
         <v>117</v>
@@ -19295,18 +19283,18 @@
         <v>54</v>
       </c>
       <c r="AO193" t="s">
+        <v>1047</v>
+      </c>
+      <c r="AP193" t="s">
         <v>1048</v>
-      </c>
-      <c r="AP193" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="194" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B194" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C194" t="s">
         <v>192</v>
@@ -19348,7 +19336,7 @@
         <v>48</v>
       </c>
       <c r="AD194" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="AE194">
         <v>113</v>
@@ -19363,21 +19351,21 @@
         <v>177</v>
       </c>
       <c r="AN194" t="s">
+        <v>1051</v>
+      </c>
+      <c r="AO194" t="s">
         <v>1052</v>
       </c>
-      <c r="AO194" t="s">
+      <c r="AP194" t="s">
         <v>1053</v>
-      </c>
-      <c r="AP194" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="195" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B195" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="C195" t="s">
         <v>166</v>
@@ -19419,7 +19407,7 @@
         <v>32</v>
       </c>
       <c r="Y195" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="Z195" t="s">
         <v>48</v>
@@ -19434,10 +19422,10 @@
         <v>48</v>
       </c>
       <c r="AD195" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="AG195" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AK195">
         <v>-130.5</v>
@@ -19446,24 +19434,24 @@
         <v>54</v>
       </c>
       <c r="AN195" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="AO195" t="s">
+        <v>1057</v>
+      </c>
+      <c r="AP195" t="s">
         <v>1058</v>
       </c>
-      <c r="AP195" t="s">
+      <c r="AS195" t="s">
         <v>1059</v>
-      </c>
-      <c r="AS195" t="s">
-        <v>1060</v>
       </c>
     </row>
     <row r="196" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B196" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C196" t="s">
         <v>131</v>
@@ -19529,7 +19517,7 @@
         <v>49</v>
       </c>
       <c r="Z196" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AA196" t="s">
         <v>48</v>
@@ -19559,21 +19547,21 @@
         <v>54</v>
       </c>
       <c r="AN196" t="s">
+        <v>1061</v>
+      </c>
+      <c r="AO196" t="s">
         <v>1062</v>
       </c>
-      <c r="AO196" t="s">
+      <c r="AP196" t="s">
         <v>1063</v>
-      </c>
-      <c r="AP196" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="197" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B197" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="C197" t="s">
         <v>166</v>
@@ -19615,7 +19603,7 @@
         <v>48</v>
       </c>
       <c r="AD197" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="AE197">
         <v>116.5</v>
@@ -19630,24 +19618,24 @@
         <v>54</v>
       </c>
       <c r="AN197" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="AO197" t="s">
+        <v>1066</v>
+      </c>
+      <c r="AP197" t="s">
         <v>1067</v>
       </c>
-      <c r="AP197" t="s">
+      <c r="AS197" t="s">
         <v>1068</v>
-      </c>
-      <c r="AS197" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="198" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B198" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C198" t="s">
         <v>166</v>
@@ -19695,7 +19683,7 @@
         <v>48</v>
       </c>
       <c r="AD198" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="AE198">
         <v>116.5</v>
@@ -19716,21 +19704,21 @@
         <v>54</v>
       </c>
       <c r="AN198" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="AO198" t="s">
+        <v>1070</v>
+      </c>
+      <c r="AP198" t="s">
         <v>1071</v>
-      </c>
-      <c r="AP198" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="199" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B199" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="C199" t="s">
         <v>131</v>
@@ -19751,18 +19739,18 @@
         <v>54</v>
       </c>
       <c r="AO199" t="s">
+        <v>1073</v>
+      </c>
+      <c r="AP199" t="s">
         <v>1074</v>
-      </c>
-      <c r="AP199" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="200" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B200" t="s">
         <v>1076</v>
-      </c>
-      <c r="B200" t="s">
-        <v>1077</v>
       </c>
       <c r="C200" t="s">
         <v>271</v>
@@ -19813,30 +19801,30 @@
         <v>66.5</v>
       </c>
       <c r="AH200" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AL200" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AM200" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AN200" t="s">
+        <v>1077</v>
+      </c>
+      <c r="AO200" t="s">
         <v>1078</v>
       </c>
-      <c r="AO200" t="s">
+      <c r="AP200" t="s">
         <v>1079</v>
-      </c>
-      <c r="AP200" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="201" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B201" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C201" t="s">
         <v>47</v>
@@ -19878,22 +19866,22 @@
         <v>49</v>
       </c>
       <c r="Z201" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AA201" t="s">
         <v>48</v>
       </c>
       <c r="AB201" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="AC201" t="s">
         <v>48</v>
       </c>
       <c r="AD201" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AG201" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AH201" t="s">
         <v>313</v>
@@ -19905,18 +19893,18 @@
         <v>54</v>
       </c>
       <c r="AO201" t="s">
+        <v>1082</v>
+      </c>
+      <c r="AP201" t="s">
         <v>1083</v>
-      </c>
-      <c r="AP201" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="202" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B202" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="C202" t="s">
         <v>47</v>
@@ -19958,36 +19946,36 @@
         <v>48</v>
       </c>
       <c r="AB202" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="AC202" t="s">
         <v>48</v>
       </c>
       <c r="AD202" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AH202" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AL202" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AM202" t="s">
         <v>54</v>
       </c>
       <c r="AO202" t="s">
+        <v>1086</v>
+      </c>
+      <c r="AP202" t="s">
         <v>1087</v>
-      </c>
-      <c r="AP202" t="s">
-        <v>1088</v>
       </c>
     </row>
     <row r="203" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B203" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="C203" t="s">
         <v>47</v>
@@ -20008,7 +19996,7 @@
         <v>2</v>
       </c>
       <c r="O203" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="P203">
         <v>1</v>
@@ -20032,10 +20020,10 @@
         <v>48</v>
       </c>
       <c r="AD203" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AH203" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AL203" t="s">
         <v>162</v>
@@ -20044,18 +20032,18 @@
         <v>54</v>
       </c>
       <c r="AO203" t="s">
+        <v>1090</v>
+      </c>
+      <c r="AP203" t="s">
         <v>1091</v>
-      </c>
-      <c r="AP203" t="s">
-        <v>1092</v>
       </c>
     </row>
     <row r="204" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B204" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C204" t="s">
         <v>47</v>
@@ -20106,10 +20094,10 @@
         <v>48</v>
       </c>
       <c r="AD204" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AH204" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="AK204">
         <v>-128</v>
@@ -20118,18 +20106,18 @@
         <v>186</v>
       </c>
       <c r="AO204" t="s">
+        <v>1094</v>
+      </c>
+      <c r="AP204" t="s">
         <v>1095</v>
-      </c>
-      <c r="AP204" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="205" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B205" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="C205" t="s">
         <v>154</v>
@@ -20162,27 +20150,27 @@
         <v>48</v>
       </c>
       <c r="AG205" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AJ205" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AM205" t="s">
         <v>186</v>
       </c>
       <c r="AO205" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AP205" t="s">
         <v>1098</v>
-      </c>
-      <c r="AP205" t="s">
-        <v>1099</v>
       </c>
     </row>
     <row r="206" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B206" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="C206" t="s">
         <v>166</v>
@@ -20230,7 +20218,7 @@
         <v>56</v>
       </c>
       <c r="AJ206" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="AK206">
         <v>-125</v>
@@ -20239,18 +20227,18 @@
         <v>177</v>
       </c>
       <c r="AO206" t="s">
+        <v>1100</v>
+      </c>
+      <c r="AP206" t="s">
         <v>1101</v>
-      </c>
-      <c r="AP206" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="207" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B207" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="C207" t="s">
         <v>192</v>
@@ -20298,10 +20286,10 @@
         <v>258</v>
       </c>
       <c r="AH207" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AI207" t="s">
         <v>1104</v>
-      </c>
-      <c r="AI207" t="s">
-        <v>1105</v>
       </c>
       <c r="AL207" t="s">
         <v>162</v>
@@ -20310,24 +20298,24 @@
         <v>177</v>
       </c>
       <c r="AN207" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AO207" t="s">
         <v>1106</v>
       </c>
-      <c r="AO207" t="s">
+      <c r="AP207" t="s">
         <v>1107</v>
       </c>
-      <c r="AP207" t="s">
+      <c r="AS207" t="s">
         <v>1108</v>
-      </c>
-      <c r="AS207" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="208" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B208" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C208" t="s">
         <v>192</v>
@@ -20384,10 +20372,10 @@
         <v>52</v>
       </c>
       <c r="AH208" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AI208" t="s">
         <v>1104</v>
-      </c>
-      <c r="AI208" t="s">
-        <v>1105</v>
       </c>
       <c r="AL208" t="s">
         <v>162</v>
@@ -20396,21 +20384,21 @@
         <v>54</v>
       </c>
       <c r="AN208" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="AO208" t="s">
+        <v>1110</v>
+      </c>
+      <c r="AP208" t="s">
         <v>1111</v>
-      </c>
-      <c r="AP208" t="s">
-        <v>1112</v>
       </c>
     </row>
     <row r="209" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B209" t="s">
         <v>1113</v>
-      </c>
-      <c r="B209" t="s">
-        <v>1114</v>
       </c>
       <c r="C209" t="s">
         <v>166</v>
@@ -20446,13 +20434,13 @@
         <v>119</v>
       </c>
       <c r="AB209" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="AC209" t="s">
         <v>48</v>
       </c>
       <c r="AD209" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AF209">
         <v>115</v>
@@ -20467,24 +20455,24 @@
         <v>143</v>
       </c>
       <c r="AM209" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AN209" t="s">
         <v>1116</v>
       </c>
-      <c r="AN209" t="s">
+      <c r="AO209" t="s">
         <v>1117</v>
       </c>
-      <c r="AO209" t="s">
+      <c r="AP209" t="s">
         <v>1118</v>
-      </c>
-      <c r="AP209" t="s">
-        <v>1119</v>
       </c>
     </row>
     <row r="210" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B210" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C210" t="s">
         <v>118</v>
@@ -20526,22 +20514,22 @@
         <v>24</v>
       </c>
       <c r="Y210" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AA210" t="s">
         <v>48</v>
       </c>
       <c r="AB210" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="AC210" t="s">
         <v>48</v>
       </c>
       <c r="AD210" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AE210" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="AF210">
         <v>129</v>
@@ -20550,27 +20538,27 @@
         <v>144</v>
       </c>
       <c r="AJ210" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AM210" t="s">
         <v>54</v>
       </c>
       <c r="AN210" t="s">
+        <v>1120</v>
+      </c>
+      <c r="AO210" t="s">
         <v>1121</v>
       </c>
-      <c r="AO210" t="s">
+      <c r="AP210" t="s">
         <v>1122</v>
-      </c>
-      <c r="AP210" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="211" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B211" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="C211" t="s">
         <v>118</v>
@@ -20612,22 +20600,22 @@
         <v>24</v>
       </c>
       <c r="Y211" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AA211" t="s">
         <v>48</v>
       </c>
       <c r="AB211" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="AC211" t="s">
         <v>48</v>
       </c>
       <c r="AD211" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AE211" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="AF211">
         <v>129</v>
@@ -20636,27 +20624,27 @@
         <v>144</v>
       </c>
       <c r="AJ211" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AM211" t="s">
         <v>54</v>
       </c>
       <c r="AN211" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="AO211" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="AP211" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="212" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B212" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="C212" t="s">
         <v>131</v>
@@ -20686,10 +20674,10 @@
         <v>24</v>
       </c>
       <c r="Y212" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AB212" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="AC212" t="s">
         <v>48</v>
@@ -20707,21 +20695,21 @@
         <v>54</v>
       </c>
       <c r="AN212" t="s">
+        <v>1126</v>
+      </c>
+      <c r="AO212" t="s">
         <v>1127</v>
       </c>
-      <c r="AO212" t="s">
+      <c r="AP212" t="s">
         <v>1128</v>
-      </c>
-      <c r="AP212" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="213" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B213" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="C213" t="s">
         <v>131</v>
@@ -20730,7 +20718,7 @@
         <v>4999</v>
       </c>
       <c r="E213" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="M213">
         <v>1</v>
@@ -20748,10 +20736,10 @@
         <v>24</v>
       </c>
       <c r="Y213" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="AB213" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="AC213" t="s">
         <v>48</v>
@@ -20766,24 +20754,24 @@
         <v>54</v>
       </c>
       <c r="AN213" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="AO213" t="s">
+        <v>1131</v>
+      </c>
+      <c r="AP213" t="s">
         <v>1132</v>
       </c>
-      <c r="AP213" t="s">
+      <c r="AS213" t="s">
         <v>1133</v>
-      </c>
-      <c r="AS213" t="s">
-        <v>1134</v>
       </c>
     </row>
     <row r="214" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B214" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="C214" t="s">
         <v>118</v>
@@ -20837,42 +20825,42 @@
         <v>24</v>
       </c>
       <c r="Y214" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AB214" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="AC214" t="s">
         <v>48</v>
       </c>
       <c r="AD214" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AF214">
         <v>129</v>
       </c>
       <c r="AI214" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="AM214" t="s">
         <v>54</v>
       </c>
       <c r="AN214" t="s">
+        <v>1136</v>
+      </c>
+      <c r="AO214" t="s">
         <v>1137</v>
       </c>
-      <c r="AO214" t="s">
+      <c r="AP214" t="s">
         <v>1138</v>
-      </c>
-      <c r="AP214" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="215" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B215" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="C215" t="s">
         <v>118</v>
@@ -20929,19 +20917,19 @@
         <v>24</v>
       </c>
       <c r="Y215" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AB215" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="AC215" t="s">
         <v>48</v>
       </c>
       <c r="AD215" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AE215" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="AF215">
         <v>130</v>
@@ -20950,27 +20938,27 @@
         <v>144</v>
       </c>
       <c r="AI215" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="AM215" t="s">
         <v>54</v>
       </c>
       <c r="AN215" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="AO215" t="s">
+        <v>1140</v>
+      </c>
+      <c r="AP215" t="s">
         <v>1141</v>
-      </c>
-      <c r="AP215" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="216" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B216" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C216" t="s">
         <v>131</v>
@@ -21024,19 +21012,19 @@
         <v>24</v>
       </c>
       <c r="Y216" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AB216" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="AC216" t="s">
         <v>48</v>
       </c>
       <c r="AD216" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AE216" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="AF216">
         <v>130</v>
@@ -21045,27 +21033,27 @@
         <v>144</v>
       </c>
       <c r="AI216" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="AM216" t="s">
         <v>54</v>
       </c>
       <c r="AN216" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="AO216" t="s">
+        <v>1143</v>
+      </c>
+      <c r="AP216" t="s">
         <v>1144</v>
-      </c>
-      <c r="AP216" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="217" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B217" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="C217" t="s">
         <v>131</v>
@@ -21077,7 +21065,7 @@
         <v>8</v>
       </c>
       <c r="F217" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G217">
         <v>8</v>
@@ -21122,19 +21110,19 @@
         <v>24</v>
       </c>
       <c r="Y217" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AB217" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="AC217" t="s">
         <v>48</v>
       </c>
       <c r="AD217" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AE217" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="AF217">
         <v>130</v>
@@ -21143,27 +21131,27 @@
         <v>144</v>
       </c>
       <c r="AI217" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="AM217" t="s">
         <v>54</v>
       </c>
       <c r="AN217" t="s">
+        <v>1146</v>
+      </c>
+      <c r="AO217" t="s">
         <v>1147</v>
       </c>
-      <c r="AO217" t="s">
+      <c r="AP217" t="s">
         <v>1148</v>
-      </c>
-      <c r="AP217" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="218" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B218" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="C218" t="s">
         <v>192</v>
@@ -21196,7 +21184,7 @@
         <v>49</v>
       </c>
       <c r="Z218" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AA218" t="s">
         <v>48</v>
@@ -21211,33 +21199,33 @@
         <v>95</v>
       </c>
       <c r="AH218" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AI218" t="s">
         <v>1151</v>
       </c>
-      <c r="AI218" t="s">
-        <v>1152</v>
-      </c>
       <c r="AK218" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AM218" t="s">
         <v>54</v>
       </c>
       <c r="AN218" t="s">
+        <v>1152</v>
+      </c>
+      <c r="AO218" t="s">
         <v>1153</v>
       </c>
-      <c r="AO218" t="s">
+      <c r="AP218" t="s">
         <v>1154</v>
-      </c>
-      <c r="AP218" t="s">
-        <v>1155</v>
       </c>
     </row>
     <row r="219" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B219" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="C219" t="s">
         <v>166</v>
@@ -21291,33 +21279,33 @@
         <v>52</v>
       </c>
       <c r="AH219" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AI219" t="s">
         <v>1151</v>
       </c>
-      <c r="AI219" t="s">
-        <v>1152</v>
-      </c>
       <c r="AK219" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AM219" t="s">
         <v>177</v>
       </c>
       <c r="AN219" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="AO219" t="s">
+        <v>1156</v>
+      </c>
+      <c r="AP219" t="s">
         <v>1157</v>
-      </c>
-      <c r="AP219" t="s">
-        <v>1158</v>
       </c>
     </row>
     <row r="220" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B220" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="C220" t="s">
         <v>192</v>
@@ -21371,33 +21359,33 @@
         <v>110</v>
       </c>
       <c r="AH220" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="AI220" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="AK220" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AM220" t="s">
         <v>177</v>
       </c>
       <c r="AN220" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="AO220" t="s">
+        <v>1160</v>
+      </c>
+      <c r="AP220" t="s">
         <v>1161</v>
-      </c>
-      <c r="AP220" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="221" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B221" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="C221" t="s">
         <v>166</v>
@@ -21448,36 +21436,36 @@
         <v>52</v>
       </c>
       <c r="AH221" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AI221" t="s">
         <v>1151</v>
       </c>
-      <c r="AI221" t="s">
-        <v>1152</v>
-      </c>
       <c r="AK221" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AM221" t="s">
         <v>177</v>
       </c>
       <c r="AN221" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="AO221" t="s">
+        <v>1163</v>
+      </c>
+      <c r="AP221" t="s">
         <v>1164</v>
       </c>
-      <c r="AP221" t="s">
+      <c r="AS221" t="s">
         <v>1165</v>
-      </c>
-      <c r="AS221" t="s">
-        <v>1166</v>
       </c>
     </row>
     <row r="222" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B222" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C222" t="s">
         <v>166</v>
@@ -21534,33 +21522,33 @@
         <v>52</v>
       </c>
       <c r="AH222" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AI222" t="s">
         <v>1151</v>
       </c>
-      <c r="AI222" t="s">
-        <v>1152</v>
-      </c>
       <c r="AK222" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AM222" t="s">
         <v>177</v>
       </c>
       <c r="AN222" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AO222" t="s">
         <v>1168</v>
       </c>
-      <c r="AO222" t="s">
+      <c r="AP222" t="s">
         <v>1169</v>
-      </c>
-      <c r="AP222" t="s">
-        <v>1170</v>
       </c>
     </row>
     <row r="223" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B223" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C223" t="s">
         <v>166</v>
@@ -21623,33 +21611,33 @@
         <v>52</v>
       </c>
       <c r="AH223" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AI223" t="s">
         <v>1151</v>
       </c>
-      <c r="AI223" t="s">
-        <v>1152</v>
-      </c>
       <c r="AK223" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AM223" t="s">
         <v>54</v>
       </c>
       <c r="AN223" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="AO223" t="s">
         <v>277</v>
       </c>
       <c r="AP223" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="224" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B224" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C224" t="s">
         <v>166</v>
@@ -21703,30 +21691,30 @@
         <v>110</v>
       </c>
       <c r="AH224" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AI224" t="s">
         <v>1151</v>
       </c>
-      <c r="AI224" t="s">
-        <v>1152</v>
-      </c>
       <c r="AK224" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AM224" t="s">
         <v>177</v>
       </c>
       <c r="AO224" t="s">
+        <v>1173</v>
+      </c>
+      <c r="AP224" t="s">
         <v>1174</v>
-      </c>
-      <c r="AP224" t="s">
-        <v>1175</v>
       </c>
     </row>
     <row r="225" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B225" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="C225" t="s">
         <v>154</v>
@@ -21771,7 +21759,7 @@
         <v>137</v>
       </c>
       <c r="V225" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="W225">
         <v>192</v>
@@ -21804,30 +21792,30 @@
         <v>119</v>
       </c>
       <c r="AH225" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AI225" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AM225" t="s">
         <v>186</v>
       </c>
       <c r="AN225" t="s">
+        <v>1177</v>
+      </c>
+      <c r="AO225" t="s">
         <v>1178</v>
       </c>
-      <c r="AO225" t="s">
+      <c r="AP225" t="s">
         <v>1179</v>
-      </c>
-      <c r="AP225" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="226" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B226" t="s">
         <v>1181</v>
-      </c>
-      <c r="B226" t="s">
-        <v>1182</v>
       </c>
       <c r="C226" t="s">
         <v>271</v>
@@ -21878,21 +21866,21 @@
         <v>177</v>
       </c>
       <c r="AN226" t="s">
+        <v>1182</v>
+      </c>
+      <c r="AO226" t="s">
         <v>1183</v>
       </c>
-      <c r="AO226" t="s">
+      <c r="AP226" t="s">
         <v>1184</v>
-      </c>
-      <c r="AP226" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="227" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B227" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="C227" t="s">
         <v>271</v>
@@ -21943,21 +21931,21 @@
         <v>177</v>
       </c>
       <c r="AN227" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="AO227" t="s">
+        <v>1186</v>
+      </c>
+      <c r="AP227" t="s">
         <v>1187</v>
-      </c>
-      <c r="AP227" t="s">
-        <v>1188</v>
       </c>
     </row>
     <row r="228" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B228" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C228" t="s">
         <v>271</v>
@@ -22008,48 +21996,48 @@
         <v>177</v>
       </c>
       <c r="AN228" t="s">
+        <v>1189</v>
+      </c>
+      <c r="AO228" t="s">
         <v>1190</v>
       </c>
-      <c r="AO228" t="s">
+      <c r="AP228" t="s">
         <v>1191</v>
       </c>
-      <c r="AP228" t="s">
+    </row>
+    <row r="229" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B229" t="s">
         <v>1192</v>
-      </c>
-    </row>
-    <row r="229" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A229" t="s">
-        <v>1181</v>
-      </c>
-      <c r="B229" t="s">
-        <v>1193</v>
       </c>
       <c r="C229" t="s">
         <v>47</v>
       </c>
-      <c r="E229" t="s">
-        <v>326</v>
-      </c>
-      <c r="F229" t="s">
-        <v>415</v>
-      </c>
-      <c r="N229" t="s">
-        <v>63</v>
-      </c>
-      <c r="O229" t="s">
-        <v>1194</v>
-      </c>
-      <c r="P229" t="s">
-        <v>137</v>
+      <c r="E229">
+        <v>16</v>
+      </c>
+      <c r="F229">
+        <v>4</v>
+      </c>
+      <c r="N229">
+        <v>2</v>
+      </c>
+      <c r="O229">
+        <v>6</v>
+      </c>
+      <c r="P229">
+        <v>1</v>
       </c>
       <c r="V229" t="s">
         <v>48</v>
       </c>
-      <c r="W229" t="s">
-        <v>1195</v>
-      </c>
-      <c r="X229" t="s">
-        <v>1196</v>
+      <c r="W229">
+        <v>96</v>
+      </c>
+      <c r="X229">
+        <v>32</v>
       </c>
       <c r="Y229" t="s">
         <v>49</v>
@@ -22060,40 +22048,40 @@
       <c r="AB229" t="s">
         <v>70</v>
       </c>
-      <c r="AD229" t="s">
-        <v>1066</v>
-      </c>
-      <c r="AF229" t="s">
-        <v>52</v>
-      </c>
-      <c r="AG229" t="s">
-        <v>378</v>
+      <c r="AD229">
+        <v>64</v>
+      </c>
+      <c r="AF229">
+        <v>110</v>
+      </c>
+      <c r="AG229">
+        <v>106</v>
       </c>
       <c r="AJ229" t="s">
-        <v>732</v>
-      </c>
-      <c r="AL229" t="s">
-        <v>684</v>
+        <v>731</v>
+      </c>
+      <c r="AL229">
+        <v>-126</v>
       </c>
       <c r="AM229" t="s">
         <v>54</v>
       </c>
       <c r="AN229" t="s">
-        <v>1197</v>
+        <v>1193</v>
       </c>
       <c r="AO229" t="s">
-        <v>1198</v>
+        <v>1194</v>
       </c>
       <c r="AP229" t="s">
-        <v>1199</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="230" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B230" t="s">
-        <v>1200</v>
+        <v>1196</v>
       </c>
       <c r="C230" t="s">
         <v>47</v>
@@ -22138,21 +22126,21 @@
         <v>54</v>
       </c>
       <c r="AN230" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="AO230" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="AP230" t="s">
-        <v>1202</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="231" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B231" t="s">
-        <v>1203</v>
+        <v>1199</v>
       </c>
       <c r="C231" t="s">
         <v>47</v>
@@ -22197,7 +22185,7 @@
         <v>48</v>
       </c>
       <c r="AJ231" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AL231" t="s">
         <v>162</v>
@@ -22206,18 +22194,18 @@
         <v>54</v>
       </c>
       <c r="AO231" t="s">
-        <v>1204</v>
+        <v>1200</v>
       </c>
       <c r="AP231" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="232" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B232" t="s">
-        <v>1206</v>
+        <v>1202</v>
       </c>
       <c r="C232" t="s">
         <v>47</v>
@@ -22268,21 +22256,21 @@
         <v>54</v>
       </c>
       <c r="AN232" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="AO232" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="AP232" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="233" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B233" t="s">
-        <v>1208</v>
+        <v>1204</v>
       </c>
       <c r="C233" t="s">
         <v>47</v>
@@ -22327,7 +22315,7 @@
         <v>48</v>
       </c>
       <c r="AJ233" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AL233" t="s">
         <v>162</v>
@@ -22336,18 +22324,18 @@
         <v>54</v>
       </c>
       <c r="AO233" t="s">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="AP233" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="234" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B234" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="C234" t="s">
         <v>47</v>
@@ -22395,10 +22383,10 @@
         <v>48</v>
       </c>
       <c r="AD234" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="AG234" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="AJ234" t="s">
         <v>53</v>
@@ -22410,21 +22398,21 @@
         <v>54</v>
       </c>
       <c r="AN234" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="AO234" t="s">
-        <v>1213</v>
+        <v>1209</v>
       </c>
       <c r="AP234" t="s">
-        <v>1214</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="235" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B235" t="s">
-        <v>1215</v>
+        <v>1211</v>
       </c>
       <c r="C235" t="s">
         <v>47</v>
@@ -22472,10 +22460,10 @@
         <v>48</v>
       </c>
       <c r="AD235" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="AF235" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="AJ235" t="s">
         <v>53</v>
@@ -22487,18 +22475,18 @@
         <v>54</v>
       </c>
       <c r="AO235" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="AP235" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="236" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B236" t="s">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="C236" t="s">
         <v>47</v>
@@ -22546,10 +22534,10 @@
         <v>48</v>
       </c>
       <c r="AD236" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="AG236" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="AJ236" t="s">
         <v>53</v>
@@ -22561,18 +22549,18 @@
         <v>54</v>
       </c>
       <c r="AO236" t="s">
-        <v>1219</v>
+        <v>1215</v>
       </c>
       <c r="AP236" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="237" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B237" t="s">
-        <v>1221</v>
+        <v>1217</v>
       </c>
       <c r="C237" t="s">
         <v>47</v>
@@ -22620,10 +22608,10 @@
         <v>48</v>
       </c>
       <c r="AD237" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="AF237" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="AJ237" t="s">
         <v>53</v>
@@ -22635,21 +22623,21 @@
         <v>54</v>
       </c>
       <c r="AN237" t="s">
-        <v>1222</v>
+        <v>1218</v>
       </c>
       <c r="AO237" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="AP237" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="238" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B238" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="C238" t="s">
         <v>118</v>
@@ -22679,7 +22667,7 @@
         <v>24</v>
       </c>
       <c r="Y238" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="AF238" t="s">
         <v>252</v>
@@ -22691,21 +22679,21 @@
         <v>54</v>
       </c>
       <c r="AN238" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
       <c r="AO238" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
       <c r="AP238" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="239" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B239" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="C239" t="s">
         <v>192</v>
@@ -22768,21 +22756,21 @@
         <v>54</v>
       </c>
       <c r="AN239" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="AO239" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
       <c r="AP239" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="240" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B240" t="s">
-        <v>1234</v>
+        <v>1230</v>
       </c>
       <c r="C240" t="s">
         <v>192</v>
@@ -22842,21 +22830,21 @@
         <v>54</v>
       </c>
       <c r="AN240" t="s">
+        <v>1227</v>
+      </c>
+      <c r="AO240" t="s">
+        <v>1228</v>
+      </c>
+      <c r="AP240" t="s">
         <v>1231</v>
-      </c>
-      <c r="AO240" t="s">
-        <v>1232</v>
-      </c>
-      <c r="AP240" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="241" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B241" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="C241" t="s">
         <v>166</v>
@@ -22889,7 +22877,7 @@
         <v>32</v>
       </c>
       <c r="Y241" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="AB241" t="s">
         <v>70</v>
@@ -22904,10 +22892,10 @@
         <v>125</v>
       </c>
       <c r="AH241" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="AI241" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="AK241" t="s">
         <v>162</v>
@@ -22916,24 +22904,24 @@
         <v>54</v>
       </c>
       <c r="AN241" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="AO241" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="AP241" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="AS241" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="242" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B242" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="C242" t="s">
         <v>166</v>
@@ -22966,7 +22954,7 @@
         <v>32</v>
       </c>
       <c r="Y242" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="Z242" t="s">
         <v>167</v>
@@ -22996,21 +22984,21 @@
         <v>54</v>
       </c>
       <c r="AN242" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="AO242" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="AP242" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="243" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B243" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="C243" t="s">
         <v>166</v>
@@ -23043,7 +23031,7 @@
         <v>32</v>
       </c>
       <c r="Y243" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="AB243" t="s">
         <v>70</v>
@@ -23058,10 +23046,10 @@
         <v>125</v>
       </c>
       <c r="AH243" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="AI243" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="AK243" t="s">
         <v>162</v>
@@ -23070,21 +23058,21 @@
         <v>54</v>
       </c>
       <c r="AN243" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="AO243" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="AP243" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="244" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B244" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="C244" t="s">
         <v>166</v>
@@ -23120,7 +23108,7 @@
         <v>32</v>
       </c>
       <c r="Y244" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="Z244" t="s">
         <v>167</v>
@@ -23132,7 +23120,7 @@
         <v>70</v>
       </c>
       <c r="AC244" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
       <c r="AD244">
         <v>54</v>
@@ -23153,21 +23141,21 @@
         <v>54</v>
       </c>
       <c r="AN244" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="AO244" t="s">
-        <v>1253</v>
+        <v>1249</v>
       </c>
       <c r="AP244" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="245" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B245" t="s">
-        <v>1255</v>
+        <v>1251</v>
       </c>
       <c r="C245" t="s">
         <v>154</v>
@@ -23200,7 +23188,7 @@
         <v>32</v>
       </c>
       <c r="Y245" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="AB245" t="s">
         <v>70</v>
@@ -23215,10 +23203,10 @@
         <v>125</v>
       </c>
       <c r="AH245" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="AI245" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="AK245" t="s">
         <v>162</v>
@@ -23227,21 +23215,21 @@
         <v>54</v>
       </c>
       <c r="AN245" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="AO245" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
       <c r="AP245" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="246" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B246" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="C246" t="s">
         <v>271</v>
@@ -23292,21 +23280,21 @@
         <v>54</v>
       </c>
       <c r="AN246" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="AO246" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="AP246" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="247" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B247" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="C247" t="s">
         <v>271</v>
@@ -23351,18 +23339,18 @@
         <v>54</v>
       </c>
       <c r="AO247" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="AP247" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="248" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="B248" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="C248" t="s">
         <v>192</v>
@@ -23407,30 +23395,30 @@
         <v>48</v>
       </c>
       <c r="AD248" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="AK248" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="AM248" t="s">
         <v>157</v>
       </c>
       <c r="AO248" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="AP248" t="s">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="AS248" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="249" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="B249" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="C249" t="s">
         <v>192</v>
@@ -23472,27 +23460,27 @@
         <v>48</v>
       </c>
       <c r="AD249" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="AK249">
         <v>-120</v>
       </c>
       <c r="AM249" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AO249" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="AP249" t="s">
-        <v>1269</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="250" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="B250" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
       <c r="C250" t="s">
         <v>192</v>
@@ -23534,30 +23522,30 @@
         <v>48</v>
       </c>
       <c r="AD250" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="AK250" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="AM250" t="s">
         <v>157</v>
       </c>
       <c r="AO250" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="AP250" t="s">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="AS250" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="251" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="B251" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="C251" t="s">
         <v>47</v>
@@ -23605,7 +23593,7 @@
         <v>70</v>
       </c>
       <c r="AD251" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="AK251" t="s">
         <v>162</v>
@@ -23614,18 +23602,18 @@
         <v>54</v>
       </c>
       <c r="AO251" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="AP251" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="252" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="B252" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="C252" t="s">
         <v>47</v>
@@ -23682,18 +23670,18 @@
         <v>177</v>
       </c>
       <c r="AO252" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="AP252" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="253" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="B253" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="C253" t="s">
         <v>47</v>
@@ -23741,27 +23729,27 @@
         <v>48</v>
       </c>
       <c r="AD253" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="AK253">
         <v>-128</v>
       </c>
       <c r="AM253" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="AO253" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="AP253" t="s">
-        <v>1287</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="254" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="B254" t="s">
-        <v>1288</v>
+        <v>1284</v>
       </c>
       <c r="C254" t="s">
         <v>47</v>
@@ -23812,24 +23800,24 @@
         <v>48</v>
       </c>
       <c r="AK254" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="AM254" t="s">
         <v>157</v>
       </c>
       <c r="AO254" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="AP254" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="255" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="B255" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
       <c r="C255" t="s">
         <v>47</v>
@@ -23874,27 +23862,27 @@
         <v>70</v>
       </c>
       <c r="AD255" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="AK255" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
       <c r="AM255" t="s">
         <v>186</v>
       </c>
       <c r="AO255" t="s">
-        <v>1294</v>
+        <v>1290</v>
       </c>
       <c r="AP255" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="256" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="B256" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
       <c r="C256" t="s">
         <v>47</v>
@@ -23939,27 +23927,27 @@
         <v>48</v>
       </c>
       <c r="AD256" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="AK256">
         <v>-128</v>
       </c>
       <c r="AM256" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="AO256" t="s">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="AP256" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="257" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="B257" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="C257" t="s">
         <v>47</v>
@@ -24010,21 +23998,21 @@
         <v>-120</v>
       </c>
       <c r="AM257" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AO257" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="AP257" t="s">
-        <v>1301</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="258" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="B258" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="C258" t="s">
         <v>271</v>
@@ -24060,18 +24048,18 @@
         <v>157</v>
       </c>
       <c r="AO258" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="AP258" t="s">
-        <v>1304</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="259" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="B259" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="C259" t="s">
         <v>271</v>
@@ -24104,27 +24092,27 @@
         <v>48</v>
       </c>
       <c r="AD259" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="AK259">
         <v>-125</v>
       </c>
       <c r="AM259" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AO259" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="AP259" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="260" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="B260" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
       <c r="C260" t="s">
         <v>271</v>
@@ -24160,24 +24148,24 @@
         <v>70</v>
       </c>
       <c r="AK260" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="AM260" t="s">
         <v>54</v>
       </c>
       <c r="AO260" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
       <c r="AP260" t="s">
-        <v>1312</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="261" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="B261" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="C261" t="s">
         <v>192</v>
@@ -24228,13 +24216,13 @@
         <v>177</v>
       </c>
       <c r="AO261" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="AP261" t="s">
-        <v>1315</v>
+        <v>1311</v>
       </c>
       <c r="AS261" t="s">
-        <v>1316</v>
+        <v>1312</v>
       </c>
     </row>
   </sheetData>
@@ -24256,7 +24244,7 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>1317</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -24309,7 +24297,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="B8">
         <v>216</v>
